--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,26 @@
       <c r="AB1" t="inlineStr">
         <is>
           <t>fetched_at</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>jobPosterName</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>jobPosterTitle</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>jobPosterPhoto</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>jobPosterProfileUrl</t>
         </is>
       </c>
     </row>
@@ -736,6 +756,10 @@
           <t>2026-08-10 23:08:44</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -906,6 +930,10 @@
           <t>2026-08-10 23:08:44</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1058,7 +1086,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Applied</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1066,6 +1094,10 @@
           <t>2026-08-10 23:08:44</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1231,7 +1263,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Applied</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1239,6 +1271,10 @@
           <t>2026-08-10 23:08:44</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1383,7 +1419,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Applied</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1391,6 +1427,10 @@
           <t>2026-08-10 23:08:44</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1550,6 +1590,10 @@
           <t>2026-08-11 03:52:50</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1679,6 +1723,10 @@
           <t>2026-08-11 03:52:50</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1688,17 +1736,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>YZLDOJbTgDN7DceTGuz6iw==</t>
+          <t>2Y/GtKDklv9m2IDcmvsS0Q==</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5gEGmjK1l08I5JmqFjxRSQ==</t>
+          <t>Ffzy0lJRgiAw/r6tRiN8hA==</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-at-modmed-4404238079?position=2&amp;pageNum=0&amp;refId=5gEGmjK1l08I5JmqFjxRSQ%3D%3D&amp;trackingId=YZLDOJbTgDN7DceTGuz6iw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-at-modmed-4404238079?position=2&amp;pageNum=0&amp;refId=Ffzy0lJRgiAw%2Fr6tRiN8hA%3D%3D&amp;trackingId=2Y%2FGtKDklv9m2IDcmvsS0Q%3D%3D</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1831,7 +1879,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2369.0</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1841,246 +1889,79 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-08-11 03:52:50</t>
-        </is>
-      </c>
+          <t>2026-08-11 05:04:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4447986743</t>
+          <t>4445514865</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>iFZVVm4WOz45d7Q2Q7vt3g==</t>
+          <t>EqjXu/bxwfV7F/9cdE7qxw==</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5gEGmjK1l08I5JmqFjxRSQ==</t>
+          <t>Ffzy0lJRgiAw/r6tRiN8hA==</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/ai-engineer-internal-enablement-productivity-at-air-4447986743?position=3&amp;pageNum=0&amp;refId=5gEGmjK1l08I5JmqFjxRSQ%3D%3D&amp;trackingId=iFZVVm4WOz45d7Q2Q7vt3g%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-at-glider-ai-4445514865?position=5&amp;pageNum=0&amp;refId=Ffzy0lJRgiAw%2Fr6tRiN8hA%3D%3D&amp;trackingId=EqjXu%2FbxwfV7F%2F9cdE7qxw%3D%3D</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Internal Enablement &amp; Productivity</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air</t>
+          <t>Glider AI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/air-enterprise-readiness?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+          <t>https://www.linkedin.com/company/gliderai?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFUgvesvqurgw/company-logo_100_100/B4EZ7viW5zHMAI-/0/1782135222131?e=2147483647&amp;v=beta&amp;t=NliZK02iNO4q7OL6nsyEZ8Ir1XvaysuGPR5AIDPYIQg</t>
+          <t>https://media.licdn.com/dms/image/v2/C4E0BAQHUPIR6pwgZ7w/company-logo_100_100/company-logo_100_100/0/1630648590497/gliderai_logo?e=2147483647&amp;v=beta&amp;t=hNJVeBZomt0-EsbukzOI6BcCYFvhGkkPl1UhWBZQ0kg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA</t>
+          <t>Houston, TX</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Company Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Air is the leader in Enterprise Readiness. Our mission is to establish readiness as a real-time condition that is continuously achieved. Today, a dangerous Readiness Gap exists between what the front line needs and what is delivered. Our AI-native platform, Air Enterprise Readiness, aligns development, production, delivery, and sustainment into one coordinated execution system for government agencies and industrial suppliers. By revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands, the front line gets what it needs to succeed.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Job Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We are seeking an experienced AI Engineer to join our AI Enablement team, focused on rapidly increasing internal employee productivity and operational efficiency across the company by scaling robust AI integrations and agentic workflows. This role will be central to designing and deploying agents to handle complex, end-to-end tasks, driving measurable improvements in how our core teams (e.g., Product, Engineering, Operations, and Customer Success) work. This strategic and execution-focused role will lead our internal AI Enablement roadmap, initially focusing deeply on improving core departments (e.g., Sales, Marketing, Product, Engineering, Operations, and Customer Success) through agentic automation.&lt;br&gt;&lt;br&gt;You'll leverage best-in-class AI tools and AI agents (e.g. Gemini and other LLMs) to dramatically increase employee productivity, drive down operational costs, and enable our teams to deliver faster, better outcomes at scale. Your goal is to build our foundation for an AI-enabled future, implementing AI-driven workflows and agents throughout the organization, starting with internal operations and coupling workflows across key functions like GTM.&lt;br&gt;&lt;br&gt;To do this job well, we are looking for someone who can demonstrate project(s) built on LLMs that showcases your skill at reliably automating complex tasks.&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Experience integrating and working with LLMs, with a strong understanding of their capabilities and limitations&lt;/li&gt;&lt;li&gt;Experience integrating and working with agent frameworks (e.g. Claude Agent SDK, Google Anti-Gravity, OpenAI Agent SDK)&lt;/li&gt;&lt;li&gt;Experience building observability, evaluation, and feedback loops for agent behavior (telemetry, prompt evaluation, regression testing, and reliability metrics).&lt;/li&gt;&lt;li&gt;Experience working in highly ambiguous environments, and operate with urgency&lt;/li&gt;&lt;li&gt;Startup experience, particularly in scaling products from zero to one&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Strong Candidates Have&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Deep experience leveraging agents across applications and business workflows to drive meaningful impact&lt;/li&gt;&lt;li&gt;Experience designing and deploying complex agentic systems using LLMs (e.g. deep research)&lt;/li&gt;&lt;li&gt;Hands-on work with multi-agent coordination, routing, and tool orchestration&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;This role is a full-time position located out of our office in Arlington, VA or Pittsburgh, PA. This role may require up to 25% travel.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Scope Of Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Designs and builds multi-agent systems with tool use, memory, routing, and planning to automate internal business processes and enhance employee capabilities.&lt;/li&gt;&lt;li&gt;Develops Agent Skills and tools as modular, composable services that interact with backend systems, models, and data processing to increase internal team velocity.&lt;/li&gt;&lt;li&gt;Contribute to the technical architecture and engineering standards for internal agentic systems, ensuring scalability, reliability, and maintainability across the organization.&lt;/li&gt;&lt;li&gt;Assist with automated evaluation of agents, skills, and prompts across the entire product lifecycle to ensure reliable internal tools.&lt;/li&gt;&lt;li&gt;Partner with internal Product, Engineering, GTM, and Operations teams to identify and implement AI-driven solutions to optimize their workflows and reduce operational costs.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;How We Define Success (Key Metrics)Internal Team Enablement (Operations, Customer Success, Engineering)&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Operational Cost Savings: Reduce operational expenses for targeted teams through workflow automation via AI agents.&lt;/li&gt;&lt;li&gt;Employee Productivity: Achieve measurable increases in internal team capacity and velocity through AI-driven workflows and tools.&lt;/li&gt;&lt;li&gt;Internal Adoption Rate: Achieve a high adoption rate of new AI agents and enablement tools within key departments within the first 90 days.&lt;/li&gt;&lt;li&gt;Accelerated Development: Reduce feature development timelines through AI-assisted coding, documentation, and testing tools.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;U.S. Citizenship is required&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Required Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Bachelor's, Master’s, or Doctorate in Computer Science, Computer Engineering, Data Science, or a related field&lt;/li&gt;&lt;li&gt;Minimum 3 years of experience building and deploying ML or LLM-powered systems in production environments&lt;/li&gt;&lt;li&gt;Practical experience in building, developing, and productionizing machine learning systems&lt;/li&gt;&lt;li&gt;Advanced software skills in Python and other programming languages&lt;/li&gt;&lt;li&gt;Experience with common LLM algorithms and implementations, including coding agents (e.g. Claude Code and GenAI coding best practices).&lt;/li&gt;&lt;li&gt;Hands-on experience with cloud infrastructure (e.g. AWS, GCP)&lt;/li&gt;&lt;li&gt;A strong desire to learn and investigate new technologies&lt;/li&gt;&lt;li&gt;Familiarity with Git source control management&lt;/li&gt;&lt;li&gt;Ability to work collaboratively with little supervision&lt;/li&gt;&lt;li&gt;A burning desire to work in a challenging fast-paced tech environment&lt;/li&gt;&lt;li&gt;A burning desire to work in a challenging fast-paced tech environment&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Desired Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Current possession of a U.S. security clearance, or the ability to obtain one with our sponsorship&lt;/li&gt;&lt;li&gt;Experience in or exposure to the nuances of a startup or other entrepreneurial environment&lt;/li&gt;&lt;li&gt;Experience with modern front-end frameworks (e.g., React, Next.js, or similar) and API-driven UI architectures&lt;/li&gt;&lt;/ul&gt;</t>
+          <t>&lt;p&gt;&lt;strong&gt;Locations (Hybrid):&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Richardson, TX&amp;nbsp;&lt;/p&gt;&lt;p&gt;Houston, TX&lt;/p&gt;&lt;p&gt;Raleigh, NC&amp;nbsp;&lt;/p&gt;&lt;p&gt;Charlotte, NC&lt;/p&gt;&lt;p&gt;Somerset, NJ&lt;/p&gt;&lt;p&gt;Tempe, AZ&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Relocation Assistance:&lt;/strong&gt; Relocation package is available for eligible candidates.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About the Role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are seeking an experienced &lt;strong&gt;AI Engineer&lt;/strong&gt; with expertise in &lt;strong&gt;Generative AI&lt;/strong&gt; to design, build, and deploy cutting-edge AI solutions that solve complex business challenges. You will work alongside talented engineers, data scientists, and product teams to develop scalable AI applications powered by Large Language Models (LLMs), machine learning, and cloud technologies.&lt;/p&gt;&lt;p&gt;If you're passionate about innovation, AI, and building production-ready intelligent systems, we'd love to hear from you.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What You'll Do&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Analyze user stories and business requirements to deliver production-ready AI solutions.&lt;/p&gt;&lt;p&gt;Design and develop scalable, high-quality, and optimized software applications.&lt;/p&gt;&lt;p&gt;Build, fine-tune, evaluate, and deploy Large Language Models (LLMs) for business use cases.&lt;/p&gt;&lt;p&gt;Develop Generative AI applications for text generation, code generation, document intelligence, automation, and other AI-driven solutions.&lt;/p&gt;&lt;p&gt;Create reusable frameworks, automation scripts, and technical assets to improve engineering productivity.&lt;/p&gt;&lt;p&gt;Debug and resolve complex technical issues across applications and databases.&lt;/p&gt;&lt;p&gt;Collaborate with cross-functional teams including Data Science, Engineering, and Product Management.&lt;/p&gt;&lt;p&gt;Support Proof of Concepts (POCs) and evaluate emerging AI technologies.&lt;/p&gt;&lt;p&gt;Ensure reliable, secure, and production-ready deployments.&lt;/p&gt;&lt;p&gt;Contribute to knowledge sharing, technical documentation, and engineering best practices.&lt;/p&gt;&lt;p&gt;Promote responsible AI development with a focus on fairness, explainability, and bias mitigation.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Required Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Experience developing and deploying &lt;strong&gt;Generative AI&lt;/strong&gt; solutions.&lt;/p&gt;&lt;p&gt;Strong understanding of Machine Learning, Deep Learning, and Natural Language Processing (NLP).&lt;/p&gt;&lt;p&gt;Experience working with Large Language Models (LLMs) and model fine-tuning.&lt;/p&gt;&lt;p&gt;Strong programming skills in &lt;strong&gt;Python&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Hands-on experience with &lt;strong&gt;TensorFlow&lt;/strong&gt;, &lt;strong&gt;PyTorch&lt;/strong&gt;, or similar deep learning frameworks.&lt;/p&gt;&lt;p&gt;Experience managing the complete AI development lifecycle, including data preparation, model training, evaluation, optimization, and deployment.&lt;/p&gt;&lt;p&gt;Strong analytical, debugging, and problem-solving skills.&lt;/p&gt;&lt;p&gt;Excellent communication and collaboration abilities.&lt;/p&gt;&lt;p&gt;Ability to thrive in a fast-paced, collaborative engineering environment.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Preferred Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Experience with cloud platforms such as &lt;strong&gt;AWS&lt;/strong&gt;, &lt;strong&gt;Azure&lt;/strong&gt;, &lt;strong&gt;Google Cloud Platform (GCP)&lt;/strong&gt;, or &lt;strong&gt;OpenShift&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Experience with open-source AI technologies and frameworks.&lt;/p&gt;&lt;p&gt;Active contributions to open-source projects or technology communities.&lt;/p&gt;&lt;p&gt;Industry certifications related to AI, Machine Learning, or Cloud technologies.&lt;/p&gt;&lt;p&gt;Strong coding background with achievements on platforms such as HackerRank, CodeChef, or similar.&lt;/p&gt;&lt;p&gt;Experience building scalable, enterprise-grade AI applications.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Education&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Bachelor's degree (or foreign equivalent) in Computer Science, Engineering, or a related technical field.&lt;/p&gt;&lt;p&gt;Equivalent professional experience will also be considered.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Work Authorization&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Candidates must be authorized to work for any employer in the United States.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Employer-based visa sponsorship is not available for this position, now or in the future.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Benefits&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We offer a competitive compensation and benefits package, including:&lt;/p&gt;&lt;p&gt;Medical, Dental &amp;amp; Vision Insurance&lt;/p&gt;&lt;p&gt;Life Insurance&lt;/p&gt;&lt;p&gt;Short-Term &amp;amp; Long-Term Disability Coverage&lt;/p&gt;&lt;p&gt;Health &amp;amp; Dependent Care Reimbursement Accounts&lt;/p&gt;&lt;p&gt;Supplemental Insurance (Accident, Critical Illness, Hospital Indemnity, Legal)&lt;/p&gt;&lt;p&gt;401(k) Retirement Plan&lt;/p&gt;&lt;p&gt;Paid Holidays&lt;/p&gt;&lt;p&gt;Generous Paid Time Off (PTO)&lt;/p&gt;&lt;p&gt;Relocation Assistance for eligible candidates&lt;/p&gt;&lt;p&gt;Career development and continuous learning opportunities&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Apply Today!&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;If you're passionate about Artificial Intelligence, Generative AI, and building innovative solutions that make a real impact, we'd love to connect with you.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;📩 Apply today or reach out directly to learn more about this opportunity.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Company Description
-Air is the leader in Enterprise Readiness. Our mission is to establish readiness as a real-time condition that is continuously achieved. Today, a dangerous Readiness Gap exists between what the front line needs and what is delivered. Our AI-native platform, Air Enterprise Readiness, aligns development, production, delivery, and sustainment into one coordinated execution system for government agencies and industrial suppliers. By revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands, the front line gets what it needs to succeed.
-Job Description
-We are seeking an experienced AI Engineer to join our AI Enablement team, focused on rapidly increasing internal employee productivity and operational efficiency across the company by scaling robust AI integrations and agentic workflows. This role will be central to designing and deploying agents to handle complex, end-to-end tasks, driving measurable improvements in how our core teams (e.g., Product, Engineering, Operations, and Customer Success) work. This strategic and execution-focused role will lead our internal AI Enablement roadmap, initially focusing deeply on improving core departments (e.g., Sales, Marketing, Product, Engineering, Operations, and Customer Success) through agentic automation.
-You'll leverage best-in-class AI tools and AI agents (e.g. Gemini and other LLMs) to dramatically increase employee productivity, drive down operational costs, and enable our teams to deliver faster, better outcomes at scale. Your goal is to build our foundation for an AI-enabled future, implementing AI-driven workflows and agents throughout the organization, starting with internal operations and coupling workflows across key functions like GTM.
-To do this job well, we are looking for someone who can demonstrate project(s) built on LLMs that showcases your skill at reliably automating complex tasks.
-- Experience integrating and working with LLMs, with a strong understanding of their capabilities and limitations
-- Experience integrating and working with agent frameworks (e.g. Claude Agent SDK, Google Anti-Gravity, OpenAI Agent SDK)
-- Experience building observability, evaluation, and feedback loops for agent behavior (telemetry, prompt evaluation, regression testing, and reliability metrics).
-- Experience working in highly ambiguous environments, and operate with urgency
-- Startup experience, particularly in scaling products from zero to one
-Strong Candidates Have
-- Deep experience leveraging agents across applications and business workflows to drive meaningful impact
-- Experience designing and deploying complex agentic systems using LLMs (e.g. deep research)
-- Hands-on work with multi-agent coordination, routing, and tool orchestration
-This role is a full-time position located out of our office in Arlington, VA or Pittsburgh, PA. This role may require up to 25% travel.
-Scope Of Responsibilities
-- Designs and builds multi-agent systems with tool use, memory, routing, and planning to automate internal business processes and enhance employee capabilities.
-- Develops Agent Skills and tools as modular, composable services that interact with backend systems, models, and data processing to increase internal team velocity.
-- Contribute to the technical architecture and engineering standards for internal agentic systems, ensuring scalability, reliability, and maintainability across the organization.
-- Assist with automated evaluation of agents, skills, and prompts across the entire product lifecycle to ensure reliable internal tools.
-- Partner with internal Product, Engineering, GTM, and Operations teams to identify and implement AI-driven solutions to optimize their workflows and reduce operational costs.
-How We Define Success (Key Metrics)Internal Team Enablement (Operations, Customer Success, Engineering)
-- Operational Cost Savings: Reduce operational expenses for targeted teams through workflow automation via AI agents.
-- Employee Productivity: Achieve measurable increases in internal team capacity and velocity through AI-driven workflows and tools.
-- Internal Adoption Rate: Achieve a high adoption rate of new AI agents and enablement tools within key departments within the first 90 days.
-- Accelerated Development: Reduce feature development timelines through AI-assisted coding, documentation, and testing tools.
-Qualifications
-- U.S. Citizenship is required
-Required Skills
-- Bachelor's, Master’s, or Doctorate in Computer Science, Computer Engineering, Data Science, or a related field
-- Minimum 3 years of experience building and deploying ML or LLM-powered systems in production environments
-- Practical experience in building, developing, and productionizing machine learning systems
-- Advanced software skills in Python and other programming languages
-- Experience with common LLM algorithms and implementations, including coding agents (e.g. Claude Code and GenAI coding best practices).
-- Hands-on experience with cloud infrastructure (e.g. AWS, GCP)
-- A strong desire to learn and investigate new technologies
-- Familiarity with Git source control management
-- Ability to work collaboratively with little supervision
-- A burning desire to work in a challenging fast-paced tech environment
-- A burning desire to work in a challenging fast-paced tech environment
-Desired Skills
-- Current possession of a U.S. security clearance, or the ability to obtain one with our sponsorship
-- Experience in or exposure to the nuances of a startup or other entrepreneurial environment
-- Experience with modern front-end frameworks (e.g., React, Next.js, or similar) and API-driven UI architectures</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Not Applicable</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Full-time</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Engineering and Information Technology</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Software Development</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>https://air.ai/</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Enterprise Readiness</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Air (formerly Govini) created Enterprise Readiness, a new category of AI-native platforms that close the Readiness Gap, a dangerous chasm between what the front line needs and what the national security enterprise delivers. Air Enterprise Readiness platform aligns development, production, delivery, and sustainment into one coordinated execution system, revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands. The result: the enterprise has what it needs to succeed.
-Air has offices in Arlington, Virginia and Pittsburgh, Pennsylvania.</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>166.0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2026-08-11 03:52:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>4445514865</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Bs2UXzWJ8rNOnOXlLgnRug==</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5gEGmjK1l08I5JmqFjxRSQ==</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/ai-engineer-at-glider-ai-4445514865?position=5&amp;pageNum=0&amp;refId=5gEGmjK1l08I5JmqFjxRSQ%3D%3D&amp;trackingId=Bs2UXzWJ8rNOnOXlLgnRug%3D%3D</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Glider AI</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/gliderai?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQHUPIR6pwgZ7w/company-logo_100_100/company-logo_100_100/0/1630648590497/gliderai_logo?e=2147483647&amp;v=beta&amp;t=hNJVeBZomt0-EsbukzOI6BcCYFvhGkkPl1UhWBZQ0kg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Houston, TX</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;strong&gt;Locations (Hybrid):&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Richardson, TX&amp;nbsp;&lt;/p&gt;&lt;p&gt;Houston, TX&lt;/p&gt;&lt;p&gt;Raleigh, NC&amp;nbsp;&lt;/p&gt;&lt;p&gt;Charlotte, NC&lt;/p&gt;&lt;p&gt;Somerset, NJ&lt;/p&gt;&lt;p&gt;Tempe, AZ&amp;nbsp;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Relocation Assistance:&lt;/strong&gt; Relocation package is available for eligible candidates.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About the Role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are seeking an experienced &lt;strong&gt;AI Engineer&lt;/strong&gt; with expertise in &lt;strong&gt;Generative AI&lt;/strong&gt; to design, build, and deploy cutting-edge AI solutions that solve complex business challenges. You will work alongside talented engineers, data scientists, and product teams to develop scalable AI applications powered by Large Language Models (LLMs), machine learning, and cloud technologies.&lt;/p&gt;&lt;p&gt;If you're passionate about innovation, AI, and building production-ready intelligent systems, we'd love to hear from you.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What You'll Do&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Analyze user stories and business requirements to deliver production-ready AI solutions.&lt;/p&gt;&lt;p&gt;Design and develop scalable, high-quality, and optimized software applications.&lt;/p&gt;&lt;p&gt;Build, fine-tune, evaluate, and deploy Large Language Models (LLMs) for business use cases.&lt;/p&gt;&lt;p&gt;Develop Generative AI applications for text generation, code generation, document intelligence, automation, and other AI-driven solutions.&lt;/p&gt;&lt;p&gt;Create reusable frameworks, automation scripts, and technical assets to improve engineering productivity.&lt;/p&gt;&lt;p&gt;Debug and resolve complex technical issues across applications and databases.&lt;/p&gt;&lt;p&gt;Collaborate with cross-functional teams including Data Science, Engineering, and Product Management.&lt;/p&gt;&lt;p&gt;Support Proof of Concepts (POCs) and evaluate emerging AI technologies.&lt;/p&gt;&lt;p&gt;Ensure reliable, secure, and production-ready deployments.&lt;/p&gt;&lt;p&gt;Contribute to knowledge sharing, technical documentation, and engineering best practices.&lt;/p&gt;&lt;p&gt;Promote responsible AI development with a focus on fairness, explainability, and bias mitigation.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Required Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Experience developing and deploying &lt;strong&gt;Generative AI&lt;/strong&gt; solutions.&lt;/p&gt;&lt;p&gt;Strong understanding of Machine Learning, Deep Learning, and Natural Language Processing (NLP).&lt;/p&gt;&lt;p&gt;Experience working with Large Language Models (LLMs) and model fine-tuning.&lt;/p&gt;&lt;p&gt;Strong programming skills in &lt;strong&gt;Python&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Hands-on experience with &lt;strong&gt;TensorFlow&lt;/strong&gt;, &lt;strong&gt;PyTorch&lt;/strong&gt;, or similar deep learning frameworks.&lt;/p&gt;&lt;p&gt;Experience managing the complete AI development lifecycle, including data preparation, model training, evaluation, optimization, and deployment.&lt;/p&gt;&lt;p&gt;Strong analytical, debugging, and problem-solving skills.&lt;/p&gt;&lt;p&gt;Excellent communication and collaboration abilities.&lt;/p&gt;&lt;p&gt;Ability to thrive in a fast-paced, collaborative engineering environment.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Preferred Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Experience with cloud platforms such as &lt;strong&gt;AWS&lt;/strong&gt;, &lt;strong&gt;Azure&lt;/strong&gt;, &lt;strong&gt;Google Cloud Platform (GCP)&lt;/strong&gt;, or &lt;strong&gt;OpenShift&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;Experience with open-source AI technologies and frameworks.&lt;/p&gt;&lt;p&gt;Active contributions to open-source projects or technology communities.&lt;/p&gt;&lt;p&gt;Industry certifications related to AI, Machine Learning, or Cloud technologies.&lt;/p&gt;&lt;p&gt;Strong coding background with achievements on platforms such as HackerRank, CodeChef, or similar.&lt;/p&gt;&lt;p&gt;Experience building scalable, enterprise-grade AI applications.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Education&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Bachelor's degree (or foreign equivalent) in Computer Science, Engineering, or a related technical field.&lt;/p&gt;&lt;p&gt;Equivalent professional experience will also be considered.&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Work Authorization&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Candidates must be authorized to work for any employer in the United States.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Employer-based visa sponsorship is not available for this position, now or in the future.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Benefits&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We offer a competitive compensation and benefits package, including:&lt;/p&gt;&lt;p&gt;Medical, Dental &amp;amp; Vision Insurance&lt;/p&gt;&lt;p&gt;Life Insurance&lt;/p&gt;&lt;p&gt;Short-Term &amp;amp; Long-Term Disability Coverage&lt;/p&gt;&lt;p&gt;Health &amp;amp; Dependent Care Reimbursement Accounts&lt;/p&gt;&lt;p&gt;Supplemental Insurance (Accident, Critical Illness, Hospital Indemnity, Legal)&lt;/p&gt;&lt;p&gt;401(k) Retirement Plan&lt;/p&gt;&lt;p&gt;Paid Holidays&lt;/p&gt;&lt;p&gt;Generous Paid Time Off (PTO)&lt;/p&gt;&lt;p&gt;Relocation Assistance for eligible candidates&lt;/p&gt;&lt;p&gt;Career development and continuous learning opportunities&lt;/p&gt;&lt;p&gt;&amp;nbsp;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Apply Today!&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;If you're passionate about Artificial Intelligence, Generative AI, and building innovative solutions that make a real impact, we'd love to connect with you.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;📩 Apply today or reach out directly to learn more about this opportunity.&lt;/li&gt;&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
         <is>
           <t xml:space="preserve">
 Locations (Hybrid):
@@ -2155,9 +2036,187 @@
 - 📩 Apply today or reach out directly to learn more about this opportunity.</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Entry level</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '702 Marshall St.', 'addressLocality': 'Redwood City', 'addressRegion': 'California', 'postalCode': '94063', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>https://glider.ai/</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI Skills Validation &amp; Learning | Make Hiring Fair &amp; Opportunity Accessible! </t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Glider AI, a Findem company, helps organizations hire and develop talent with confidence. Our Skills Validation and ID Verification Platform replicates your best recruiter, interviewer, and trainer to identify top talent faster, validate real-world skills, reduce hiring risk, and improve hiring quality through AI-powered assessments, interviews, and learning.</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:04:10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4447986743</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fGHrX5xnz+fuMk0X9aJSOQ==</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ffzy0lJRgiAw/r6tRiN8hA==</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-internal-enablement-productivity-at-air-4447986743?position=3&amp;pageNum=0&amp;refId=Ffzy0lJRgiAw%2Fr6tRiN8hA%3D%3D&amp;trackingId=fGHrX5xnz%2BfuMk0X9aJSOQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Internal Enablement &amp; Productivity</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/air-enterprise-readiness?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFUgvesvqurgw/company-logo_100_100/B4EZ7viW5zHMAI-/0/1782135222131?e=2147483647&amp;v=beta&amp;t=NliZK02iNO4q7OL6nsyEZ8Ir1XvaysuGPR5AIDPYIQg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Company Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Air is the leader in Enterprise Readiness. Our mission is to establish readiness as a real-time condition that is continuously achieved. Today, a dangerous Readiness Gap exists between what the front line needs and what is delivered. Our AI-native platform, Air Enterprise Readiness, aligns development, production, delivery, and sustainment into one coordinated execution system for government agencies and industrial suppliers. By revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands, the front line gets what it needs to succeed.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Job Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We are seeking an experienced AI Engineer to join our AI Enablement team, focused on rapidly increasing internal employee productivity and operational efficiency across the company by scaling robust AI integrations and agentic workflows. This role will be central to designing and deploying agents to handle complex, end-to-end tasks, driving measurable improvements in how our core teams (e.g., Product, Engineering, Operations, and Customer Success) work. This strategic and execution-focused role will lead our internal AI Enablement roadmap, initially focusing deeply on improving core departments (e.g., Sales, Marketing, Product, Engineering, Operations, and Customer Success) through agentic automation.&lt;br&gt;&lt;br&gt;You'll leverage best-in-class AI tools and AI agents (e.g. Gemini and other LLMs) to dramatically increase employee productivity, drive down operational costs, and enable our teams to deliver faster, better outcomes at scale. Your goal is to build our foundation for an AI-enabled future, implementing AI-driven workflows and agents throughout the organization, starting with internal operations and coupling workflows across key functions like GTM.&lt;br&gt;&lt;br&gt;To do this job well, we are looking for someone who can demonstrate project(s) built on LLMs that showcases your skill at reliably automating complex tasks.&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Experience integrating and working with LLMs, with a strong understanding of their capabilities and limitations&lt;/li&gt;&lt;li&gt;Experience integrating and working with agent frameworks (e.g. Claude Agent SDK, Google Anti-Gravity, OpenAI Agent SDK)&lt;/li&gt;&lt;li&gt;Experience building observability, evaluation, and feedback loops for agent behavior (telemetry, prompt evaluation, regression testing, and reliability metrics).&lt;/li&gt;&lt;li&gt;Experience working in highly ambiguous environments, and operate with urgency&lt;/li&gt;&lt;li&gt;Startup experience, particularly in scaling products from zero to one&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Strong Candidates Have&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Deep experience leveraging agents across applications and business workflows to drive meaningful impact&lt;/li&gt;&lt;li&gt;Experience designing and deploying complex agentic systems using LLMs (e.g. deep research)&lt;/li&gt;&lt;li&gt;Hands-on work with multi-agent coordination, routing, and tool orchestration&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;This role is a full-time position located out of our office in Arlington, VA or Pittsburgh, PA. This role may require up to 25% travel.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Scope Of Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Designs and builds multi-agent systems with tool use, memory, routing, and planning to automate internal business processes and enhance employee capabilities.&lt;/li&gt;&lt;li&gt;Develops Agent Skills and tools as modular, composable services that interact with backend systems, models, and data processing to increase internal team velocity.&lt;/li&gt;&lt;li&gt;Contribute to the technical architecture and engineering standards for internal agentic systems, ensuring scalability, reliability, and maintainability across the organization.&lt;/li&gt;&lt;li&gt;Assist with automated evaluation of agents, skills, and prompts across the entire product lifecycle to ensure reliable internal tools.&lt;/li&gt;&lt;li&gt;Partner with internal Product, Engineering, GTM, and Operations teams to identify and implement AI-driven solutions to optimize their workflows and reduce operational costs.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;How We Define Success (Key Metrics)Internal Team Enablement (Operations, Customer Success, Engineering)&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Operational Cost Savings: Reduce operational expenses for targeted teams through workflow automation via AI agents.&lt;/li&gt;&lt;li&gt;Employee Productivity: Achieve measurable increases in internal team capacity and velocity through AI-driven workflows and tools.&lt;/li&gt;&lt;li&gt;Internal Adoption Rate: Achieve a high adoption rate of new AI agents and enablement tools within key departments within the first 90 days.&lt;/li&gt;&lt;li&gt;Accelerated Development: Reduce feature development timelines through AI-assisted coding, documentation, and testing tools.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;U.S. Citizenship is required&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Required Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Bachelor's, Master’s, or Doctorate in Computer Science, Computer Engineering, Data Science, or a related field&lt;/li&gt;&lt;li&gt;Minimum 3 years of experience building and deploying ML or LLM-powered systems in production environments&lt;/li&gt;&lt;li&gt;Practical experience in building, developing, and productionizing machine learning systems&lt;/li&gt;&lt;li&gt;Advanced software skills in Python and other programming languages&lt;/li&gt;&lt;li&gt;Experience with common LLM algorithms and implementations, including coding agents (e.g. Claude Code and GenAI coding best practices).&lt;/li&gt;&lt;li&gt;Hands-on experience with cloud infrastructure (e.g. AWS, GCP)&lt;/li&gt;&lt;li&gt;A strong desire to learn and investigate new technologies&lt;/li&gt;&lt;li&gt;Familiarity with Git source control management&lt;/li&gt;&lt;li&gt;Ability to work collaboratively with little supervision&lt;/li&gt;&lt;li&gt;A burning desire to work in a challenging fast-paced tech environment&lt;/li&gt;&lt;li&gt;A burning desire to work in a challenging fast-paced tech environment&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Desired Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Current possession of a U.S. security clearance, or the ability to obtain one with our sponsorship&lt;/li&gt;&lt;li&gt;Experience in or exposure to the nuances of a startup or other entrepreneurial environment&lt;/li&gt;&lt;li&gt;Experience with modern front-end frameworks (e.g., React, Next.js, or similar) and API-driven UI architectures&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Company Description
+Air is the leader in Enterprise Readiness. Our mission is to establish readiness as a real-time condition that is continuously achieved. Today, a dangerous Readiness Gap exists between what the front line needs and what is delivered. Our AI-native platform, Air Enterprise Readiness, aligns development, production, delivery, and sustainment into one coordinated execution system for government agencies and industrial suppliers. By revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands, the front line gets what it needs to succeed.
+Job Description
+We are seeking an experienced AI Engineer to join our AI Enablement team, focused on rapidly increasing internal employee productivity and operational efficiency across the company by scaling robust AI integrations and agentic workflows. This role will be central to designing and deploying agents to handle complex, end-to-end tasks, driving measurable improvements in how our core teams (e.g., Product, Engineering, Operations, and Customer Success) work. This strategic and execution-focused role will lead our internal AI Enablement roadmap, initially focusing deeply on improving core departments (e.g., Sales, Marketing, Product, Engineering, Operations, and Customer Success) through agentic automation.
+You'll leverage best-in-class AI tools and AI agents (e.g. Gemini and other LLMs) to dramatically increase employee productivity, drive down operational costs, and enable our teams to deliver faster, better outcomes at scale. Your goal is to build our foundation for an AI-enabled future, implementing AI-driven workflows and agents throughout the organization, starting with internal operations and coupling workflows across key functions like GTM.
+To do this job well, we are looking for someone who can demonstrate project(s) built on LLMs that showcases your skill at reliably automating complex tasks.
+- Experience integrating and working with LLMs, with a strong understanding of their capabilities and limitations
+- Experience integrating and working with agent frameworks (e.g. Claude Agent SDK, Google Anti-Gravity, OpenAI Agent SDK)
+- Experience building observability, evaluation, and feedback loops for agent behavior (telemetry, prompt evaluation, regression testing, and reliability metrics).
+- Experience working in highly ambiguous environments, and operate with urgency
+- Startup experience, particularly in scaling products from zero to one
+Strong Candidates Have
+- Deep experience leveraging agents across applications and business workflows to drive meaningful impact
+- Experience designing and deploying complex agentic systems using LLMs (e.g. deep research)
+- Hands-on work with multi-agent coordination, routing, and tool orchestration
+This role is a full-time position located out of our office in Arlington, VA or Pittsburgh, PA. This role may require up to 25% travel.
+Scope Of Responsibilities
+- Designs and builds multi-agent systems with tool use, memory, routing, and planning to automate internal business processes and enhance employee capabilities.
+- Develops Agent Skills and tools as modular, composable services that interact with backend systems, models, and data processing to increase internal team velocity.
+- Contribute to the technical architecture and engineering standards for internal agentic systems, ensuring scalability, reliability, and maintainability across the organization.
+- Assist with automated evaluation of agents, skills, and prompts across the entire product lifecycle to ensure reliable internal tools.
+- Partner with internal Product, Engineering, GTM, and Operations teams to identify and implement AI-driven solutions to optimize their workflows and reduce operational costs.
+How We Define Success (Key Metrics)Internal Team Enablement (Operations, Customer Success, Engineering)
+- Operational Cost Savings: Reduce operational expenses for targeted teams through workflow automation via AI agents.
+- Employee Productivity: Achieve measurable increases in internal team capacity and velocity through AI-driven workflows and tools.
+- Internal Adoption Rate: Achieve a high adoption rate of new AI agents and enablement tools within key departments within the first 90 days.
+- Accelerated Development: Reduce feature development timelines through AI-assisted coding, documentation, and testing tools.
+Qualifications
+- U.S. Citizenship is required
+Required Skills
+- Bachelor's, Master’s, or Doctorate in Computer Science, Computer Engineering, Data Science, or a related field
+- Minimum 3 years of experience building and deploying ML or LLM-powered systems in production environments
+- Practical experience in building, developing, and productionizing machine learning systems
+- Advanced software skills in Python and other programming languages
+- Experience with common LLM algorithms and implementations, including coding agents (e.g. Claude Code and GenAI coding best practices).
+- Hands-on experience with cloud infrastructure (e.g. AWS, GCP)
+- A strong desire to learn and investigate new technologies
+- Familiarity with Git source control management
+- Ability to work collaboratively with little supervision
+- A burning desire to work in a challenging fast-paced tech environment
+- A burning desire to work in a challenging fast-paced tech environment
+Desired Skills
+- Current possession of a U.S. security clearance, or the ability to obtain one with our sponsorship
+- Experience in or exposure to the nuances of a startup or other entrepreneurial environment
+- Experience with modern front-end frameworks (e.g., React, Next.js, or similar) and API-driven UI architectures</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Entry level</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -2181,10 +2240,27 @@
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>https://air.ai/</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Enterprise Readiness</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Air (formerly Govini) created Enterprise Readiness, a new category of AI-native platforms that close the Readiness Gap, a dangerous chasm between what the front line needs and what the national security enterprise delivers. Air Enterprise Readiness platform aligns development, production, delivery, and sustainment into one coordinated execution system, revealing true capacity, exposing real constraints, coordinating resources, and executing at the speed of operational demands. The result: the enterprise has what it needs to succeed.
+Air has offices in Arlington, Virginia and Pittsburgh, Pennsylvania.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>Failed</t>
@@ -2192,7 +2268,1866 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-08-11 03:52:50</t>
+          <t>2026-08-11 05:04:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4452043370</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>92gc6nFg+RtJ3xayvjTVMw==</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-llm-engineer-at-k-k-global-talent-solutions-inc-4452043370?position=7&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=92gc6nFg%2BRtJ3xayvjTVMw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI/LLM Engineer</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>K&amp;K Global Talent Solutions INC.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/knk-gt?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFLa8vszDvSPQ/company-logo_100_100/B4EZU4XGN_HgAQ-/0/1740407334309/knk_gts_logo?e=2147483647&amp;v=beta&amp;t=JrlaqmTUkVWwiSV8VvKHE7Fm0IUbUzpdg57Gyx6jBBM</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>New York, United States</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Job Title: AI/LLM Engineer&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location:&lt;/strong&gt; &lt;strong&gt;New York, NY/Onsite&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Position Type: Full time/Permanent role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Job Description&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Must Have Technical/Functional Skills:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We are looking for a highly skilled AI/LLM Engineer to design and build intelligent agent-based systems that can reason, plan, and act autonomously. The role requires strong Python engineering expertise and hands-on experience with modern agent frameworks, along with a solid understanding of data platforms and scalable architectures.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Key Responsibilities&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Agent &amp;amp; AI System Development&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;· Design and build agent-based systems using frameworks such as LangChain, LangGraph, or similar&lt;/p&gt;&lt;p&gt;· Develop intelligent components capable of reasoning, planning, and executing tasks autonomously&lt;/p&gt;&lt;p&gt;· Implement advanced cognitive patterns such as ReAct (Reasoning + Acting)&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;LLM Capabilities &amp;amp; Enhancements&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;· Develop and integrate memory, tool usage, and context management capabilities (MCP)&lt;/p&gt;&lt;p&gt;· Build systems that leverage tool calling, chaining, and orchestration of LLM workflows&lt;/p&gt;&lt;p&gt;· Collaborate with prompt engineers to enhance model responses and performance&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Engineering &amp;amp; Development &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;· Write high-quality, scalable code using Python (including async programming)&lt;/p&gt;&lt;p&gt;· Build and maintain APIs and microservices for AI/agent-based applications&lt;/p&gt;&lt;p&gt;· Ensure systems are efficient, reliable, and production-ready&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Guardrails &amp;amp; Responsible AI &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;· Design and implement guardrails and safety mechanisms for LLM-driven systems&lt;/p&gt;&lt;p&gt;· Ensure robust handling of edge cases, failure scenarios, and unintended outputs&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Data &amp;amp; Platform Integration &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;· Work with modern data platforms such as:&lt;/p&gt;&lt;p&gt;o Snowflake&lt;/p&gt;&lt;p&gt;o Databricks&lt;/p&gt;&lt;p&gt;o Lakehouse architectures&lt;/p&gt;&lt;p&gt;· Integrate AI solutions with enterprise data pipelines and systems&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Job Title: AI/LLM Engineer
+Location: New York, NY/Onsite
+Position Type: Full time/Permanent role
+Job Description
+Must Have Technical/Functional Skills:
+We are looking for a highly skilled AI/LLM Engineer to design and build intelligent agent-based systems that can reason, plan, and act autonomously. The role requires strong Python engineering expertise and hands-on experience with modern agent frameworks, along with a solid understanding of data platforms and scalable architectures.
+Key Responsibilities
+Agent &amp;amp; AI System Development
+· Design and build agent-based systems using frameworks such as LangChain, LangGraph, or similar
+· Develop intelligent components capable of reasoning, planning, and executing tasks autonomously
+· Implement advanced cognitive patterns such as ReAct (Reasoning + Acting)
+LLM Capabilities &amp;amp; Enhancements
+· Develop and integrate memory, tool usage, and context management capabilities (MCP)
+· Build systems that leverage tool calling, chaining, and orchestration of LLM workflows
+· Collaborate with prompt engineers to enhance model responses and performance
+Engineering &amp;amp; Development 
+· Write high-quality, scalable code using Python (including async programming)
+· Build and maintain APIs and microservices for AI/agent-based applications
+· Ensure systems are efficient, reliable, and production-ready
+Guardrails &amp;amp; Responsible AI 
+· Design and implement guardrails and safety mechanisms for LLM-driven systems
+· Ensure robust handling of edge cases, failure scenarios, and unintended outputs
+Data &amp;amp; Platform Integration 
+· Work with modern data platforms such as:
+o Snowflake
+o Databricks
+o Lakehouse architectures
+· Integrate AI solutions with enterprise data pipelines and systems
+</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Information Services</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '7901 4th St N', 'addressLocality': 'St Petersburg', 'addressRegion': 'Florida', 'postalCode': '33702', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>https://www.knkglobaltalents.com/</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Your strategic partner for IT Talents, AI Projects, IT Consulting &amp; 
+System Integration across US, CA, EU, UK &amp; IND.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>With more than 33+ years of experience, we enable organizations to build, scale, and optimize their digital capabilities across the United States, Europe, Canada, United Kingdom and India.
+We deliver high-impact solutions across IT talent, AI-driven transformation, consulting, and system integration.
+Our Core Services
+• IT Talent Solutions — Contract, Contract-to-Hire &amp; Full-Time hiring across Software, Cloud, Data, ERP &amp; Cybersecurity (30-day SLA)
+• IT Consulting &amp; Advisory — IT roadmaps, technology assessments &amp; programme governance
+• AI &amp; Machine Learning — End-to-end AI/ML execution from strategy to deployment
+• System Integration — Connecting enterprise, cloud &amp; legacy systems
+• Cloud Services &amp; Migration — AWS, Azure &amp; Google Cloud solutions
+• Digital Transformation — Modernizing systems &amp; automating workflows
+• Cybersecurity — Talent &amp; advisory for security, compliance &amp; threat management
+• Offshore &amp; GCC Services — Building scalable offshore teams in India
+• ERP Staffing — SAP, Oracle, Microsoft Dynamics &amp; enterprise platforms
+• Local Compliance — Managing regulatory, legal, and workforce compliance requirements
+Industries We Serve
+Banking &amp; Financial Services | Technology &amp; SaaS | Healthcare &amp; Life Sciences (supporting) | Manufacturing | Logistics &amp; Supply Chain
+Why K&amp;K
+- Strong Global Talent Network
+- Expertise Across Modern Tech Stacks
+- End-to-End Technology &amp; Talent Solutions
+- Trusted by Growing &amp; Enterprise Businesses
+Partner with K&amp;K to build scalable, future-ready technology ecosystems that drive long-term growth.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Sanjay Kumar Yadav</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Account Manager</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D03AQHr8JluLEglZw/profile-displayphoto-shrink_400_400/profile-displayphoto-shrink_400_400/0/1701793494526?e=2147483647&amp;v=beta&amp;t=tr48PvRZBEzMslnCNUOjVyx8jKoY-Sh1PQRXAn3d1Nw</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanjay-kumar-yadav-2b6008113</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>4452075106</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pj+VnWnJhoS9veHTabToSg==</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-at-tata-consultancy-services-4452075106?position=9&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=pj%2BVnWnJhoS9veHTabToSg%3D%3D</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/tata-consultancy-services?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D0BAQGsGR9p4ikS5w/company-logo_100_100/company-logo_100_100/0/1708946550425/tata_consultancy_services_logo?e=2147483647&amp;v=beta&amp;t=P-PkUMh7Ks1GQY0_l7GhzQiwfyLfQpvKWwX8Tq18Yc4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Job Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;AI Engineer (Backend TypeScript or Python… the team is leaning to Typescript)&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Strong backend engineering in TypeScript/Node.js (preferred) or Python, with production API design experience&lt;/li&gt;&lt;li&gt; Has built LLM harnesses/scaffolds with agentic loops, RAG pipelines, and tool-calling architectures&lt;/li&gt;&lt;li&gt; Experience designing multi-agent systems and integrating LLMs with internal/external APIs&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Added Advantage: AI platform/developer tooling, evaluation &amp;amp; observability frameworks, AI security &amp;amp; guardrails&lt;br&gt;&lt;br&gt;Salary Range: $100,000-$130,000 a year&lt;br&gt;&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description
+AI Engineer (Backend TypeScript or Python… the team is leaning to Typescript)
+-  Strong backend engineering in TypeScript/Node.js (preferred) or Python, with production API design experience
+-  Has built LLM harnesses/scaffolds with agentic loops, RAG pipelines, and tool-calling architectures
+-  Experience designing multi-agent systems and integrating LLMs with internal/external APIs
+Added Advantage: AI platform/developer tooling, evaluation &amp;amp; observability frameworks, AI security &amp;amp; guardrails
+Salary Range: $100,000-$130,000 a year
+</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>IT Services and IT Consulting</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': 'Tata Consultancy Services', 'addressLocality': 'Mumbai', 'addressRegion': 'Maharashtra', 'postalCode': '400001', 'addressCountry': 'IN'}</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>https://www.tcs.com/</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS) is the technology partner of choice for industry leading organizations worldwide. Since its inception in 1968, TCS has upheld the highest standards of innovation, engineering excellence, and customer service. 
+It has set an aspiration to become the world's largest AI-led technology services company and is enabling its clients to transform themselves across the full AI stack, from infrastructure to intelligence. 
+Rooted in the heritage of the Tata Group, TCS is focused on creating long term value for its clients, its investors, its employees, and the community at large. With a highly skilled workforce spread across 55 countries and 202 service delivery centers across the world, the company has been recognized as a top employer in six continents. With the ability to rapidly apply and scale new technologies, the company has built long term partnerships with its clients – helping them emerge as perpetually adaptive enterprises. Many of these relationships have endured into decades and navigated every technology cycle, from mainframes in the 1970s to artificial intelligence today. 
+TCS sponsors 14 of the world’s most prestigious marathons and endurance events, including the TCS New York City Marathon, TCS London Marathon and TCS Sydney Marathon with a focus on promoting health, sustainability, and community empowerment. 
+Caution against fraudulent job offers: TCS doesn’t charge any fee throughout the recruitment process. Refer here: https://www.tcs.com/careers/india/recruitment-fraud-alert</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>724421</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4451560525</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sGT+Oe9L+Okjqh/1/a3+iQ==</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-bain-company-4451560525?position=10&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=sGT%2BOe9L%2BOkjqh%2F1%2Fa3%2BiQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bain-and-company?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQHJWWQNCmnqKg/company-logo_100_100/company-logo_100_100/0/1719929153718/bain_and_company_logo?e=2147483647&amp;v=beta&amp;t=hOsU1bVj9dJZI9c0TujGpXV69c1dwdAsI9khve8rwOk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;WHAT MAKES US A GREAT PLACE TO WORK&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.&lt;/span&gt;&lt;span&gt;&lt;br&gt;&lt;/span&gt;&lt;span&gt;&lt;strong&gt;WHO YOU’LL WORK WITH&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making. &amp;nbsp;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;WHERE YOU’LL FIT WITHIN THE TEAM&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;WHAT YOU'LL DO&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Core ML and Data Pipeline Engineering (65%)&amp;nbsp;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Collaboration and Support (25%)&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Other (10%):&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Take on interviewing and hiring-loop participation as your experience grows.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;ABOUT YOU&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to model deployment, serving, or monitoring is a plus.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Experience working with structured feedback and code review, and a track record of improving code quality over time.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.&lt;br&gt;&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;ML engineering / LLMOps&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Docker: comfortable containerising pipeline or serving code and running it locally for testing.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Git: confident with PR-based workflows.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Generative AI and agentic systems&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Contributes to inference and retrieval services that feed agent workflows as structured tool responses.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;General&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;This role follows a hybrid model, requiring in-office presence at least 1 day per week&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;U.S. COMPENSATION INFORMATION&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Placement within these ranges will vary based on factors such as experience, education, training, and skill level.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Annual discretionary performance bonus&amp;nbsp;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;This role may also be eligible for other elements of discretionary compensation&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Generous paid time off, including parental leave, sick leave and paid holidays&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Fully vested 401(k) company contribution&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Paid Life and Long-Term Disability insurance&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Annual fitness reimbursements&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+WHAT MAKES US A GREAT PLACE TO WORK
+We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.
+Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.
+WHO YOU’LL WORK WITH
+As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.
+Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making. &amp;nbsp;
+The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.
+WHERE YOU’LL FIT WITHIN THE TEAM
+AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.
+WHAT YOU'LL DO
+Core ML and Data Pipeline Engineering (65%)&amp;nbsp;
+- Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.
+- Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.
+- Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.
+- Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.
+- Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.
+Collaboration and Support (25%)
+- Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.
+- Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.
+- Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.
+- Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.
+Other (10%):
+- Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.
+- Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.
+- Take on interviewing and hiring-loop participation as your experience grows.
+ABOUT YOU
+- Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).
+- 2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.
+- Exposure to model deployment, serving, or monitoring is a plus.
+- Experience working with structured feedback and code review, and a track record of improving code quality over time.
+- Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.
+- Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.
+- Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.
+ML engineering / LLMOps
+- Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.
+- Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.
+- Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).
+- Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.
+- RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.
+- Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.
+- Docker: comfortable containerising pipeline or serving code and running it locally for testing.
+- Git: confident with PR-based workflows.
+Generative AI and agentic systems
+- Contributes to inference and retrieval services that feed agent workflows as structured tool responses.
+- Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.
+- Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.
+General
+- Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.
+- Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.
+- Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.
+- Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.
+- This role follows a hybrid model, requiring in-office presence at least 1 day per week
+U.S. COMPENSATION INFORMATION
+Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).
+Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:
+In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500
+In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750
+In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250
+Placement within these ranges will vary based on factors such as experience, education, training, and skill level.
+Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.
+Annual discretionary performance bonus&amp;nbsp;
+This role may also be eligible for other elements of discretionary compensation
+4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date
+Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.
+Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck
+Generous paid time off, including parental leave, sick leave and paid holidays
+Fully vested 401(k) company contribution
+Paid Life and Long-Term Disability insurance
+Annual fitness reimbursements</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Business Consulting and Services</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '350 Boylston St', 'addressLocality': 'Boston', 'addressRegion': 'Massachusetts', 'postalCode': '02116', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>http://www.bain.com</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company is a global consultancy that helps the world’s most ambitious change makers define the future. 
+Across 65 cities in 40 countries, we work alongside our clients as one team with a shared ambition to achieve extraordinary results, outperform the competition, and redefine industries. We complement our tailored, integrated expertise with a vibrant ecosystem of digital innovators to deliver better, faster, and more enduring outcomes. Our 10-year commitment to invest more than $1 billion in pro bono services brings our talent, expertise, and insight to organizations tackling today’s urgent challenges in education, racial equity, social justice, economic development, and the environment. We earned a platinum rating from EcoVadis, the leading platform for environmental, social, and ethical performance ratings for global supply chains, putting us in the top 1% of all companies. Since our founding in 1973, we have measured our success by the success of our clients.</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>26107</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4451196390</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NGSQpRez5D9DWBRGujZYew==</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-python-machine-learning-generative-ai-at-atc-4451196390?position=5&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=NGSQpRez5D9DWBRGujZYew%3D%3D</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AI Engineer (Python, Machine Learning &amp; Generative AI)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/american-technology-consulting?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C4E0BAQHR71hWsUHv0g/company-logo_100_100/company-logo_100_100/0/1630586230009/american_technology_consulting_logo?e=2147483647&amp;v=beta&amp;t=5jQ1atzm92pOlcmnVypSolo7YAtJLJrCQBcBVzy8_4I</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Texas, United States</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Job Title: AI Engineer (Python, Machine Learning &amp;amp; Generative AI)&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Experience developing REST APIs using FastAPI or Flask.&lt;/p&gt;&lt;p&gt;We are looking for an AI Engineer with 3+ years of experience in Artificial Intelligence, Machine Learning, and Generative AI. The ideal candidate will have hands-on experience developing AI-powered applications using Python, Large Language Models (LLMs), LangChain, LangGraph, and Retrieval-Augmented Generation (RAG). You will work on designing, building, and deploying scalable AI solutions for enterprise applications.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Key Responsibilities&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;● Develop and deploy AI and Machine Learning solutions using Python.&lt;/p&gt;&lt;p&gt;● Build LLM-powered applications using LangChain and LangGraph.&lt;/p&gt;&lt;p&gt;● Design and implement Retrieval-Augmented Generation (RAG) pipelines with vector databases.&lt;/p&gt;&lt;p&gt;● Develop AI agents and conversational AI applications.&lt;/p&gt;&lt;p&gt;● Train, evaluate, and optimize machine learning and deep learning models.&lt;/p&gt;&lt;p&gt;● Build REST APIs using FastAPI or Flask to integrate AI services.&lt;/p&gt;&lt;p&gt;● Integrate AI applications with enterprise systems, databases, and third-party APIs.&lt;/p&gt;&lt;p&gt;● Work with structured and unstructured data for model training and inference.&lt;/p&gt;&lt;p&gt;● Deploy AI applications using Docker and cloud platforms such as AWS, Azure, or GCP.&lt;/p&gt;&lt;p&gt;● Collaborate with cross-functional teams to deliver AI-driven business solutions.&lt;/p&gt;&lt;p&gt;● Troubleshoot, optimize, and maintain AI applications in production.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Required Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;● Master’s degree in Computer Science, Artificial Intelligence, Data Science, or a related field.&lt;/p&gt;&lt;p&gt;● 3+ years of experience in AI, Machine Learning, or Software Development.&lt;/p&gt;&lt;p&gt;● Strong programming skills in Python.&lt;/p&gt;&lt;p&gt;● Hands-on experience with TensorFlow, PyTorch, or Scikit-learn.&lt;/p&gt;&lt;p&gt;● Experience building applications with Large Language Models (LLMs).&lt;/p&gt;&lt;p&gt;● Experience with LangChain and LangGraph.&lt;/p&gt;&lt;p&gt;● Hands-on experience implementing Retrieval-Augmented Generation (RAG).&lt;/p&gt;&lt;p&gt;● Experience with vector databases such as Pinecone, ChromaDB, FAISS, or Milvus.&lt;/p&gt;&lt;p&gt;● Knowledge of SQL and NoSQL databases.&lt;/p&gt;&lt;p&gt;● Experience with Git, Docker, and CI/CD pipelines.&lt;/p&gt;&lt;p&gt;● Familiarity with cloud platforms (AWS, Azure, or Google Cloud Platform).&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Preferred Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;● Experience with OpenAI, Anthropic, or open-source LLMs.&lt;/p&gt;&lt;p&gt;● Knowledge of prompt engineering, function calling, and AI agent frameworks.&lt;/p&gt;&lt;p&gt;● Familiarity with Hugging Face Transformers and LlamaIndex.&lt;/p&gt;&lt;p&gt;● Experience with Kubernetes and MLOps tools such as MLflow or Kubeflow.&lt;/p&gt;&lt;p&gt;● Exposure to NLP, deep learning, or computer vision.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Job Title: AI Engineer (Python, Machine Learning &amp;amp; Generative AI)
+Experience developing REST APIs using FastAPI or Flask.
+We are looking for an AI Engineer with 3+ years of experience in Artificial Intelligence, Machine Learning, and Generative AI. The ideal candidate will have hands-on experience developing AI-powered applications using Python, Large Language Models (LLMs), LangChain, LangGraph, and Retrieval-Augmented Generation (RAG). You will work on designing, building, and deploying scalable AI solutions for enterprise applications.
+Key Responsibilities
+● Develop and deploy AI and Machine Learning solutions using Python.
+● Build LLM-powered applications using LangChain and LangGraph.
+● Design and implement Retrieval-Augmented Generation (RAG) pipelines with vector databases.
+● Develop AI agents and conversational AI applications.
+● Train, evaluate, and optimize machine learning and deep learning models.
+● Build REST APIs using FastAPI or Flask to integrate AI services.
+● Integrate AI applications with enterprise systems, databases, and third-party APIs.
+● Work with structured and unstructured data for model training and inference.
+● Deploy AI applications using Docker and cloud platforms such as AWS, Azure, or GCP.
+● Collaborate with cross-functional teams to deliver AI-driven business solutions.
+● Troubleshoot, optimize, and maintain AI applications in production.
+Required Qualifications
+● Master’s degree in Computer Science, Artificial Intelligence, Data Science, or a related field.
+● 3+ years of experience in AI, Machine Learning, or Software Development.
+● Strong programming skills in Python.
+● Hands-on experience with TensorFlow, PyTorch, or Scikit-learn.
+● Experience building applications with Large Language Models (LLMs).
+● Experience with LangChain and LangGraph.
+● Hands-on experience implementing Retrieval-Augmented Generation (RAG).
+● Experience with vector databases such as Pinecone, ChromaDB, FAISS, or Milvus.
+● Knowledge of SQL and NoSQL databases.
+● Experience with Git, Docker, and CI/CD pipelines.
+● Familiarity with cloud platforms (AWS, Azure, or Google Cloud Platform).
+Preferred Qualifications
+● Experience with OpenAI, Anthropic, or open-source LLMs.
+● Knowledge of prompt engineering, function calling, and AI agent frameworks.
+● Familiarity with Hugging Face Transformers and LlamaIndex.
+● Experience with Kubernetes and MLOps tools such as MLflow or Kubeflow.
+● Exposure to NLP, deep learning, or computer vision.
+</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Information Technology &amp; Services</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '12951 University Ave', 'addressLocality': 'Clive', 'addressRegion': 'Iowa', 'postalCode': '50325', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>http://www.atc.xyz</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enterprise AI | SaaS product Development
+ </t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Founded in the wake of the 2008 Great Recession, ATC has evolved into a dynamic tech company, known for its ability to adapt quickly to the ever-changing business landscape. For over a decade, we’ve been at the forefront of technological innovation, helping companies transform challenges into opportunities.
+In a world where innovation is essential, ATC empowers businesses to stay ahead by creating cutting-edge software solutions that drive productivity and outperform the competition. We go beyond conventional software development to solve complex business problems with creativity and a passion for technology that enriches lives.
+Our comprehensive offerings span strategy, design, automation, custom software development, managed services, and advanced IT solutions, including chatbots and cloud transformations. Through ATC Ventures, we support visionary entrepreneurs, helping them build groundbreaking SaaS startups from the ground up.
+Our commitment to technology extends to our Training Division, which has trained over 10,000 professionals across various IT disciplines. As a proud Scaled Agile Gold Transformation Partner, we provide expert training, coaching, and consulting services.
+With headquarters in Iowa and delivery centers across the U.S. and India, our talented, dedicated team is driven to bring bold ideas to life. ATC specializes in a wide range of services, including:
+Enterprise AI
+Cybersecurity
+DevSecOps
+Staffing
+Software Testing &amp; Automation
+SaaS Product Development
+Product Design (UX/UI)
+Custom AI Models
+Public Sector Services (State and Federal)
+At ATC, we don’t just build software – we create solutions that shape the future.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1756</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Yaser Sayed</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Operations Intelligence and Business Process Manager</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5603AQENacPJkalSNw/profile-displayphoto-scale_400_400/B56Z1t_pD_IcAg-/0/1775666899478?e=2147483647&amp;v=beta&amp;t=MDQA-6iGFCjHqGZmY-NnrNR-HdRKG4T4HRB-mG3-aAk</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yaser-sayed-11830070</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4452103275</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>K1D36ZUhCFf+PXVLLGtZ1A==</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/agentic-ai-engineer-intelligence-engineering-san-francisco-at-slalom-4452103275?position=8&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=K1D36ZUhCFf%2BPXVLLGtZ1A%3D%3D</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer - Intelligence Engineering (San Francisco)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Slalom</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/slalom-consulting?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQG5l3nKnBCEWA/company-logo_100_100/company-logo_100_100/0/1719861816497/slalom_consulting_logo?e=2147483647&amp;v=beta&amp;t=RMKFTGulqo2H4IUgFNTlPiYXXVPaHpsYx0MSR67KaB0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;&lt;span&gt;Who You’ll Work With&lt;/span&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;At Slalom, we co-create modern technology and software products with clients who are ready to accelerate their digital product development. We imagine how things can be made better, then set out to realize what’s possible — driving innovation with quality, resilience, and purpose. By blending design, product engineering, analytics, and automation, we build the custom-built software and data products of tomorrow. As a member of Intelligence Engineering, you’ll design and deliver innovative AI/ML and agentic AI solutions as part of intelligent products and automating / re-envisioning human workflows on Amazon Web Services, Azure, and Google Cloud. This includes architecting multi-agent systems, LLM-powered autonomous workflows, retrieval-augmented generation (RAG) pipelines, and enterprise-grade AI governance frameworks using cutting-edge orchestration frameworks, tool-use protocols, and cloud-native AI services. You’ll help clients move from isolated proofs of concept to secure, scalable, observable systems that create real business value, while helping craft projects in their initial phases and delivering them with a team. We are open to hiring Engineer level across the San Franciso area.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;em&gt;&lt;span&gt;We offer a flexible working environment to balance the need to work independently, with some days that may require in-person collaboration at our office.&amp;nbsp;&lt;/span&gt;&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;What You’ll Do&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Provide thought leadership on AI/ML, Generative AI, and Agentic AI internally and with clients, while contributing to a culture of collaboration, learning, and curiosity&lt;/li&gt;&lt;li&gt;Design end-to-end agentic AI architectures including planning loops, memory management, tool integration, and agent coordination patterns&lt;/li&gt;&lt;li&gt;Architect multi-agent orchestration systems using frameworks such asStrands Agents SDK,OpenAI Agents SDK, Google ADK, Lang Graph or similar for autonomous reasoning, decision-making, and task execution&lt;/li&gt;&lt;li&gt;Design and implement Model Context Protocol (MCP) server integrations for tool use, data access, and cross-system interoperability with enterprise systems&lt;/li&gt;&lt;li&gt;Build advanced retrieval-augmented generation (RAG) systems including vector databases, embedding strategies, chunking optimization, hybrid search, re-ranking, and multi-source data synthesis&lt;/li&gt;&lt;li&gt;Design and deliver AI and ML solutions across AWS, Azure, and GCP, using the right mix combination of cloud-native data services, ML tooling, LLM platforms, and software engineering practices&lt;/li&gt;&lt;li&gt;Build in Python and, where useful, other languages to deliver machine learning systems, APIs, evaluation harnesses, retrieval pipelines, agent workflows, and production services&lt;/li&gt;&lt;li&gt;Recommend and implement architecture for model and agent pipelines, CI/CD, testing, deployment, observability, andMLOps/LLMOps at scale&lt;/li&gt;&lt;li&gt;Implement evaluation frameworks (e.g., RAGAS, DeepEval, LangSmith) to measure task success rates, tool-call accuracy, and reasoning integrity for GenAI systems&lt;/li&gt;&lt;li&gt;Build guardrails for safety, compliance, and performance monitoring including human-in-the-loop (HITL) approval workflows, escalation policies, and sandbox isolation&lt;/li&gt;&lt;li&gt;Define AI governance frameworks including model risk management, responsible AI practices, regulatory compliance, and authorization boundaries for autonomous decision-making&lt;/li&gt;&lt;li&gt;Explain model and system behavior to both technical and non-technical audiences, including leading deep technical presentations, workshops, and architecture conversations&lt;/li&gt;&lt;li&gt;Collaborate with Product Owners to apply Slalom’s agile process and lead the initiation, delivery, and transition of projects in a client-facing role&lt;/li&gt;&lt;li&gt;Lead and mentor engineers and machine learning practitioners. Lead smaller projects (3 to 5 people) as the technical lead from project initiation to delivery&lt;/li&gt;&lt;li&gt;Build trusted relationships with customers and collaborate across Slalom teams to share learnings and strengthen the broader Intelligence Engineering practice&lt;/li&gt;&lt;li&gt;Will be delivery-focused approximately 85–95% of the time&lt;/li&gt;&lt;li&gt;Willingness to travel up to 50%, at peak times&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;em&gt;&lt;span&gt;Travel may be required on a limited basis dependent on your client engagement or internal meetings/events.&lt;/span&gt;&lt;/em&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;What You’ll Bring&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;3+ years of software engineering experience building and deploying production systems; experience with machine learning, applied AI, or intelligent software systems is a plus, with 1+ years focused on generative AI, LLMs, or agentic AI systems&lt;/li&gt;&lt;li&gt;Hands-on experience designing or building multi-agent systems including agent orchestration, tool integration, and autonomous decision-making workflows&lt;/li&gt;&lt;li&gt;Proficiency with at least one agentic AI or workflow framework such as Lang Graph, Strands, AutoGen, CrewAI, Semantic Kernel, OpenAI Agents SDK, Google ADK, or similar&lt;/li&gt;&lt;li&gt;Experience with RAG architectures including vector databases, embeddings, and retrieval optimization, and context management techniques such as chunking, summarization, and memory handling&lt;/li&gt;&lt;li&gt;Experience developing production-ready solutions on at least one major cloud AI platform, such as AWS Bedrock, Azure AI Foundry/OpenAI Service, GCP Vertex AI/Gemini, or Databricks; experience operating and maintaining production environments is a plus&lt;/li&gt;&lt;li&gt;Experience with AI-assisted development tools such as Claude Code, Cursor, Kiro, or similar IDE-based coding agents, including effective use for code generation, refactoring, debugging, and developer workflow acceleration&lt;/li&gt;&lt;li&gt;Strong Python development skills; experience withFastAPI, Flask, or equivalent API frameworks&lt;/li&gt;&lt;li&gt;Experience building ML or AI systems end to end, including data access, feature or retrieval flows, APIs, testing, deployment, and production support&lt;/li&gt;&lt;li&gt;Familiarity with evaluation frameworks, tracing, observability, model behavior analysis, and regression testing for GenAI systems&lt;/li&gt;&lt;li&gt;Understanding of prompt engineering, LLM fine-tuning, chain-of-thought reasoning, and structured output techniques&lt;/li&gt;&lt;li&gt;Recognized as an authority on at least one technical domain (e.g., Agentic Systems, RAG, Multi-Agent Orchestration) with generalist familiarity across AI/ML techniques&lt;/li&gt;&lt;li&gt;Ability to work across new domains and unfamiliar data structures and lead exploratory analysis when requirements are not fully defined&lt;/li&gt;&lt;li&gt;Excellent verbal and written communication skills; ability to lead highly technical presentations&lt;/li&gt;&lt;li&gt;Familiarity with Agile project delivery&lt;/li&gt;&lt;li&gt;(Preferred) Experience with Model Context Protocol (MCP) server development and integration&lt;/li&gt;&lt;li&gt;(Preferred) Experience with MLOps/LLMOps pipelines, CI/CD for ML, and model monitoring/observability&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;About Us&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Slalom is a fiercely human business and technology consulting company that leads with outcomes to bring more value, in all ways, always. From strategy through delivery, our agile teams across 52 offices in 12 countries partner with clients to co-create powerful customer experiences, modern ways of working, and meaningful impact. What sets us apart? We believe work should be challenging and fulfilling, not perfect, but possible. That’s why we prioritize purpose, flexibility, connection, and recognition, so our people can thrive and love what they do, most days.&lt;/span&gt;&lt;span&gt;&amp;nbsp;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Compensation and Benefits&amp;nbsp;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Slalom prides itself on helping team members thrive in their work and life. As a result, Slalom is proud to invest in benefits that include meaningful time off and paid holidays, parental leave, 401(k) with a match, a range of choices for highly subsidized health, dental, &amp;amp; vision coverage, adoption and fertility assistance, and short/long-term disability. We also offer yearly $350 reimbursement account for any well-being-related expenses, as well as discounted home, auto, and pet insurance.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Slalom is committed to fair and equitable compensation practices. For this role, we are hiring at the following levels and salary ranges:&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;East Bay, San Francisco, Silicon Valley:&lt;ul&gt;&lt;li&gt;Engineer: $102,000-$125,000&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In addition, individuals may be eligible for an annual discretionary bonus. Actual compensation will depend upon an individual’s skills, experience, qualifications, location, and other relevant factors. The pay range is subject to change and may be modified at any time.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;We will accept applicants until the position is filled.&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;EEO and Accommodations&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;em&gt;&lt;span&gt;Slalom is an equal opportunity employer and is committed to attracting, developing and retaining highly qualified talent who empower our innovative teams through unique perspectives and experiences. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, national origin, disability status, protected veterans’ status, or any other characteristic protected by federal, state, or local laws. Slalom will also consider qualified applications with criminal histories, consistent with legal requirements. Slalom welcomes and encourages applications from individuals with disabilities. Reasonable accommodations are available for candidates during all aspects of the selection process. Please advise the talent acquisition team if you require accommodations during the interview process.&lt;/span&gt;&lt;/em&gt;&lt;/span&gt;&lt;em&gt;&lt;span&gt; &lt;/span&gt;&lt;/em&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Who You’ll Work With
+At Slalom, we co-create modern technology and software products with clients who are ready to accelerate their digital product development. We imagine how things can be made better, then set out to realize what’s possible — driving innovation with quality, resilience, and purpose. By blending design, product engineering, analytics, and automation, we build the custom-built software and data products of tomorrow. As a member of Intelligence Engineering, you’ll design and deliver innovative AI/ML and agentic AI solutions as part of intelligent products and automating / re-envisioning human workflows on Amazon Web Services, Azure, and Google Cloud. This includes architecting multi-agent systems, LLM-powered autonomous workflows, retrieval-augmented generation (RAG) pipelines, and enterprise-grade AI governance frameworks using cutting-edge orchestration frameworks, tool-use protocols, and cloud-native AI services. You’ll help clients move from isolated proofs of concept to secure, scalable, observable systems that create real business value, while helping craft projects in their initial phases and delivering them with a team. We are open to hiring Engineer level across the San Franciso area.
+We offer a flexible working environment to balance the need to work independently, with some days that may require in-person collaboration at our office.&amp;nbsp;
+What You’ll Do
+- Provide thought leadership on AI/ML, Generative AI, and Agentic AI internally and with clients, while contributing to a culture of collaboration, learning, and curiosity
+- Design end-to-end agentic AI architectures including planning loops, memory management, tool integration, and agent coordination patterns
+- Architect multi-agent orchestration systems using frameworks such asStrands Agents SDK,OpenAI Agents SDK, Google ADK, Lang Graph or similar for autonomous reasoning, decision-making, and task execution
+- Design and implement Model Context Protocol (MCP) server integrations for tool use, data access, and cross-system interoperability with enterprise systems
+- Build advanced retrieval-augmented generation (RAG) systems including vector databases, embedding strategies, chunking optimization, hybrid search, re-ranking, and multi-source data synthesis
+- Design and deliver AI and ML solutions across AWS, Azure, and GCP, using the right mix combination of cloud-native data services, ML tooling, LLM platforms, and software engineering practices
+- Build in Python and, where useful, other languages to deliver machine learning systems, APIs, evaluation harnesses, retrieval pipelines, agent workflows, and production services
+- Recommend and implement architecture for model and agent pipelines, CI/CD, testing, deployment, observability, andMLOps/LLMOps at scale
+- Implement evaluation frameworks (e.g., RAGAS, DeepEval, LangSmith) to measure task success rates, tool-call accuracy, and reasoning integrity for GenAI systems
+- Build guardrails for safety, compliance, and performance monitoring including human-in-the-loop (HITL) approval workflows, escalation policies, and sandbox isolation
+- Define AI governance frameworks including model risk management, responsible AI practices, regulatory compliance, and authorization boundaries for autonomous decision-making
+- Explain model and system behavior to both technical and non-technical audiences, including leading deep technical presentations, workshops, and architecture conversations
+- Collaborate with Product Owners to apply Slalom’s agile process and lead the initiation, delivery, and transition of projects in a client-facing role
+- Lead and mentor engineers and machine learning practitioners. Lead smaller projects (3 to 5 people) as the technical lead from project initiation to delivery
+- Build trusted relationships with customers and collaborate across Slalom teams to share learnings and strengthen the broader Intelligence Engineering practice
+- Will be delivery-focused approximately 85–95% of the time
+- Willingness to travel up to 50%, at peak times
+Travel may be required on a limited basis dependent on your client engagement or internal meetings/events.
+What You’ll Bring
+- 3+ years of software engineering experience building and deploying production systems; experience with machine learning, applied AI, or intelligent software systems is a plus, with 1+ years focused on generative AI, LLMs, or agentic AI systems
+- Hands-on experience designing or building multi-agent systems including agent orchestration, tool integration, and autonomous decision-making workflows
+- Proficiency with at least one agentic AI or workflow framework such as Lang Graph, Strands, AutoGen, CrewAI, Semantic Kernel, OpenAI Agents SDK, Google ADK, or similar
+- Experience with RAG architectures including vector databases, embeddings, and retrieval optimization, and context management techniques such as chunking, summarization, and memory handling
+- Experience developing production-ready solutions on at least one major cloud AI platform, such as AWS Bedrock, Azure AI Foundry/OpenAI Service, GCP Vertex AI/Gemini, or Databricks; experience operating and maintaining production environments is a plus
+- Experience with AI-assisted development tools such as Claude Code, Cursor, Kiro, or similar IDE-based coding agents, including effective use for code generation, refactoring, debugging, and developer workflow acceleration
+- Strong Python development skills; experience withFastAPI, Flask, or equivalent API frameworks
+- Experience building ML or AI systems end to end, including data access, feature or retrieval flows, APIs, testing, deployment, and production support
+- Familiarity with evaluation frameworks, tracing, observability, model behavior analysis, and regression testing for GenAI systems
+- Understanding of prompt engineering, LLM fine-tuning, chain-of-thought reasoning, and structured output techniques
+- Recognized as an authority on at least one technical domain (e.g., Agentic Systems, RAG, Multi-Agent Orchestration) with generalist familiarity across AI/ML techniques
+- Ability to work across new domains and unfamiliar data structures and lead exploratory analysis when requirements are not fully defined
+- Excellent verbal and written communication skills; ability to lead highly technical presentations
+- Familiarity with Agile project delivery
+- (Preferred) Experience with Model Context Protocol (MCP) server development and integration
+- (Preferred) Experience with MLOps/LLMOps pipelines, CI/CD for ML, and model monitoring/observability
+About Us
+Slalom is a fiercely human business and technology consulting company that leads with outcomes to bring more value, in all ways, always. From strategy through delivery, our agile teams across 52 offices in 12 countries partner with clients to co-create powerful customer experiences, modern ways of working, and meaningful impact. What sets us apart? We believe work should be challenging and fulfilling, not perfect, but possible. That’s why we prioritize purpose, flexibility, connection, and recognition, so our people can thrive and love what they do, most days.&amp;nbsp;
+Compensation and Benefits&amp;nbsp;
+Slalom prides itself on helping team members thrive in their work and life. As a result, Slalom is proud to invest in benefits that include meaningful time off and paid holidays, parental leave, 401(k) with a match, a range of choices for highly subsidized health, dental, &amp;amp; vision coverage, adoption and fertility assistance, and short/long-term disability. We also offer yearly $350 reimbursement account for any well-being-related expenses, as well as discounted home, auto, and pet insurance.
+Slalom is committed to fair and equitable compensation practices. For this role, we are hiring at the following levels and salary ranges:
+- East Bay, San Francisco, Silicon Valley:
+- Engineer: $102,000-$125,000
+In addition, individuals may be eligible for an annual discretionary bonus. Actual compensation will depend upon an individual’s skills, experience, qualifications, location, and other relevant factors. The pay range is subject to change and may be modified at any time.
+We will accept applicants until the position is filled.
+EEO and Accommodations
+Slalom is an equal opportunity employer and is committed to attracting, developing and retaining highly qualified talent who empower our innovative teams through unique perspectives and experiences. All qualified applicants will receive consideration for employment without regard to race, color, religion, sex, national origin, disability status, protected veterans’ status, or any other characteristic protected by federal, state, or local laws. Slalom will also consider qualified applications with criminal histories, consistent with legal requirements. Slalom welcomes and encourages applications from individuals with disabilities. Reasonable accommodations are available for candidates during all aspects of the selection process. Please advise the talent acquisition team if you require accommodations during the interview process. </t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Business Consulting and Services</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '821 2nd Ave.', 'addressLocality': 'Seattle', 'addressRegion': 'WA', 'postalCode': '98104', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>https://www.slalom.com/</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>We help people and organizations dream bigger, move faster, and build better tomorrows for all.</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Slalom is a fiercely human business and technology consulting company that leads with outcomes to bring more value, in all ways, always. We team with leaders who expect more. So we bring more.
+From strategy through delivery, our agile teams across 53 offices in 12 countries collaborate with you to bring powerful customer experiences, innovative ways of working, and new products, services, and businesses to life. Every day, we work at the forefront of industry, combining our deep roots in technology and data, to help you tackle challenges, improve operations, and drive sustainable growth. It’s why we are trusted by leaders across the majority of the Global 1000, many of the world’s most successful enterprise, mid-market, and emerging companies, and more than 500 high-impact public sector agencies, foundations, and universities.
+We lead with a balance of heart and practicality, curiosity and agility, local soul and global expertise. That means understanding your culture, goals, organization, and customers. That means being tireless problem solvers. And that means always standing by you as your trusted advisor, respectful challenger, and unwavering champion.
+Even our partnerships are built different. For more than 20 years, we've sought out and made strategic investments in the world’s emerging and leading technology platforms. Our 360-degree relationships with these innovators, built on mutual trust and respect, has cemented our position as a premier (and often first) partner of choice. We work together as one to offer tailored solutions that unlock the full potential of these technologies.
+At Slalom, we bring more day-one advantages, more connections and breakthroughs, more doing the right thing, more care for you and your team, and more return on your investment. So that together, we can dream bigger, move faster, and build better tomorrows for all.</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10212</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4451616068</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9/QcNmLh6mFLbrDFhHFBzA==</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-tech-economy-4451616068?position=4&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=9%2FQcNmLh6mFLbrDFhHFBzA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tech Economy</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/tech-economy-limited?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C4D0BAQHQ0gjkgfHrxQ/company-logo_100_100/company-logo_100_100/0/1630570389803/tech_economy_partners_logo?e=2147483647&amp;v=beta&amp;t=zgNSd56ZvUbK77RDSDbdqQInfuuDCNhr9Sq34JCFdc4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Greater Houston</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;What Makes Us a Great Place To Work&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.&lt;br&gt;&lt;br&gt;Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Who You’ll Work With&lt;br&gt;&lt;br&gt;&lt;/strong&gt;As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.&lt;br&gt;&lt;br&gt;Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making.&lt;br&gt;&lt;br&gt;The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.&lt;br&gt;&lt;br&gt;&lt;strong&gt;WHERE YOU’LL FIT WITHIN THE TEAM&lt;br&gt;&lt;br&gt;&lt;/strong&gt;AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.&lt;br&gt;&lt;br&gt;&lt;strong&gt;What You'll Do&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;strong&gt;Core ML and Data Pipeline Engineering (65%) &lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.&lt;/li&gt;&lt;li&gt;Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.&lt;/li&gt;&lt;li&gt;Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.&lt;/li&gt;&lt;li&gt;Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.&lt;/li&gt;&lt;li&gt;Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Collaboration and Support (25%)&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.&lt;/li&gt;&lt;li&gt;Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.&lt;/li&gt;&lt;li&gt;Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.&lt;/li&gt;&lt;li&gt;Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Other (10%):&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.&lt;/li&gt;&lt;li&gt;Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.&lt;/li&gt;&lt;li&gt;Take on interviewing and hiring-loop participation as your experience grows.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;About You&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).&lt;/li&gt;&lt;li&gt;2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.&lt;/li&gt;&lt;li&gt;Exposure to model deployment, serving, or monitoring is a plus.&lt;/li&gt;&lt;li&gt;Experience working with structured feedback and code review, and a track record of improving code quality over time.&lt;/li&gt;&lt;li&gt;Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.&lt;/li&gt;&lt;li&gt;Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.&lt;/li&gt;&lt;li&gt;Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;ML engineering / LLMOps&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.&lt;/li&gt;&lt;li&gt;Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.&lt;/li&gt;&lt;li&gt;Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).&lt;/li&gt;&lt;li&gt;Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.&lt;/li&gt;&lt;li&gt;RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.&lt;/li&gt;&lt;li&gt;Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.&lt;/li&gt;&lt;li&gt;Docker: comfortable containerising pipeline or serving code and running it locally for testing.&lt;/li&gt;&lt;li&gt;Git: confident with PR-based workflows.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Generative AI and agentic systems&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Contributes to inference and retrieval services that feed agent workflows as structured tool responses.&lt;/li&gt;&lt;li&gt;Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.&lt;/li&gt;&lt;li&gt;Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;General&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.&lt;/li&gt;&lt;li&gt;Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.&lt;/li&gt;&lt;li&gt;Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.&lt;/li&gt;&lt;li&gt;Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.&lt;/li&gt;&lt;li&gt;This role follows a hybrid model, requiring in-office presence at least 1 day per week&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;U.s. Compensation Information&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).&lt;br&gt;&lt;br&gt;&lt;strong&gt;Role&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:&lt;br&gt;&lt;br&gt;In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500&lt;br&gt;&lt;br&gt;In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750&lt;br&gt;&lt;br&gt;In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250&lt;br&gt;&lt;br&gt;Placement within these ranges will vary based on factors such as experience, education, training, and skill level.&lt;br&gt;&lt;br&gt;Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.&lt;br&gt;&lt;br&gt;Annual discretionary performance bonus&lt;br&gt;&lt;br&gt;This role may also be eligible for other elements of discretionary compensation&lt;br&gt;&lt;br&gt;4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date&lt;br&gt;&lt;br&gt;Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.&lt;br&gt;&lt;br&gt;Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck&lt;br&gt;&lt;br&gt;Generous paid time off, including parental leave, sick leave and paid holidays&lt;br&gt;&lt;br&gt;Fully vested 401(k) company contribution&lt;br&gt;&lt;br&gt;Paid Life and Long-Term Disability insurance&lt;br&gt;&lt;br&gt;Annual fitness reimbursements</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>What Makes Us a Great Place To Work
+We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.
+Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.
+Who You’ll Work With
+As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.
+Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making.
+The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.
+WHERE YOU’LL FIT WITHIN THE TEAM
+AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.
+What You'll Do
+Core ML and Data Pipeline Engineering (65%) 
+- Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.
+- Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.
+- Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.
+- Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.
+- Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.
+Collaboration and Support (25%)
+- Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.
+- Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.
+- Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.
+- Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.
+Other (10%):
+- Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.
+- Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.
+- Take on interviewing and hiring-loop participation as your experience grows.
+About You
+- Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).
+- 2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.
+- Exposure to model deployment, serving, or monitoring is a plus.
+- Experience working with structured feedback and code review, and a track record of improving code quality over time.
+- Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.
+- Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.
+- Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.
+ML engineering / LLMOps
+- Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.
+- Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.
+- Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).
+- Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.
+- RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.
+- Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.
+- Docker: comfortable containerising pipeline or serving code and running it locally for testing.
+- Git: confident with PR-based workflows.
+Generative AI and agentic systems
+- Contributes to inference and retrieval services that feed agent workflows as structured tool responses.
+- Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.
+- Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.
+General
+- Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.
+- Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.
+- Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.
+- Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.
+- This role follows a hybrid model, requiring in-office presence at least 1 day per week
+U.s. Compensation Information
+Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).
+Role
+Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:
+In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500
+In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750
+In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250
+Placement within these ranges will vary based on factors such as experience, education, training, and skill level.
+Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.
+Annual discretionary performance bonus
+This role may also be eligible for other elements of discretionary compensation
+4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date
+Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.
+Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck
+Generous paid time off, including parental leave, sick leave and paid holidays
+Fully vested 401(k) company contribution
+Paid Life and Long-Term Disability insurance
+Annual fitness reimbursements</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Business Consulting and Services</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '16-19 Eastcastle Street', 'addressLocality': 'London', 'addressRegion': 'England', 'postalCode': 'W1W 8DY', 'addressCountry': 'GB'}</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://techeconomy.net</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Strategic Advisers to Technology-Enabled Companies and Private Equity Investors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Tech Economy is a technology focused specialty consulting firm. We conduct buy-side and sell-side Tech DDs as well as value creation assignments. Our clients include leading global and mid-market PE firms on both sides of the Atlantic, as well as their software and tech enabled portfolio companies. We cover the entire PE ownership lifecycle: from pre-investment technology diligence, post-closing 100-day planning, tech value creation, through to Vendor DD exit preparation.
+Our firm works and has deep experience across a wide range of technology segments including, ERP, Healthcare IT, E-commerce, Cybersecurity, E-Learning, IT services, Data Analytics, and AI.
+We know what it takes to run a successful technology company and how to ensure investment transaction completion. We have the expertise, experience, and resources to deliver rapid and actionable output and create lasting value for our clients.</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4432375310</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0jcgBl5aHR2wfDLfnrxdFQ==</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-hashlist-4432375310?position=6&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=0jcgBl5aHR2wfDLfnrxdFQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hashlist</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hashlist?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C4D0BAQGofOBg3f4OEQ/company-logo_100_100/company-logo_100_100/0/1658843664544/talentrator_logo?e=2147483647&amp;v=beta&amp;t=68CqZEHSUlh5WaYPqyCS8YCwR8yC9FbVRjwGTviPwJM</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;About the job&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;We're looking for an AI/ML Engineer to join a forward-thinking Software Engineering organisation within a major global automotive OEM.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;The role is engineering-first — designing, building, and delivering end-to-end AI/ML solutions that solve real engineering and product problems. Engineers in this role contribute across the full lifecycle, from design and development through validation and production handoff, working closely with product teams and the MLOps function.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Engagement detail&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Location: Auburn Hills&lt;/li&gt;&lt;li&gt;Contract type: Permanent or freelance&lt;/li&gt;&lt;li&gt;Start date: ASAP&lt;/li&gt;&lt;li&gt;Work model: Hybrid&lt;/li&gt;&lt;li&gt;Benefits: Competitive package; high-impact, high-visibility role within a major software-defined vehicle programme&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Responsibilities&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Design and implement ML models using structured, time-series, and unstructured data&lt;/li&gt;&lt;li&gt;Apply AI/ML techniques pragmatically to engineering, quality, and product use cases&lt;/li&gt;&lt;li&gt;Build production-ready AI systems including data pipelines, feature engineering, model training and inference services, and integration with downstream systems&lt;/li&gt;&lt;li&gt;Develop agentic solutions combining LLMs and other systems&lt;/li&gt;&lt;li&gt;Contribute to reusable AI/ML components and shared engineering frameworks&lt;/li&gt;&lt;li&gt;Write clean, maintainable, and testable Python code&lt;/li&gt;&lt;li&gt;Own implementation tasks from design through deployment readiness&lt;/li&gt;&lt;li&gt;Work closely with stakeholders to clarify requirements and iterate solutions&lt;/li&gt;&lt;li&gt;Prepare solutions for operationalisation in partnership with MLOps teams&lt;/li&gt;&lt;li&gt;Develop lightweight front-end components or internal tools — dashboards, experimentation interfaces, or demonstration tools — where required&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Qualifications&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Strong software engineering fundamentals&lt;/li&gt;&lt;li&gt;Practical experience applying machine learning in real production systems&lt;/li&gt;&lt;li&gt;Proficiency in Python and common ML libraries&lt;/li&gt;&lt;li&gt;Ability to work across data, modelling, and software concerns&lt;/li&gt;&lt;li&gt;Degree in engineering, computer science, applied mathematics, or a related field&lt;/li&gt;&lt;li&gt;Experience with cloud-based data or ML platforms is a plus&lt;/li&gt;&lt;li&gt;Experience building agentic solutions is advantageous&lt;/li&gt;&lt;li&gt;Familiarity with MLOps concepts — CI/CD for ML, monitoring, retraining — is beneficial&lt;/li&gt;&lt;li&gt;Frontend or full-stack experience supporting AI tools is a plus&lt;/li&gt;&lt;li&gt;Background in regulated or industrial engineering environments is advantageous&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Next Steps&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Click Apply&lt;/li&gt;&lt;li&gt;We will review your application. If qualified, you'll be accepted into the Hashlist network and considered for this and other relevant projects&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+About the job
+We're looking for an AI/ML Engineer to join a forward-thinking Software Engineering organisation within a major global automotive OEM.
+The role is engineering-first — designing, building, and delivering end-to-end AI/ML solutions that solve real engineering and product problems. Engineers in this role contribute across the full lifecycle, from design and development through validation and production handoff, working closely with product teams and the MLOps function.
+Engagement detail
+- Location: Auburn Hills
+- Contract type: Permanent or freelance
+- Start date: ASAP
+- Work model: Hybrid
+- Benefits: Competitive package; high-impact, high-visibility role within a major software-defined vehicle programme
+Responsibilities
+- Design and implement ML models using structured, time-series, and unstructured data
+- Apply AI/ML techniques pragmatically to engineering, quality, and product use cases
+- Build production-ready AI systems including data pipelines, feature engineering, model training and inference services, and integration with downstream systems
+- Develop agentic solutions combining LLMs and other systems
+- Contribute to reusable AI/ML components and shared engineering frameworks
+- Write clean, maintainable, and testable Python code
+- Own implementation tasks from design through deployment readiness
+- Work closely with stakeholders to clarify requirements and iterate solutions
+- Prepare solutions for operationalisation in partnership with MLOps teams
+- Develop lightweight front-end components or internal tools — dashboards, experimentation interfaces, or demonstration tools — where required
+Qualifications
+- Strong software engineering fundamentals
+- Practical experience applying machine learning in real production systems
+- Proficiency in Python and common ML libraries
+- Ability to work across data, modelling, and software concerns
+- Degree in engineering, computer science, applied mathematics, or a related field
+- Experience with cloud-based data or ML platforms is a plus
+- Experience building agentic solutions is advantageous
+- Familiarity with MLOps concepts — CI/CD for ML, monitoring, retraining — is beneficial
+- Frontend or full-stack experience supporting AI tools is a plus
+- Background in regulated or industrial engineering environments is advantageous
+Next Steps
+- Click Apply
+- We will review your application. If qualified, you'll be accepted into the Hashlist network and considered for this and other relevant projects</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>General Business</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Motor Vehicle Manufacturing</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'addressLocality': 'San Francisco', 'addressRegion': 'California', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>http://www.hashlist.com</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Tools &amp; Services to Build Physical AI</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>For decades, vehicles and robots were mechanical products.
+Today, they run on chips, software &amp; AI.
+The bottleneck is integration.
+Hashlist is a leading integrator for physical AI, vehicle platforms, and safety critical systems.
+We build machines from the future.
+Our work is supported by AI-native development tools and a service delivery network of
+100,000+ integration experts for an incredible speed of execution.
+https://www.hashlist.com/</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4451566377</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>q3Md2xn2JeIXmkEu3v9nkw==</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-bain-company-4451566377?position=2&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=q3Md2xn2JeIXmkEu3v9nkw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bain-and-company?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQHJWWQNCmnqKg/company-logo_100_100/company-logo_100_100/0/1719929153718/bain_and_company_logo?e=2147483647&amp;v=beta&amp;t=hOsU1bVj9dJZI9c0TujGpXV69c1dwdAsI9khve8rwOk</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;span&gt;&lt;strong&gt;&lt;span&gt;WHAT MAKES US A GREAT PLACE TO WORK&lt;/span&gt;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.&lt;/span&gt;&lt;span&gt;&lt;br&gt;&lt;/span&gt;&lt;span&gt;&lt;strong&gt;WHO YOU’LL WORK WITH&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making. &amp;nbsp;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;WHERE YOU’LL FIT WITHIN THE TEAM&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;WHAT YOU'LL DO&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Core ML and Data Pipeline Engineering (65%)&amp;nbsp;&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Collaboration and Support (25%)&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Other (10%):&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Take on interviewing and hiring-loop participation as your experience grows.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;ABOUT YOU&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to model deployment, serving, or monitoring is a plus.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Experience working with structured feedback and code review, and a track record of improving code quality over time.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.&lt;br&gt;&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;ML engineering / LLMOps&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Docker: comfortable containerising pipeline or serving code and running it locally for testing.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Git: confident with PR-based workflows.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;Generative AI and agentic systems&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Contributes to inference and retrieval services that feed agent workflows as structured tool responses.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;General&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;span&gt;Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;span&gt;This role follows a hybrid model, requiring in-office presence at least 1 day per week&lt;/span&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;span&gt;&lt;strong&gt;U.S. COMPENSATION INFORMATION&lt;/strong&gt;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Placement within these ranges will vary based on factors such as experience, education, training, and skill level.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Annual discretionary performance bonus&amp;nbsp;&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;This role may also be eligible for other elements of discretionary compensation&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Generous paid time off, including parental leave, sick leave and paid holidays&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Fully vested 401(k) company contribution&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Paid Life and Long-Term Disability insurance&lt;/span&gt;&lt;/p&gt;&lt;p&gt;&lt;span&gt;Annual fitness reimbursements&lt;/span&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+WHAT MAKES US A GREAT PLACE TO WORK
+We are proud to be consistently recognized as one of the world’s best places to work. We are currently the top ranked consulting firm on Glassdoor’s Best Places to Work list and have earned the #1 overall spot a record seven times.
+Extraordinary teams are at the heart of our business strategy, but these don’t happen by chance. They require intentional focus on bringing together a broad set of backgrounds, cultures, experiences, perspectives, and skills in a supportive and inclusive work environment. We hire people with exceptional talent and create an environment in which every individual can thrive professionally and personally.
+WHO YOU’LL WORK WITH
+As the premier consulting partner for the private equity industry, Bain's PEG boasts a global practice that is over three times larger than any competitor. Our network of over 1,000 professionals supports private equity and institutional investor clients through every stage of the investment life cycle, from deal generation and due diligence to portfolio value creation and exit planning.
+Bain &amp;amp; Company is developing a suite of cutting-edge data and software solutions designed to revolutionize how the private equity industry uses data for investment insights and decision-making. &amp;nbsp;
+The PEG Innovation team's mission is to create analytical solutions for Bain clients, teams, and the broader institutional investor space using proprietary software and data products. This includes the development, commercialization, and daily management of Bain's proprietary datasets, data, and software businesses.
+WHERE YOU’LL FIT WITHIN THE TEAM
+AI/ML Engineers on the Diligence Platform build and maintain the data, feature, and retrieval pipelines that power production RAG and ML systems. You work under the guidance of Senior ML Engineers and the Engineering Manager to implement and operate components of the ingestion, embedding, and retrieval stack, ship well-tested production code, and grow your ownership of these systems over time. You partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined pieces of larger pipelines and RAG workstreams, and you build the habits, tooling fluency, and production judgment expected of a Senior ML Engineer. This is a hands-on, growth-oriented engineering role: you are expected to ship reliable, observable code from your first weeks, and to take on increasing ownership as your track record builds.
+WHAT YOU'LL DO
+Core ML and Data Pipeline Engineering (65%)&amp;nbsp;
+- Implement and maintain components of production data and ML pipelines: ingestion jobs, feature and embedding pipelines, and Celery-based workers, under the direction of senior engineers.
+- Build and support pieces of the RAG and retrieval stack: chunking, embedding calls, indexing into pgvector, and basic retrieval and re-ranking logic, following established patterns.
+- Write production-quality Python: type hints, tests, and linting to the team's standards, with code reviewed by senior engineers before merge.
+- Instrument the pipelines and services you own with structured logs and metrics, and help build the dashboards and alerts that make issues visible.
+- Reproduce, triage, and fix bugs in pipeline and serving code, escalating ambiguous or high-severity issues to senior engineers.
+Collaboration and Support (25%)
+- Partner with Data Engineers, Data Scientists, and the Agent / AI squad on defined tasks within larger pipeline, retrieval, and evaluation workstreams.
+- Contribute test cases and sample data to evaluation harnesses and golden datasets, under the direction of senior engineers.
+- Participate in design reviews and code reviews, both as reviewer and reviewee, building judgment about production trade-offs.
+- Keep runbooks, READMEs, and pipeline documentation current as you build and change the systems you touch.
+Other (10%):
+- Use AI coding assistants to accelerate scaffolding and boilerplate, and review generated code against team standards before committing.
+- Use LLMs to draft documentation and status notes; validate and refine outputs before sharing them.
+- Take on interviewing and hiring-loop participation as your experience grows.
+ABOUT YOU
+- Bachelor's degree in Computer Science, Engineering, Machine Learning, Data Science, Statistics, or a related field (or equivalent practical experience).
+- 2+ years of experience building software, data, or ML systems, ideally including some exposure to production pipelines or services.
+- Exposure to model deployment, serving, or monitoring is a plus.
+- Experience working with structured feedback and code review, and a track record of improving code quality over time.
+- Experience collaborating with Data Engineers, Data Scientists, or the Agent / AI squad to ship features that depend on retrieval or ML outputs.
+- Comfort with Python as a primary language; exposure to a modern cloud environment (Databricks, Azure, or AWS) is a plus.
+- Demonstrated ability to take a well-scoped task from specification to a tested, reviewed implementation with limited supervision.
+ML engineering / LLMOps
+- Working knowledge of Python for data and ML workloads: type hints, Pydantic, pytest, Ruff, with production-quality pipeline and serving code that would pass a code review.
+- Familiarity with MLflow concepts: experiment tracking, model registry, and promotion workflows.
+- Exposure to LLMOps concepts: prompt versioning, model gateways (e.g., Portkey), and inference orchestration frameworks (LangChain, LlamaIndex, or equivalent).
+- Good understanding of model-serving concepts: latency, throughput, and batching, even without direct production ownership yet.
+- RAG pipeline building blocks: chunking strategies, embeddings, and vector stores such as pgvector; able to contribute to indexing and retrieval jobs under senior guidance.
+- Understanding of model and pipeline evaluation basics: what a golden dataset is, and why regression gates matter in CI.
+- Docker: comfortable containerising pipeline or serving code and running it locally for testing.
+- Git: confident with PR-based workflows.
+Generative AI and agentic systems
+- Contributes to inference and retrieval services that feed agent workflows as structured tool responses.
+- Supports RAG quality work: helps build and run recall and precision checks against defined benchmarks.
+- Exposure to LLM-as-judge evaluation patterns, even if applied under senior-engineer direction.
+General
+- Treats testing, observability, and documentation as part of the job, not an afterthought, even on smaller tasks.
+- Raises questions and surfaces uncertainty early rather than guessing silently on ambiguous requirements.
+- Uses AI tooling to move faster, and reviews all generated code and documentation critically before it enters the codebase.
+- Communicates clearly with teammates about progress, blockers, and trade-offs; asks for help early.
+- This role follows a hybrid model, requiring in-office presence at least 1 day per week
+U.S. COMPENSATION INFORMATION
+Compensation for this role includes base salary, annual discretionary performance bonus, 401(k) plan with an annual employer contribution based on years of service and Bain’s best in class benefits package (details listed below).
+Some local governments in the United States require a good-faith, reasonable salary range be included in job postings for open roles. The estimated annualized compensation for this role is as follows:
+In Atlanta, the good-faith, reasonable annualized full-time salary range for this role is between $79,250 - $86,500
+In Texas, the good-faith, reasonable annualized full-time salary range for this role is between $83,313 - $90,750
+In Chicago, the good-faith, reasonable annualized full-time salary range for this role is between $87,438 - $95,250
+Placement within these ranges will vary based on factors such as experience, education, training, and skill level.
+Compensation also includes a discretionary annual performance bonus, 401(k) plan with employer contribution, and Bain’s best-in-class benefits—including full premium coverage for medical, dental, and vision, generous paid time off, and more.
+Annual discretionary performance bonus&amp;nbsp;
+This role may also be eligible for other elements of discretionary compensation
+4.5% 401(k) company contribution, which increases after 3 years of service and is 100% vested upon start date
+Bain &amp;amp; Company's comprehensive benefits and wellness program is designed to help employees achieve personal independence, protection and stability in the areas most important to you and your family.
+Bain pays 100% individual employee premiums for medical, dental and vision programs, offering one of the most comprehensive medical plans for employees without impacting your paycheck
+Generous paid time off, including parental leave, sick leave and paid holidays
+Fully vested 401(k) company contribution
+Paid Life and Long-Term Disability insurance
+Annual fitness reimbursements</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Business Consulting and Services</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '350 Boylston St', 'addressLocality': 'Boston', 'addressRegion': 'Massachusetts', 'postalCode': '02116', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>http://www.bain.com</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company is a global consultancy that helps the world’s most ambitious change makers define the future. 
+Across 65 cities in 40 countries, we work alongside our clients as one team with a shared ambition to achieve extraordinary results, outperform the competition, and redefine industries. We complement our tailored, integrated expertise with a vibrant ecosystem of digital innovators to deliver better, faster, and more enduring outcomes. Our 10-year commitment to invest more than $1 billion in pro bono services brings our talent, expertise, and insight to organizations tackling today’s urgent challenges in education, racial equity, social justice, economic development, and the environment. We earned a platinum rating from EcoVadis, the leading platform for environmental, social, and ethical performance ratings for global supply chains, putting us in the top 1% of all companies. Since our founding in 1973, we have measured our success by the success of our clients.</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>26107</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4452104057</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>hcZgoH4/4mRb3cYJ15MDGA==</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/artificial-intelligence-engineer-at-yara-ai-4452104057?position=3&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=hcZgoH4%2F4mRb3cYJ15MDGA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yara AI</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/yara-jobs?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFTgTqK-HzZuA/company-logo_100_100/B4EZ5__10ZI8AM-/0/1780263904406?e=2147483647&amp;v=beta&amp;t=JSP0sS5tJ0mYJGRzekEnCaFeu0Xw51gsVy9isOC34FY</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;About Yara&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Yara is building the future of finding work. Most hiring tools are stuck in the 90s and AI is making it worse, not better. More spam, more noise, more generic outreach that wastes everyone's time. We're reworking how people find their next role with one profile that actually shows your work, smart matching that puts you in front of the right companies, and a real person on the other side who cares about getting it right.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;We work with companies across AI, developer tools, consumer, fintech, and health tech, ranging from teams that have raised $1B+ with 3,000+ employees to earlier stage companies at $50M+ with 100+ employees. We've helped talent from Google, Apple, Palantir, Uber, and Ramp connect with companies like Vercel, Paraform, Abridge, and Parallel.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About this role&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Every company in the Yara Network is building with LLMs, and engineers who can take agents to production are the most requested profile we have. If you've built with models beyond the demo stage, with tools, evals, retrieval, and real users, this pipeline moves fast.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;This is a Yara Network Application. Apply once and get matched across our partner companies.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Who this is for&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;You've shipped something LLM-powered that real people used, at work or on your own.&lt;/li&gt;&lt;li&gt;You know the difference between a wrapper and a system, because you've had to fix the wrapper.&lt;/li&gt;&lt;li&gt;You keep up. New models, new patterns, new tooling, weekly.&lt;/li&gt;&lt;li&gt;Your agent work sits on real engineering fundamentals, and interviews confirm it.&lt;/li&gt;&lt;li&gt;You want to work at the companies defining this wave, from seed to scale.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You may be a good fit if you have&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Production LLM integration: tool-calling, RAG, evals, observability&lt;/li&gt;&lt;li&gt;Strong software fundamentals in TypeScript, Python, or Go&lt;/li&gt;&lt;li&gt;Shipped agentic products or serious agentic side projects&lt;/li&gt;&lt;li&gt;Experience at a startup or high-bar engineering org is a plus&lt;/li&gt;&lt;li&gt;Links to anything agentic you've built&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;If we don't move forward together, you can still use your Yara to list your work, browse millions of roles, manage your job search, and stay in our network for when something new comes up.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>$200,000.00/yr - $500,000.00/yr</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+About Yara
+Yara is building the future of finding work. Most hiring tools are stuck in the 90s and AI is making it worse, not better. More spam, more noise, more generic outreach that wastes everyone's time. We're reworking how people find their next role with one profile that actually shows your work, smart matching that puts you in front of the right companies, and a real person on the other side who cares about getting it right.
+We work with companies across AI, developer tools, consumer, fintech, and health tech, ranging from teams that have raised $1B+ with 3,000+ employees to earlier stage companies at $50M+ with 100+ employees. We've helped talent from Google, Apple, Palantir, Uber, and Ramp connect with companies like Vercel, Paraform, Abridge, and Parallel.
+About this role
+Every company in the Yara Network is building with LLMs, and engineers who can take agents to production are the most requested profile we have. If you've built with models beyond the demo stage, with tools, evals, retrieval, and real users, this pipeline moves fast.
+This is a Yara Network Application. Apply once and get matched across our partner companies.
+Who this is for
+- You've shipped something LLM-powered that real people used, at work or on your own.
+- You know the difference between a wrapper and a system, because you've had to fix the wrapper.
+- You keep up. New models, new patterns, new tooling, weekly.
+- Your agent work sits on real engineering fundamentals, and interviews confirm it.
+- You want to work at the companies defining this wave, from seed to scale.
+You may be a good fit if you have
+- Production LLM integration: tool-calling, RAG, evals, observability
+- Strong software fundamentals in TypeScript, Python, or Go
+- Shipped agentic products or serious agentic side projects
+- Experience at a startup or high-bar engineering org is a plus
+- Links to anything agentic you've built
+If we don't move forward together, you can still use your Yara to list your work, browse millions of roles, manage your job search, and stay in our network for when something new comes up.
+</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'addressLocality': 'San Francisco', 'addressRegion': 'California', 'postalCode': '94102', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://www.yara.so/</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Your AI job search agent</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yara is an AI agent that runs your job search for you.
+It's like having a recruiter by your side. Someone who knows the market, keeps track of every opportunity, and is always in your corner. The more you use Yara, the better it understands what you actually want and the roles worth your time, so it can support you the way a great recruiter would, available whenever you need it.
+Most job seekers spend hours doing the same repetitive work: digging through listings, researching companies, rewriting the same application a hundred times, and then waiting in silence. Yara handles that work so you can focus on the conversations that actually matter.
+Tell Yara what you're looking for and it goes to work. It finds roles that fit, researches each company and team so you walk in informed, drafts tailored outreach, and applies on your behalf, including filling out the tedious ATS forms. You stay in control the whole way through. Yara does the work, you click submit when you're ready.
+Yara is built by Flows, an AI talent lab building the tools that make hiring and getting hired actually work.</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4450304107</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>eWb4h4xfg7BjfGaXxgv+aA==</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BWZMqS91XeFqN/I3y0U8Uw==</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-at-recruiting-from-scratch-4450304107?position=1&amp;pageNum=0&amp;refId=BWZMqS91XeFqN%2FI3y0U8Uw%3D%3D&amp;trackingId=eWb4h4xfg7BjfGaXxgv%2BaA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Recruiting from Scratch</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/recruiting-from-scratch?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQExPmR_VOSIGg/company-logo_100_100/company-logo_100_100/0/1692290558535/recruiting_from_scratch_logo?e=2147483647&amp;v=beta&amp;t=fBJ47VIH8QzIQVOOhL2zRan_vQhUwfHstSEXXDMb8mg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Who is Recruiting from Scratch:&lt;/strong&gt; Recruiting from Scratch is a specialized talent firm dedicated to helping companies build exceptional teams. We partner closely with our clients to deeply understand their needs, then connect them with top-tier candidates who are not only highly skilled but also the right fit for the company’s culture and vision. Our mission is simple: place the best people in the right roles to drive long-term success for both clients and candidates.&lt;/p&gt;&lt;p&gt;https://www.recruitingfromscratch.com/&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Title of the Role: &lt;/strong&gt;Machine Learning Engineer&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location&lt;/strong&gt;: New York, NY&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Company Stage of Funding&lt;/strong&gt;: Early-Stage, Venture-Backed AI Healthcare Startup&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Office Type:&lt;/strong&gt; Hybrid; some weeks may require up to 5 days/week in-office, other weeks only 1 days but we average 3 days a week&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Salary&lt;/strong&gt;: $120,000–$150,000 + Equity&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Role Overview&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;We’re an early-stage, venture-backed startup building AI systems for medical coding and revenue cycle workflows. We’re looking for a &lt;strong&gt;Founding AI Engineer&lt;/strong&gt; to take end-to-end ownership of core AI systems—from data ingestion and retrieval to model adaptation and production deployment.&lt;/p&gt;&lt;p&gt;This is a hands-on role in a fast-paced environment with high responsibility and meaningful equity upside.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What You’ll Work On&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Design and build &lt;strong&gt;RAG systems&lt;/strong&gt; over clinical notes, billing data, and coding guidelines&lt;/li&gt;&lt;li&gt;Adapt and fine-tune LLMs (LoRA/QLoRA, instruction tuning) for medical coding and explanations&lt;/li&gt;&lt;li&gt;Help architect and operate &lt;strong&gt;GCP-based infrastructure&lt;/strong&gt; (Cloud Run/GKE, Vertex AI, BigQuery, Pub/Sub)&lt;/li&gt;&lt;li&gt;Build evaluation and feedback loops to measure accuracy and quality&lt;/li&gt;&lt;li&gt;Own integrations with EHRs, RCM systems, and other healthcare data sources&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What We’re Looking For&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Experience building and shipping &lt;strong&gt;LLM + RAG systems in production&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;Hands-on experience with model adaptation or fine-tuning techniques&lt;/li&gt;&lt;li&gt;Strong backend engineering skills (Python, TypeScript, or similar)&lt;/li&gt;&lt;li&gt;Comfortable working with messy, real-world data and production systems&lt;/li&gt;&lt;li&gt;Ownership mindset and ability to move quickly in an early-stage startup&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Nice to Have&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Healthcare, EHR, or medical coding experience (ICD-10, CPT, HCPCS)&lt;/li&gt;&lt;li&gt;Experience handling PHI and working in HIPAA-regulated environments&lt;/li&gt;&lt;li&gt;Familiarity with Vertex AI or high-performance inference&lt;/li&gt;&lt;li&gt;NYC-based or able to be in-office periodically&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Compensation&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Base Salary:&lt;/strong&gt; $120,000 – $150,000&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Equity:&lt;/strong&gt; Meaningful early-stage equity&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>$120,000.00/yr - $150,000.00/yr</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Who is Recruiting from Scratch: Recruiting from Scratch is a specialized talent firm dedicated to helping companies build exceptional teams. We partner closely with our clients to deeply understand their needs, then connect them with top-tier candidates who are not only highly skilled but also the right fit for the company’s culture and vision. Our mission is simple: place the best people in the right roles to drive long-term success for both clients and candidates.
+https://www.recruitingfromscratch.com/
+Title of the Role: Machine Learning Engineer
+Location: New York, NY
+Company Stage of Funding: Early-Stage, Venture-Backed AI Healthcare Startup
+Office Type: Hybrid; some weeks may require up to 5 days/week in-office, other weeks only 1 days but we average 3 days a week
+Salary: $120,000–$150,000 + Equity
+Role Overview
+We’re an early-stage, venture-backed startup building AI systems for medical coding and revenue cycle workflows. We’re looking for a Founding AI Engineer to take end-to-end ownership of core AI systems—from data ingestion and retrieval to model adaptation and production deployment.
+This is a hands-on role in a fast-paced environment with high responsibility and meaningful equity upside.
+What You’ll Work On
+- Design and build RAG systems over clinical notes, billing data, and coding guidelines
+- Adapt and fine-tune LLMs (LoRA/QLoRA, instruction tuning) for medical coding and explanations
+- Help architect and operate GCP-based infrastructure (Cloud Run/GKE, Vertex AI, BigQuery, Pub/Sub)
+- Build evaluation and feedback loops to measure accuracy and quality
+- Own integrations with EHRs, RCM systems, and other healthcare data sources
+What We’re Looking For
+- Experience building and shipping LLM + RAG systems in production
+- Hands-on experience with model adaptation or fine-tuning techniques
+- Strong backend engineering skills (Python, TypeScript, or similar)
+- Comfortable working with messy, real-world data and production systems
+- Ownership mindset and ability to move quickly in an early-stage startup
+Nice to Have
+- Healthcare, EHR, or medical coding experience (ICD-10, CPT, HCPCS)
+- Experience handling PHI and working in HIPAA-regulated environments
+- Familiarity with Vertex AI or high-performance inference
+- NYC-based or able to be in-office periodically
+Compensation
+- Base Salary: $120,000 – $150,000
+- Equity: Meaningful early-stage equity
+</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Engineering, Research, and Product Management</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Financial Services, Software Development, and Hospitals and Health Care</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'addressLocality': 'New York', 'addressRegion': 'NY', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>http://recruitingfromscratch.com</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>We help hire across the best roles in engineering, product, marketing, design, accounting &amp; finance.</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Recruiting from Scratch provides recruiting services for companies that need to hire the best talent in software engineering, hardware engineering, product design, product management, marketing, GTM, and accounting &amp; finance.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-08-11 05:05:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Dominique Barber</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Senior Technical Recruiter at Recruiting from Scratch</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D5603AQEolhBTPKI1Hw/profile-displayphoto-shrink_400_400/profile-displayphoto-shrink_400_400/0/1688064084736?e=2147483647&amp;v=beta&amp;t=ijiJAWFI4OUwJ8ydhax4qf7e2u4NAPHDr-fPrOj6P8s</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dlbarber91</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -1884,7 +1884,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Not Applied</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Not Applied</t>
+          <t>Failed</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -4131,6 +4131,1766 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4454012661</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dII1y5WGyKGOqqap+dwppA==</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-product-engineer-at-alexander-chapman-4454012661?position=7&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=dII1y5WGyKGOqqap%2BdwppA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Product Engineer</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Alexander Chapman</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/alexander-chapman?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C4E0BAQHetz_sr_qHBQ/company-logo_100_100/company-logo_100_100/0/1647822869660/alexander_chapman_logo?e=2147483647&amp;v=beta&amp;t=fXf23KD1xm92km0--__xsbUDUOxFVSIlMPe2k053cE0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>California, United States</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Connect for more:&lt;/strong&gt; https://www.linkedin.com/in/arianit-krasniqi-b6ba66388/&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;I'm working with a fast-growing startup building an &lt;strong&gt;AI platform that runs business operations autonomously&lt;/strong&gt; through &lt;strong&gt;multi-agent systems&lt;/strong&gt;. They are seeking a &lt;strong&gt;Product Engineer&lt;/strong&gt; to own and ship &lt;strong&gt;LLM-powered features end-to-end&lt;/strong&gt;, directly impacting how enterprises operate.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;This is a highly &lt;strong&gt;builder-first role&lt;/strong&gt;, where engineers take full ownership from &lt;strong&gt;customer problem → design → production → iteration&lt;/strong&gt;, working closely with users and shipping continuously. The focus is on building &lt;strong&gt;agent systems&lt;/strong&gt; that execute workflows like &lt;strong&gt;OKRs, reporting cadences, and operational playbooks&lt;/strong&gt;, while ensuring &lt;strong&gt;enterprise-grade reliability&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Engineers will design and implement &lt;strong&gt;multi-agent architectures&lt;/strong&gt;, make decisions around &lt;strong&gt;model selection, orchestration, and evaluation&lt;/strong&gt;, and build &lt;strong&gt;chat-native product experiences&lt;/strong&gt; used daily by customers. The role combines &lt;strong&gt;systems thinking with product intuition&lt;/strong&gt;, requiring strong judgment on tradeoffs between capability, reliability, and user impact.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Ideal candidates have &lt;strong&gt;2–5 years of experience&lt;/strong&gt;, strong skills in &lt;strong&gt;Python&lt;/strong&gt; and familiarity with &lt;strong&gt;React/Next.js&lt;/strong&gt;, and hands-on experience shipping &lt;strong&gt;LLM or agent-based systems in production&lt;/strong&gt;. They are fast-moving, customer-focused builders who use &lt;strong&gt;AI tools daily&lt;/strong&gt;, iterate quickly in production, and thrive in &lt;strong&gt;high-ownership, early-stage environments&lt;/strong&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Connect for more: https://www.linkedin.com/in/arianit-krasniqi-b6ba66388/
+I'm working with a fast-growing startup building an AI platform that runs business operations autonomously through multi-agent systems. They are seeking a Product Engineer to own and ship LLM-powered features end-to-end, directly impacting how enterprises operate.
+This is a highly builder-first role, where engineers take full ownership from customer problem → design → production → iteration, working closely with users and shipping continuously. The focus is on building agent systems that execute workflows like OKRs, reporting cadences, and operational playbooks, while ensuring enterprise-grade reliability.
+Engineers will design and implement multi-agent architectures, make decisions around model selection, orchestration, and evaluation, and build chat-native product experiences used daily by customers. The role combines systems thinking with product intuition, requiring strong judgment on tradeoffs between capability, reliability, and user impact.
+Ideal candidates have 2–5 years of experience, strong skills in Python and familiarity with React/Next.js, and hands-on experience shipping LLM or agent-based systems in production. They are fast-moving, customer-focused builders who use AI tools daily, iterate quickly in production, and thrive in high-ownership, early-stage environments.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'addressLocality': 'London', 'addressCountry': 'gb'}</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>http://www.alexanderchapmanltd.com</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matching excellence. </t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alexander Chapman is a leading global search firm specializing in comprehensive staffing and talent management solutions tailored to the unique needs of local, regional, national, and international businesses. With a dedicated focus on niche recruiting expertise and expert project management, Alexander Chapman excels in providing innovative solutions within the Finance sectors.
+</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Arianit Krasniqi</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>https://static.licdn.com/aero-v1/sc/h/9c8pery4andzj6ohjkjp54ma2</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arianit-krasniqi-b6ba66388</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4439922787</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sKIn5g4B7M3fkzMKgR8m5g==</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/artificial-intelligence-engineer-at-neubird-ai-4439922787?position=8&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=sKIn5g4B7M3fkzMKgR8m5g%3D%3D</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NeuBird AI</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/neubird-ai?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQF6OENzsfBHaQ/company-logo_100_100/B56ZwGcOhMHcAQ-/0/1769634589064/neubird_ai_logo?e=2147483647&amp;v=beta&amp;t=0YlYZc_RW7iV6oiiAEdYX3Q-CTVcdsCFWaZGYXB5ETQ</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>California, United States</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Job Description:&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;As an AI engineer, you will be involved in model training, deployment, and maintenance. You will work with RLHF and fine-tuning of LLMs. This role requires a blend of analytical skills, creativity, and strong AI domain knowledge. This role is critical in delivering an enterprise experience with LLMs.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;br&gt;Responsibilitie&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;s:Lead the development and customization of large-scale language models that drive the NeuBird AI platfor&lt;/li&gt;&lt;li&gt;m.Implement and experiment with RLHF to enhance model performance and decision-makin&lt;/li&gt;&lt;li&gt;g.Collaborate with cross-functional teams to integrate language models into various applications and platform&lt;/li&gt;&lt;li&gt;s.Work on model fine-tuning, performance optimization, and continuous improvemen&lt;/li&gt;&lt;li&gt;t.Stay up-to-date with the latest research and trends in language modeling and RLH&lt;/li&gt;&lt;li&gt;F.Contribute to research projects and technical publication&lt;/li&gt;&lt;li&gt;s.Participate in code reviews and mentorship of junior engineer&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;s.&lt;br&gt;&lt;br&gt;Qualificati&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;ons:Bachelor's or Master's degree in Computer Science, Machine Learning, or a related f&lt;/li&gt;&lt;li&gt;ieldExperience with model training, deploying, and maintena&lt;/li&gt;&lt;li&gt;nce.Strong knowledge of reinforced feedback techniques and reinforcement learn&lt;/li&gt;&lt;li&gt;ing.Proficiency in frameworks like PyTorch, TensorFlow, or simi&lt;/li&gt;&lt;li&gt;lar.Familiarity with NLP, text generation, and language understand&lt;/li&gt;&lt;li&gt;ing.Strong problem-solving skills and a passion for addressing complex AI challen&lt;/li&gt;&lt;li&gt;ges.Excellent communication and collaboration abilit&lt;/li&gt;&lt;li&gt;ies.Self-motivated and eager to stay at the forefront of AI advanceme&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;nts.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Job Description:
+As an AI engineer, you will be involved in model training, deployment, and maintenance. You will work with RLHF and fine-tuning of LLMs. This role requires a blend of analytical skills, creativity, and strong AI domain knowledge. This role is critical in delivering an enterprise experience with LLMs.
+Responsibilitie
+- s:Lead the development and customization of large-scale language models that drive the NeuBird AI platfor
+- m.Implement and experiment with RLHF to enhance model performance and decision-makin
+- g.Collaborate with cross-functional teams to integrate language models into various applications and platform
+- s.Work on model fine-tuning, performance optimization, and continuous improvemen
+- t.Stay up-to-date with the latest research and trends in language modeling and RLH
+- F.Contribute to research projects and technical publication
+- s.Participate in code reviews and mentorship of junior engineer
+s.
+Qualificati
+- ons:Bachelor's or Master's degree in Computer Science, Machine Learning, or a related f
+- ieldExperience with model training, deploying, and maintena
+- nce.Strong knowledge of reinforced feedback techniques and reinforcement learn
+- ing.Proficiency in frameworks like PyTorch, TensorFlow, or simi
+- lar.Familiarity with NLP, text generation, and language understand
+- ing.Strong problem-solving skills and a passion for addressing complex AI challen
+- ges.Excellent communication and collaboration abilit
+- ies.Self-motivated and eager to stay at the forefront of AI advanceme
+nts.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Entry level</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>IT System Custom Software Development</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '2000 Broadway St', 'addressLocality': 'Redwood City', 'addressRegion': 'California', 'postalCode': '94063', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>https://neubird.ai</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Autonomous production operations. 
+Prevent issues. Resolve in minutes. Operate autonomously.</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production ops agent for modern engineering teams. Prevent issues before impact, resolve incidents in minutes, and operate production systems autonomously.
+Built for enterprise SRE, platform, DevOps, and on-call teams, NeuBird AI applies advanced context engineering and deep domain expertise to correlate telemetry, surface risks early, and automate root cause analysis securely across hybrid cloud environments.
+</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4454304447</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>aH1wKYh1EjTn88dx66XmPQ==</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-developer-at-booz-allen-hamilton-4454304447?position=9&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=aH1wKYh1EjTn88dx66XmPQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/booz-allen-hamilton?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFXBzVcVDSTOQ/company-logo_100_100/company-logo_100_100/0/1737465459820/booz_allen_hamilton_logo?e=2147483647&amp;v=beta&amp;t=SswDqk5ZXqP0jtQgXL12ktHuwfRb0zf8se42kJe-lFM</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Arlington, VA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Job Number: R0246928&lt;br&gt;&lt;br&gt;&lt;/strong&gt;AI Developer&lt;br&gt;&lt;br&gt;&lt;strong&gt;The Opportunity: &lt;br&gt;&lt;br&gt;&lt;/strong&gt;As an experienced AI engineer, you know that AI systems are critical to understanding and processing massive datasets in an organization. Your ability to conduct statistical analyses on business processes using ML techniques makes you an integral part of delivering a customer-focused solution. We need your technical knowledge and desire to solve problems to support optimizing organizational efficiency. As an AI Developer on our Air Power team, you’ll train, test, deploy, and maintain models that learn from data.&lt;br&gt;&lt;br&gt;In this role, you’ll own and define the direction of mission-critical solutions by applying cutting-edge Agentic frameworks. You’ll be part of a large community of AI professionals across the company and collaborate with data engineers, data scientists, solutions architects, and product owners to deliver world-class solutions to transform how the Air Force manages its day-to-day business. Your skills and extensive technical expertise will guide clients as they navigate the landscape of Agentic Frameworks.&lt;br&gt;&lt;br&gt;Join us. The world can’t wait.&lt;br&gt;&lt;br&gt;&lt;strong&gt;You Have:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;2+ years of experience building production-grade software in Python, TypeScript, or Java with APIs and data services, including FastAPI, Flask, REST, GraphQL, or SQL&lt;/li&gt;&lt;li&gt;Experience developing and deploying AI-enabled applications such as LLMs, RAG, and agentic workflows to solve mission problems&lt;/li&gt;&lt;li&gt;Ability to design event-driven integrations and workflow automation such as asynchronous messaging or audit logging to move from insight to action&lt;/li&gt;&lt;li&gt;Ability to implement MLOps or DevSecOps practices such as CI/CD, containerization, automated testing, or model evaluation&lt;/li&gt;&lt;li&gt;Secret clearance&lt;/li&gt;&lt;li&gt;Bachelor’s degree in Mathematics, Computer Science, Software Engineering, or Data Science&lt;br&gt;&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Nice If You Have:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Experience working with geospatial or 3D data, including point clouds, LiDAR, or photogrammetry, or digital-twin or facility and asset data models&lt;/li&gt;&lt;li&gt;Experience integrating sensor streams or IoT telemetry and edge-to-cloud data flows such as Kafka, NATS, RabbitMQ, or equivalent for asset monitoring and situational awareness&lt;/li&gt;&lt;li&gt;Experience deploying software and data or ML pipelines in disconnected, air-gapped, or classified environments&lt;/li&gt;&lt;li&gt;Experience with cross-domain data handling constraints&lt;/li&gt;&lt;li&gt;Experience with RMF or STIG-aligned delivery&lt;/li&gt;&lt;li&gt;Experience with AI-assisted software development tools and practices such as code copilots, automated tests, or secure-by-design patterns to increase delivery velocity responsibly&lt;/li&gt;&lt;li&gt;TS/SCI clearance&lt;br&gt;&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Clearance:&lt;/strong&gt; &lt;br&gt;&lt;br&gt;Applicants selected will be subject to a security investigation and may need to meet eligibility requirements for access to classified information; Secret clearance is required.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Compensation&lt;br&gt;&lt;br&gt;&lt;/strong&gt;At Booz Allen, we celebrate your contributions, provide you with opportunities and choices, and support your total well-being. Our offerings include health, life, disability, financial, and retirement benefits, as well as paid leave, professional development, tuition assistance, work-life programs, and dependent care. Our recognition awards program acknowledges employees for exceptional performance and superior demonstration of our values. Full-time and part-time employees working at least 20 hours a week on a regular basis are eligible to participate in Booz Allen’s benefit programs. Individuals that do not meet the threshold are only eligible for select offerings, not inclusive of health benefits. We encourage you to learn more about our total benefits by visiting the Resource page on our Careers site and reviewing Our Employee Benefits page.&lt;br&gt;&lt;br&gt;Salary at Booz Allen is determined by various factors, including but not limited to location, the individual’s particular combination of education, knowledge, skills, competencies, and experience, as well as contract-specific affordability and organizational requirements. The projected compensation range for this position is $77,500.00 to $176,000.00 (annualized USD). The estimate displayed represents the typical salary range for this position and is just one component of Booz Allen’s total compensation package for employees. This posting will close within 90 days from the Posting Date.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Identity Statement&lt;br&gt;&lt;br&gt;&lt;/strong&gt;As part of the hiring process, we will ask you to complete an identity verification process that leverages advanced biometrics and artificial intelligence to ensure authenticity and protect against identity fraud. You are expected to be on camera during interviews and assessments. We reserve the right to take your picture to verify your identity and prevent fraud.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Candidate AI Usage Policy&lt;br&gt;&lt;br&gt;&lt;/strong&gt;AI is a part of our daily work at Booz Allen, and we are committed to the responsible and ethical use of AI tools. However, we want to ensure a fair candidate process based on &lt;strong&gt;your &lt;/strong&gt;own skills and knowledge. As part of this commitment, the use of artificial intelligence (AI) or other tools to assist with responses during interviews (whether in-person or virtual) is prohibited &lt;strong&gt;unless permission is explicitly provided&lt;/strong&gt;.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Work Model&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Our people-first culture prioritizes the benefits of collaboration, whether it occurs in person or virtually. To support engagement and effective communication, employees working virtually are generally expected to have their cameras on during meetings.&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Remote: If this position is listed as remote, there may still be occasions when you are required to work in person at a Booz Allen or customer facility.&lt;/li&gt;&lt;li&gt;Hybrid: If this position is listed as hybrid, you will be expected to work from a Booz Allen facility frequently, in alignment with leadership expectations and the needs of the role. You may also be required to work from or visit a customer facility.&lt;/li&gt;&lt;li&gt;Onsite: If this position is listed as onsite, work will primarily be performed at a Booz Allen office or customer facility, where employees will collaborate directly with colleagues and customers as required by the role.&lt;br&gt;&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Commitment to Non-Discrimination&lt;br&gt;&lt;br&gt;&lt;/strong&gt;All qualified applicants will receive consideration for employment without regard to disability, status as a protected veteran or any other status protected by applicable federal, state, local, or international law.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Job Number: R0246928
+AI Developer
+The Opportunity: 
+As an experienced AI engineer, you know that AI systems are critical to understanding and processing massive datasets in an organization. Your ability to conduct statistical analyses on business processes using ML techniques makes you an integral part of delivering a customer-focused solution. We need your technical knowledge and desire to solve problems to support optimizing organizational efficiency. As an AI Developer on our Air Power team, you’ll train, test, deploy, and maintain models that learn from data.
+In this role, you’ll own and define the direction of mission-critical solutions by applying cutting-edge Agentic frameworks. You’ll be part of a large community of AI professionals across the company and collaborate with data engineers, data scientists, solutions architects, and product owners to deliver world-class solutions to transform how the Air Force manages its day-to-day business. Your skills and extensive technical expertise will guide clients as they navigate the landscape of Agentic Frameworks.
+Join us. The world can’t wait.
+You Have:
+- 2+ years of experience building production-grade software in Python, TypeScript, or Java with APIs and data services, including FastAPI, Flask, REST, GraphQL, or SQL
+- Experience developing and deploying AI-enabled applications such as LLMs, RAG, and agentic workflows to solve mission problems
+- Ability to design event-driven integrations and workflow automation such as asynchronous messaging or audit logging to move from insight to action
+- Ability to implement MLOps or DevSecOps practices such as CI/CD, containerization, automated testing, or model evaluation
+- Secret clearance
+- Bachelor’s degree in Mathematics, Computer Science, Software Engineering, or Data Science
+Nice If You Have:
+- Experience working with geospatial or 3D data, including point clouds, LiDAR, or photogrammetry, or digital-twin or facility and asset data models
+- Experience integrating sensor streams or IoT telemetry and edge-to-cloud data flows such as Kafka, NATS, RabbitMQ, or equivalent for asset monitoring and situational awareness
+- Experience deploying software and data or ML pipelines in disconnected, air-gapped, or classified environments
+- Experience with cross-domain data handling constraints
+- Experience with RMF or STIG-aligned delivery
+- Experience with AI-assisted software development tools and practices such as code copilots, automated tests, or secure-by-design patterns to increase delivery velocity responsibly
+- TS/SCI clearance
+Clearance: 
+Applicants selected will be subject to a security investigation and may need to meet eligibility requirements for access to classified information; Secret clearance is required.
+Compensation
+At Booz Allen, we celebrate your contributions, provide you with opportunities and choices, and support your total well-being. Our offerings include health, life, disability, financial, and retirement benefits, as well as paid leave, professional development, tuition assistance, work-life programs, and dependent care. Our recognition awards program acknowledges employees for exceptional performance and superior demonstration of our values. Full-time and part-time employees working at least 20 hours a week on a regular basis are eligible to participate in Booz Allen’s benefit programs. Individuals that do not meet the threshold are only eligible for select offerings, not inclusive of health benefits. We encourage you to learn more about our total benefits by visiting the Resource page on our Careers site and reviewing Our Employee Benefits page.
+Salary at Booz Allen is determined by various factors, including but not limited to location, the individual’s particular combination of education, knowledge, skills, competencies, and experience, as well as contract-specific affordability and organizational requirements. The projected compensation range for this position is $77,500.00 to $176,000.00 (annualized USD). The estimate displayed represents the typical salary range for this position and is just one component of Booz Allen’s total compensation package for employees. This posting will close within 90 days from the Posting Date.
+Identity Statement
+As part of the hiring process, we will ask you to complete an identity verification process that leverages advanced biometrics and artificial intelligence to ensure authenticity and protect against identity fraud. You are expected to be on camera during interviews and assessments. We reserve the right to take your picture to verify your identity and prevent fraud.
+Candidate AI Usage Policy
+AI is a part of our daily work at Booz Allen, and we are committed to the responsible and ethical use of AI tools. However, we want to ensure a fair candidate process based on your own skills and knowledge. As part of this commitment, the use of artificial intelligence (AI) or other tools to assist with responses during interviews (whether in-person or virtual) is prohibited unless permission is explicitly provided.
+Work Model
+Our people-first culture prioritizes the benefits of collaboration, whether it occurs in person or virtually. To support engagement and effective communication, employees working virtually are generally expected to have their cameras on during meetings.
+- Remote: If this position is listed as remote, there may still be occasions when you are required to work in person at a Booz Allen or customer facility.
+- Hybrid: If this position is listed as hybrid, you will be expected to work from a Booz Allen facility frequently, in alignment with leadership expectations and the needs of the role. You may also be required to work from or visit a customer facility.
+- Onsite: If this position is listed as onsite, work will primarily be performed at a Booz Allen office or customer facility, where employees will collaborate directly with colleagues and customers as required by the role.
+Commitment to Non-Discrimination
+All qualified applicants will receive consideration for employment without regard to disability, status as a protected veteran or any other status protected by applicable federal, state, local, or international law.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '8283 Greensboro Drive', 'addressLocality': 'McLean', 'addressRegion': 'VA', 'postalCode': '22102', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>https://boozallen.co/3PbO3a2</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Whether at the border, up in space, or on the battlefield, we build the advanced technology that makes America stronger, faster, and safer. It’s who we are and what we do. It’s in our code. </t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>37257</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4426733766</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>XQYJD1Wcn8a5HPS6YzIHtg==</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/agentic-ai-engineer-%E2%80%94-healthcare-ai-at-deloitte-4426733766?position=10&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=XQYJD1Wcn8a5HPS6YzIHtg%3D%3D</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Agentic AI Engineer — Healthcare AI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deloitte?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C560BAQGNtpblgQpJoQ/company-logo_100_100/company-logo_100_100/0/1662120928214/deloitte_logo?e=2147483647&amp;v=beta&amp;t=OSF8M5LreT0Sf2F-JcNk6XMT0ArCuPfDmRR-knCC4HY</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>San Jose, CA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Three hundred fifty million Americans rely on a healthcare system whose decision-making has become slow, costly, and adversarial - care delayed by prior authorization and paperwork, claims that misfire, clinical decisions made without the right information at the right moment, and patients who struggle to navigate or afford the care they need. Deloitte has a new AI-first effort, backed by $1B in committed investment, building the reasoning models and agentic systems to rebuild how that system decides - across payers, providers, and life sciences, and for the patients they serve - so that care is faster, fairer, and far less wasteful. This is not AI applied at the margins. It is a ground-up rebuild of the decision-making machinery behind American healthcare, at national scale.&lt;br&gt;&lt;br&gt;This is an early, well-funded build. You will own agent systems end to end - from architecture through production - and your work ships into live clinical and operational settings within your first months, not into a lab.&lt;br&gt;&lt;br&gt;As an Agentic AI Engineer, you will design, build, and operationalize the LLM- and SLM-powered systems behind real healthcare decisioning - the reasoning, orchestration, retrieval, memory, and control layers that let intelligent agents operate reliably across the hardest decisions in the industry: clinical reasoning, prior authorization and claims integrity, care navigation, and the operational workflows that run across payers, providers, and life sciences. This is not a prompt-only role. We are looking for builders who think deeply about system behavior, grounding, and reliability where a wrong action has real consequences for patients and the clinicians who serve them.&lt;br&gt;&lt;br&gt;You do not need a healthcare background. We pair every engineer with clinical and domain experts and teach you the domain - you bring the agentic engineering depth.&lt;br&gt;&lt;br&gt;We hire on demonstrated depth, not years - the level you join at is determined through our interview process, based on the depth and judgment you demonstrate, not your years in a title.&lt;br&gt;&lt;br&gt;Work you'll do&lt;br&gt;&lt;br&gt;Agent architecture &amp;amp; orchestration&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Design and implement agentic systems capable of multi-step reasoning, planning, tool use, and workflow execution against complex, regulated operational processes.&lt;/li&gt;&lt;li&gt; Build stateful workflows using frameworks such as LangGraph and LangChain - including branching, retries, self-correction, human-in-the-loop checkpoints, and reusable orchestration patterns.&lt;/li&gt;&lt;li&gt; Engineer for long-horizon reliability - multi-step task completion, recovery from compounding errors, planning under uncertainty, and robust tool use when individual steps fail.&lt;/li&gt;&lt;li&gt; Build the reasoning behind regulated decisions - policy- and criteria-grounded outputs, structured proposer/critic/judge-style review, and auditable rationales for high-stakes decisions across the industry, from clinical review and prior authorization to claims integrity and care management.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Retrieval, grounding &amp;amp; context engineering&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Develop end-to-end Retrieval-Augmented Generation (RAG) pipelines: ingestion, chunking, embeddings, vector and hybrid retrieval, reranking, contextual compression, and grounding strategies.&lt;/li&gt;&lt;li&gt; Engineer memory and context management - conversational state, persistent memory, retrieval-aware context assembly, and token-efficient context selection.&lt;/li&gt;&lt;li&gt; Apply modern context-delivery patterns (e.g., MCP-style tool/context interfaces) so agents access the right information at the right time.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Reliability, evaluation &amp;amp; safety&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Implement observability and tracing for prompts, tool calls, retrieval quality, agent traces, failures, drift, latency, and production behavior.&lt;/li&gt;&lt;li&gt; Apply guardrails, safety controls, and failure-handling to reduce hallucinations and unsafe actions.&lt;/li&gt;&lt;li&gt; Evaluate agents at the trajectory and task level - multi-step task success, failure-mode and regression analysis, and sandboxed test environments - alongside retrieval- and generation-quality metrics, automated checks, and human review.&lt;/li&gt;&lt;li&gt; Engineer healthcare-grade safety - deployment eval gates, human-oversight and escalation models, auditability and traceability for regulated decisions, and PHI/HIPAA-aware data handling.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Integration &amp;amp; production craft&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Build integrations with internal and external tools, APIs, enterprise systems, databases, and model providers so agents operate safely within real business workflows.&lt;/li&gt;&lt;li&gt; Deliver production-quality code with strong practices in testing, CI/CD, logging, versioning, and documentation; make architecture decisions that balance quality, safety, latency, cost, and model risk.&lt;/li&gt;&lt;li&gt; Partner with our modeling and post-training engineers to improve model behavior for tool use, grounding, and long-horizon reasoning - through evaluation-driven feedback and, where it helps, fine-tuned or reasoning-optimized models.&lt;/li&gt;&lt;li&gt; Translate ambiguous, high-complexity operational processes into robust system logic and reusable AI patterns; stay current with advances in agentic systems and translate research into practical engineering decisions.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;The team&lt;br&gt;&lt;br&gt;Deloitte brings together AI researchers, modeling and platform engineers, architects, clinical and domain specialists, and product leaders to build, deploy, and operate verticalized AI systems across software, data, models, and cloud infrastructure - engineered for one of the most complex operating environments in the world. The work spans the healthcare industry - payers, providers, and life sciences - and involves genuinely hard reasoning problems, nuanced operational workflows, and a high bar for reliability, with little tolerance for shallow or unreliable outputs. We pair frontier AI research with production-grade engineering, and we ship into real clinical and operational settings rather than leaving models in the lab.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Required Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Bachelor's degree in Computer Science, Engineering, Data Science, Computational Linguistics, or a related field.&lt;/li&gt;&lt;li&gt; Demonstrated depth building and shipping production agentic systems - this is your primary craft, not a recent exploration. We weigh shipped systems, research, model releases, and open source over years in a title; expect strong software/ML fundamentals plus substantial, recent hands-on agentic work.&lt;/li&gt;&lt;li&gt; Strong, hands-on experience building production agent systems with modern orchestration - LangGraph/LangChain or equivalent, including custom orchestration.&lt;/li&gt;&lt;li&gt; Experience designing and optimizing end-to-end RAG systems: indexing, retrieval, reranking, grounding, and evaluation.&lt;/li&gt;&lt;li&gt; Strong understanding of memory and context management, including context windows, retrieval-driven context assembly, persistent memory, and high-signal context selection.&lt;/li&gt;&lt;li&gt; Deep, practical understanding of LLM behavior - strengths, limitations, hallucination risks, reasoning constraints, and latency/cost trade-offs - and the evaluation methods used to measure them.&lt;/li&gt;&lt;li&gt; Experience evaluating and debugging agent behavior - task-success and trajectory analysis, not just output quality.&lt;/li&gt;&lt;li&gt; Strong Python engineering skills and modern software practices: testing, CI/CD, version control, and API integration; experience implementing observability, tracing, and debugging for LLM-based systems in production.&lt;/li&gt;&lt;li&gt; Hands-on experience with at least one frontier model platform (e.g., Anthropic, Google, OpenAI) and/or open-weight/self-hosted models (e.g., Llama via vLLM), including production tool use and agent capabilities.&lt;/li&gt;&lt;li&gt; Ability to travel 0-50%, on average, based on the work you do and the clients and industries/sectors you serve.&lt;/li&gt;&lt;li&gt; Limited immigration sponsorship may be available.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Preferred Qualifications&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt; Experience with multi-agent systems and agent collaboration patterns.&lt;/li&gt;&lt;li&gt; Familiarity with vector databases and retrieval infrastructure such as Pinecone, Weaviate, or Milvus.&lt;/li&gt;&lt;li&gt; Exposure to model adaptation and fine-tuning techniques such as LoRA or QLoRA.&lt;/li&gt;&lt;li&gt; Understanding of traditional NLP concepts: tokenization, semantic similarity, entity extraction, summarization, and transformer fundamentals.&lt;/li&gt;&lt;li&gt; Experience operating in highly regulated, high-stakes, or operationally complex environments; healthcare exposure - clinical, payer, or life-sciences workflows, or standards such as FHIR - is a plus, not a requirement.&lt;/li&gt;&lt;li&gt; Demonstrated habit of staying current with AI research, benchmarks, and emerging engineering patterns.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Compensation&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Base salary is benchmarked to leading technology companies rather than traditional consulting scales, and the role carries a substantial performance-based incentive opportunity designed to grow with the value you help create - startup-style upside, with the backing of a committed, well-capitalized platform. The estimated base salary range is $110,700-$372,900 (not adjusted for geographic differential); actual base pay depends on your skills, experience, and level, and you may also be eligible for a discretionary annual incentive based on individual and organizational performance.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Three hundred fifty million Americans rely on a healthcare system whose decision-making has become slow, costly, and adversarial - care delayed by prior authorization and paperwork, claims that misfire, clinical decisions made without the right information at the right moment, and patients who struggle to navigate or afford the care they need. Deloitte has a new AI-first effort, backed by $1B in committed investment, building the reasoning models and agentic systems to rebuild how that system decides - across payers, providers, and life sciences, and for the patients they serve - so that care is faster, fairer, and far less wasteful. This is not AI applied at the margins. It is a ground-up rebuild of the decision-making machinery behind American healthcare, at national scale.
+This is an early, well-funded build. You will own agent systems end to end - from architecture through production - and your work ships into live clinical and operational settings within your first months, not into a lab.
+As an Agentic AI Engineer, you will design, build, and operationalize the LLM- and SLM-powered systems behind real healthcare decisioning - the reasoning, orchestration, retrieval, memory, and control layers that let intelligent agents operate reliably across the hardest decisions in the industry: clinical reasoning, prior authorization and claims integrity, care navigation, and the operational workflows that run across payers, providers, and life sciences. This is not a prompt-only role. We are looking for builders who think deeply about system behavior, grounding, and reliability where a wrong action has real consequences for patients and the clinicians who serve them.
+You do not need a healthcare background. We pair every engineer with clinical and domain experts and teach you the domain - you bring the agentic engineering depth.
+We hire on demonstrated depth, not years - the level you join at is determined through our interview process, based on the depth and judgment you demonstrate, not your years in a title.
+Work you'll do
+Agent architecture &amp;amp; orchestration
+-  Design and implement agentic systems capable of multi-step reasoning, planning, tool use, and workflow execution against complex, regulated operational processes.
+-  Build stateful workflows using frameworks such as LangGraph and LangChain - including branching, retries, self-correction, human-in-the-loop checkpoints, and reusable orchestration patterns.
+-  Engineer for long-horizon reliability - multi-step task completion, recovery from compounding errors, planning under uncertainty, and robust tool use when individual steps fail.
+-  Build the reasoning behind regulated decisions - policy- and criteria-grounded outputs, structured proposer/critic/judge-style review, and auditable rationales for high-stakes decisions across the industry, from clinical review and prior authorization to claims integrity and care management.
+Retrieval, grounding &amp;amp; context engineering
+-  Develop end-to-end Retrieval-Augmented Generation (RAG) pipelines: ingestion, chunking, embeddings, vector and hybrid retrieval, reranking, contextual compression, and grounding strategies.
+-  Engineer memory and context management - conversational state, persistent memory, retrieval-aware context assembly, and token-efficient context selection.
+-  Apply modern context-delivery patterns (e.g., MCP-style tool/context interfaces) so agents access the right information at the right time.
+Reliability, evaluation &amp;amp; safety
+-  Implement observability and tracing for prompts, tool calls, retrieval quality, agent traces, failures, drift, latency, and production behavior.
+-  Apply guardrails, safety controls, and failure-handling to reduce hallucinations and unsafe actions.
+-  Evaluate agents at the trajectory and task level - multi-step task success, failure-mode and regression analysis, and sandboxed test environments - alongside retrieval- and generation-quality metrics, automated checks, and human review.
+-  Engineer healthcare-grade safety - deployment eval gates, human-oversight and escalation models, auditability and traceability for regulated decisions, and PHI/HIPAA-aware data handling.
+Integration &amp;amp; production craft
+-  Build integrations with internal and external tools, APIs, enterprise systems, databases, and model providers so agents operate safely within real business workflows.
+-  Deliver production-quality code with strong practices in testing, CI/CD, logging, versioning, and documentation; make architecture decisions that balance quality, safety, latency, cost, and model risk.
+-  Partner with our modeling and post-training engineers to improve model behavior for tool use, grounding, and long-horizon reasoning - through evaluation-driven feedback and, where it helps, fine-tuned or reasoning-optimized models.
+-  Translate ambiguous, high-complexity operational processes into robust system logic and reusable AI patterns; stay current with advances in agentic systems and translate research into practical engineering decisions.
+The team
+Deloitte brings together AI researchers, modeling and platform engineers, architects, clinical and domain specialists, and product leaders to build, deploy, and operate verticalized AI systems across software, data, models, and cloud infrastructure - engineered for one of the most complex operating environments in the world. The work spans the healthcare industry - payers, providers, and life sciences - and involves genuinely hard reasoning problems, nuanced operational workflows, and a high bar for reliability, with little tolerance for shallow or unreliable outputs. We pair frontier AI research with production-grade engineering, and we ship into real clinical and operational settings rather than leaving models in the lab.
+Required Qualifications
+-  Bachelor's degree in Computer Science, Engineering, Data Science, Computational Linguistics, or a related field.
+-  Demonstrated depth building and shipping production agentic systems - this is your primary craft, not a recent exploration. We weigh shipped systems, research, model releases, and open source over years in a title; expect strong software/ML fundamentals plus substantial, recent hands-on agentic work.
+-  Strong, hands-on experience building production agent systems with modern orchestration - LangGraph/LangChain or equivalent, including custom orchestration.
+-  Experience designing and optimizing end-to-end RAG systems: indexing, retrieval, reranking, grounding, and evaluation.
+-  Strong understanding of memory and context management, including context windows, retrieval-driven context assembly, persistent memory, and high-signal context selection.
+-  Deep, practical understanding of LLM behavior - strengths, limitations, hallucination risks, reasoning constraints, and latency/cost trade-offs - and the evaluation methods used to measure them.
+-  Experience evaluating and debugging agent behavior - task-success and trajectory analysis, not just output quality.
+-  Strong Python engineering skills and modern software practices: testing, CI/CD, version control, and API integration; experience implementing observability, tracing, and debugging for LLM-based systems in production.
+-  Hands-on experience with at least one frontier model platform (e.g., Anthropic, Google, OpenAI) and/or open-weight/self-hosted models (e.g., Llama via vLLM), including production tool use and agent capabilities.
+-  Ability to travel 0-50%, on average, based on the work you do and the clients and industries/sectors you serve.
+-  Limited immigration sponsorship may be available.
+Preferred Qualifications
+-  Experience with multi-agent systems and agent collaboration patterns.
+-  Familiarity with vector databases and retrieval infrastructure such as Pinecone, Weaviate, or Milvus.
+-  Exposure to model adaptation and fine-tuning techniques such as LoRA or QLoRA.
+-  Understanding of traditional NLP concepts: tokenization, semantic similarity, entity extraction, summarization, and transformer fundamentals.
+-  Experience operating in highly regulated, high-stakes, or operationally complex environments; healthcare exposure - clinical, payer, or life-sciences workflows, or standards such as FHIR - is a plus, not a requirement.
+-  Demonstrated habit of staying current with AI research, benchmarks, and emerging engineering patterns.
+Compensation
+Base salary is benchmarked to leading technology companies rather than traditional consulting scales, and the role carries a substantial performance-based incentive opportunity designed to grow with the value you help create - startup-style upside, with the backing of a committed, well-capitalized platform. The estimated base salary range is $110,700-$372,900 (not adjusted for geographic differential); actual base pay depends on your skills, experience, and level, and you may also be eligible for a discretionary annual incentive based on individual and organizational performance.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Accounting, IT Services and IT Consulting, and Business Consulting and Services</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': 'Worldwide', 'addressLocality': 'Worldwide', 'addressCountry': 'OO'}</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>http://www.deloitte.com/</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Together makes progress</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Deloitte drives progress. Our firms around the world help clients become leaders wherever they choose to compete. Deloitte invests in outstanding people of diverse talents and backgrounds and empowers them to achieve more than they could elsewhere. Our work combines advice with action and integrity. We believe that when our clients and society are stronger, so are we. 
+Deloitte refers to one or more of Deloitte Touche Tohmatsu Limited (“DTTL”), its global network of member firms, and their related entities. DTTL (also referred to as “Deloitte Global”) and each of its member firms are legally separate and independent entities. DTTL does not provide services to clients. Please see www.deloitte.com/about to learn more.
+The content on this page contains general information only, and none of Deloitte Touche Tohmatsu Limited, its member firms, or their related entities (collectively the “Deloitte Network”) is, by means of this publication, rendering professional advice or services. Before making any decision or taking any action that may affect your finances or your business, you should consult a qualified professional adviser. No entity in the Deloitte Network shall be responsible for any loss whatsoever sustained by any person who relies on content from this page.</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>532502</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4453270200</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ff5GK9IMT2kdjYzk9ubFug==</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-tata-consultancy-services-4453270200?position=6&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=Ff5GK9IMT2kdjYzk9ubFug%3D%3D</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/tata-consultancy-services?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D0BAQGsGR9p4ikS5w/company-logo_100_100/company-logo_100_100/0/1708946550425/tata_consultancy_services_logo?e=2147483647&amp;v=beta&amp;t=P-PkUMh7Ks1GQY0_l7GhzQiwfyLfQpvKWwX8Tq18Yc4</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Job Description&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Must Have Technical/Functional Skills&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Python (Expert level)&lt;/li&gt;&lt;li&gt; Machine Learning &amp;amp; Model Training&lt;/li&gt;&lt;li&gt;Training, evaluation, fine tuning&lt;/li&gt;&lt;li&gt;Tagging and labeling workflows&lt;/li&gt;&lt;li&gt; Generative AI &amp;amp; LLMs&lt;/li&gt;&lt;li&gt;Prompt engineering for LLM-based applications&lt;/li&gt;&lt;li&gt; Document Processing&lt;/li&gt;&lt;li&gt;Document extraction, parsing, and chunking&lt;/li&gt;&lt;li&gt;Handling structured &amp;amp; unstructured data&lt;/li&gt;&lt;li&gt; Embeddings &amp;amp; Vector Search&lt;/li&gt;&lt;li&gt;Embedding generation&lt;/li&gt;&lt;li&gt;Vector database integration&lt;/li&gt;&lt;li&gt; Databases&lt;/li&gt;&lt;li&gt;Vector Databases&lt;/li&gt;&lt;li&gt;MongoDB&lt;/li&gt;&lt;li&gt; Production-grade ML Engineering&lt;/li&gt;&lt;li&gt;Scalable, production-ready ML/GenAI solutions&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Roles &amp;amp; Responsibilities&lt;br&gt;&lt;br&gt;This role is for a hands-on AI/ML Engineer who will design, build, and deploy production‑grade Machine Learning and Generative AI solutions. The candidate must have strong Python expertise and practical experience taking ML and GenAI use cases from development to deployment.&lt;br&gt;&lt;br&gt;The role focuses heavily on LLM-based applications, including prompt engineering, document processing pipelines, and embedding-based search solutions. The engineer will work with both structured and unstructured data, building pipelines for document extraction, parsing, and chunking, and integrating ML models with Vector Databases and MongoDB.&lt;br&gt;&lt;br&gt;An ideal candidate is someone who understands end-to-end ML workflows—from data preparation, tagging, and labeling, through model training, evaluation, and fine-tuning—while ensuring solutions are scalable, high quality, and production ready.&lt;br&gt;&lt;br&gt;For recruiter to interpret accurately&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Not a pure data analyst → this is an engineering-focused ML/GenAI role&lt;/li&gt;&lt;li&gt; Not theoretical AI → requires real-world deployment experience&lt;/li&gt;&lt;li&gt; Strong fit for candidates with backgrounds in:&lt;/li&gt;&lt;li&gt;ML Engineering&lt;/li&gt;&lt;li&gt;Applied Data Science&lt;/li&gt;&lt;li&gt;GenAI / LLM application development&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Key Responsibilities&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Design and implement AI/ML solutions using Python and modern ML frameworks&lt;/li&gt;&lt;li&gt; Develop and optimize Prompt Engineering strategies for LLM-based systems&lt;/li&gt;&lt;li&gt; Build and deploy Retrieval-Augmented Generation (RAG) pipelines&lt;/li&gt;&lt;li&gt; Integrate LLMs via APIs (Azure OpenAI preferred) into enterprise applications&lt;/li&gt;&lt;li&gt; Develop and orchestrate Agent ic AI workflows with tool/function calling&lt;/li&gt;&lt;li&gt; Implement vector search solutions using Vector Databases&lt;/li&gt;&lt;li&gt; Ensure CI/CD integration and cloud deployment (Azure preferred)&lt;/li&gt;&lt;li&gt; Establish observability, monitoring, and evaluation frameworks for AI systems&lt;/li&gt;&lt;li&gt; Collaborate with cross-functional teams to deliver production-ready AI features&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Generic Managerial Skills, If any&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt; Ability to explain complex ML / GenAI concepts to non‑technical stakeholders and collaborate effectively with cross‑functional teams.&lt;/li&gt;&lt;li&gt; Strong analytical thinking to break down ambiguous business problems into workable ML or GenAI solutions.&lt;/li&gt;&lt;li&gt; Takes end‑to‑end responsibility for solutions—from design to production readiness—without constant supervision.&lt;/li&gt;&lt;li&gt; Works well with data engineers, product owners, and platform teams to deliver integrated, scalable solutions.&lt;/li&gt;&lt;li&gt; Actively keeps up with evolving ML, LLM, and GenAI technologies and improves skills proactively.&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;Salary Range: $140,000 -$165,000 year&lt;br&gt;&lt;br&gt;&lt;strong&gt;TCS Employee Benefits Summary&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Discretionary Annual Incentive.&lt;br&gt;&lt;br&gt;Comprehensive Medical Coverage: Medical &amp;amp; Health, Dental &amp;amp; Vision, Disability Planning &amp;amp; Insurance, Pet Insurance Plans.&lt;br&gt;&lt;br&gt;Family Support: Maternal &amp;amp; Parental Leaves.&lt;br&gt;&lt;br&gt;Insurance Options: Auto &amp;amp; Home Insurance, Identity Theft Protection.&lt;br&gt;&lt;br&gt;Convenience &amp;amp; Professional Growth: Commuter Benefits &amp; Certification &amp; amp; Training Reimbursement.&lt;br&gt;&lt;br&gt;Time Off: Vacation, Time Off, Sick Leave &amp;amp; Holidays.&lt;br&gt;&lt;br&gt;Legal &amp;amp; Financial Assistance: Legal Assistance, 401K Plan, Performance Bonus, College Fund, Student Loan Refinancing.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Qualifications: &lt;/strong&gt;BACHELOR OF COMPUTER SCIENCE&lt;br&gt;&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job Description
+Must Have Technical/Functional Skills
+-  Python (Expert level)
+-  Machine Learning &amp;amp; Model Training
+- Training, evaluation, fine tuning
+- Tagging and labeling workflows
+-  Generative AI &amp;amp; LLMs
+- Prompt engineering for LLM-based applications
+-  Document Processing
+- Document extraction, parsing, and chunking
+- Handling structured &amp;amp; unstructured data
+-  Embeddings &amp;amp; Vector Search
+- Embedding generation
+- Vector database integration
+-  Databases
+- Vector Databases
+- MongoDB
+-  Production-grade ML Engineering
+- Scalable, production-ready ML/GenAI solutions
+Roles &amp;amp; Responsibilities
+This role is for a hands-on AI/ML Engineer who will design, build, and deploy production‑grade Machine Learning and Generative AI solutions. The candidate must have strong Python expertise and practical experience taking ML and GenAI use cases from development to deployment.
+The role focuses heavily on LLM-based applications, including prompt engineering, document processing pipelines, and embedding-based search solutions. The engineer will work with both structured and unstructured data, building pipelines for document extraction, parsing, and chunking, and integrating ML models with Vector Databases and MongoDB.
+An ideal candidate is someone who understands end-to-end ML workflows—from data preparation, tagging, and labeling, through model training, evaluation, and fine-tuning—while ensuring solutions are scalable, high quality, and production ready.
+For recruiter to interpret accurately
+-  Not a pure data analyst → this is an engineering-focused ML/GenAI role
+-  Not theoretical AI → requires real-world deployment experience
+-  Strong fit for candidates with backgrounds in:
+- ML Engineering
+- Applied Data Science
+- GenAI / LLM application development
+Key Responsibilities
+-  Design and implement AI/ML solutions using Python and modern ML frameworks
+-  Develop and optimize Prompt Engineering strategies for LLM-based systems
+-  Build and deploy Retrieval-Augmented Generation (RAG) pipelines
+-  Integrate LLMs via APIs (Azure OpenAI preferred) into enterprise applications
+-  Develop and orchestrate Agent ic AI workflows with tool/function calling
+-  Implement vector search solutions using Vector Databases
+-  Ensure CI/CD integration and cloud deployment (Azure preferred)
+-  Establish observability, monitoring, and evaluation frameworks for AI systems
+-  Collaborate with cross-functional teams to deliver production-ready AI features
+Generic Managerial Skills, If any
+-  Ability to explain complex ML / GenAI concepts to non‑technical stakeholders and collaborate effectively with cross‑functional teams.
+-  Strong analytical thinking to break down ambiguous business problems into workable ML or GenAI solutions.
+-  Takes end‑to‑end responsibility for solutions—from design to production readiness—without constant supervision.
+-  Works well with data engineers, product owners, and platform teams to deliver integrated, scalable solutions.
+-  Actively keeps up with evolving ML, LLM, and GenAI technologies and improves skills proactively.
+Salary Range: $140,000 -$165,000 year
+TCS Employee Benefits Summary
+Discretionary Annual Incentive.
+Comprehensive Medical Coverage: Medical &amp;amp; Health, Dental &amp;amp; Vision, Disability Planning &amp;amp; Insurance, Pet Insurance Plans.
+Family Support: Maternal &amp;amp; Parental Leaves.
+Insurance Options: Auto &amp;amp; Home Insurance, Identity Theft Protection.
+Convenience &amp;amp; Professional Growth: Commuter Benefits &amp; Certification &amp; amp; Training Reimbursement.
+Time Off: Vacation, Time Off, Sick Leave &amp;amp; Holidays.
+Legal &amp;amp; Financial Assistance: Legal Assistance, 401K Plan, Performance Bonus, College Fund, Student Loan Refinancing.
+Qualifications: BACHELOR OF COMPUTER SCIENCE
+</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>IT Services and IT Consulting</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': 'Tata Consultancy Services', 'addressLocality': 'Mumbai', 'addressRegion': 'Maharashtra', 'postalCode': '400001', 'addressCountry': 'IN'}</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>https://www.tcs.com/</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS) is the technology partner of choice for industry leading organizations worldwide. Since its inception in 1968, TCS has upheld the highest standards of innovation, engineering excellence, and customer service. 
+It has set an aspiration to become the world's largest AI-led technology services company and is enabling its clients to transform themselves across the full AI stack, from infrastructure to intelligence. 
+Rooted in the heritage of the Tata Group, TCS is focused on creating long term value for its clients, its investors, its employees, and the community at large. With a highly skilled workforce spread across 55 countries and 202 service delivery centers across the world, the company has been recognized as a top employer in six continents. With the ability to rapidly apply and scale new technologies, the company has built long term partnerships with its clients – helping them emerge as perpetually adaptive enterprises. Many of these relationships have endured into decades and navigated every technology cycle, from mainframes in the 1970s to artificial intelligence today. 
+TCS sponsors 14 of the world’s most prestigious marathons and endurance events, including the TCS New York City Marathon, TCS London Marathon and TCS Sydney Marathon with a focus on promoting health, sustainability, and community empowerment. 
+Caution against fraudulent job offers: TCS doesn’t charge any fee throughout the recruitment process. Refer here: https://www.tcs.com/careers/india/recruitment-fraud-alert</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>724977</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4454057834</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4BwzntIQuBpekghj0K1opA==</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-harnham-4454057834?position=5&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=4BwzntIQuBpekghj0K1opA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Harnham</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/harnham?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFDh4hZFsU8qA/company-logo_100_100/company-logo_100_100/0/1732180104917/harnham_logo?e=2147483647&amp;v=beta&amp;t=2K2PZUjKIx7QPtNOXOgU2XOjaiYyj1Gnd8g_8LaDJhc</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Title&lt;/strong&gt;: AI/ML Engineer (All Levels)&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location&lt;/strong&gt;: Bay Area (Hybrid)&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Compensation&lt;/strong&gt;: Up to $350,000 + Equity&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;We're partnered with a well-funded, high-growth Series B startup building the next generation of AI-native data infrastructure for Fortune 500 enterprises. With 3.5x revenue growth in FY'24 and 160% net revenue retention, they're scaling fast and investing heavily in the AI engineering team that powers their core product.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;This is a high-impact role where you'll own the intelligence layer of the platform, making real architectural decisions around agent design, model selection, and evaluation strategy. Everything you build ships directly to customers; this is not a POC or internal tooling team.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What You'll Do&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Architect multi-step AI agents end-to-end, covering problem decomposition, context retrieval, error recovery, and output quality&lt;/li&gt;&lt;li&gt;Own RAG pipelines, vector and graph-based retrieval systems, and knowledge representations that let agents reason accurately over complex enterprise data&lt;/li&gt;&lt;li&gt;Build the AI layer behind the platform's core code generation capability, from prompt design and model selection through to fine-tuning and output validation&lt;/li&gt;&lt;li&gt;Make production AI work at scale, balancing latency, throughput, and observability, and knowing when to optimize a model versus restructure a system&lt;/li&gt;&lt;li&gt;Think in failure modes and evaluation strategy, not capability demos, and own the improvement loop&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Requirements&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;4-6+ years of software engineering experience with meaningful AI/ML depth&lt;/li&gt;&lt;li&gt;Proven experience building and shipping AI agents or coding agents in production&lt;/li&gt;&lt;li&gt;Strong Python skills with hands-on experience across RAG, vector databases, and knowledge graphs&lt;/li&gt;&lt;li&gt;Experience with LLM APIs, prompt engineering, fine-tuning, and structured outputs in production&lt;/li&gt;&lt;li&gt;Familiarity with AWS and Kubernetes for production AI deployment&lt;/li&gt;&lt;li&gt;Experience with data platforms such as Databricks, Snowflake, BigQuery, or Spark is a strong bonus&lt;/li&gt;&lt;li&gt;Scale or Go experience is a bonus&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;If you're a builder who thinks in failure modes, owns what you ship, and thrives in environments where last year's best practice is already obsolete, this is a rare opportunity to have direct leverage on a product used by some of the world's largest enterprises.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+Title: AI/ML Engineer (All Levels)
+Location: Bay Area (Hybrid)
+Compensation: Up to $350,000 + Equity
+We're partnered with a well-funded, high-growth Series B startup building the next generation of AI-native data infrastructure for Fortune 500 enterprises. With 3.5x revenue growth in FY'24 and 160% net revenue retention, they're scaling fast and investing heavily in the AI engineering team that powers their core product.
+This is a high-impact role where you'll own the intelligence layer of the platform, making real architectural decisions around agent design, model selection, and evaluation strategy. Everything you build ships directly to customers; this is not a POC or internal tooling team.
+What You'll Do
+- Architect multi-step AI agents end-to-end, covering problem decomposition, context retrieval, error recovery, and output quality
+- Own RAG pipelines, vector and graph-based retrieval systems, and knowledge representations that let agents reason accurately over complex enterprise data
+- Build the AI layer behind the platform's core code generation capability, from prompt design and model selection through to fine-tuning and output validation
+- Make production AI work at scale, balancing latency, throughput, and observability, and knowing when to optimize a model versus restructure a system
+- Think in failure modes and evaluation strategy, not capability demos, and own the improvement loop
+Requirements
+- 4-6+ years of software engineering experience with meaningful AI/ML depth
+- Proven experience building and shipping AI agents or coding agents in production
+- Strong Python skills with hands-on experience across RAG, vector databases, and knowledge graphs
+- Experience with LLM APIs, prompt engineering, fine-tuning, and structured outputs in production
+- Familiarity with AWS and Kubernetes for production AI deployment
+- Experience with data platforms such as Databricks, Snowflake, BigQuery, or Spark is a strong bonus
+- Scale or Go experience is a bonus
+If you're a builder who thinks in failure modes, owns what you ship, and thrives in environments where last year's best practice is already obsolete, this is a rare opportunity to have direct leverage on a product used by some of the world's largest enterprises.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Software Development</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': 'Melbury House, 51 Wimbledon Hill Road', 'addressLocality': 'Wimbledon', 'addressRegion': 'London', 'postalCode': 'SW19 7QW', 'addressCountry': 'GB'}</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>http://www.harnham.com</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harnham is the global leader in Data and AI talent solutions. </t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Harnham provides specialist Data and AI recruitment and staffing services, along with bespoke training solutions, across multiple industry verticals, operating in the UK, the USA and EU - contact us today to discuss your requirements: info@harnham.com 
+Our recruitment and talent teams cover all aspects of the data and AI pipeline, from collection to consumption, across multiple data roles and functions. 
+Whether you need full-time staff, contract talent, specialized training, Data-qualified graduates, or C-suite executives, Harnham Group is equipped to fulfill all your data talent requirements.
+Our five core services:
+* ATD - Rockborne – our graduate development arm – deploys expertly trained data consultants, who have gone through an intensive 12-week data training programme. After two years in the scheme, your consultant could become a 
+* Contract / C2C / Freelance: Whether you're addressing a talent shortage, augmenting a project team, or encountering resource gaps, our specialist consultants offer bespoke interim talent solutions to address your unique challenges and drive success.
+* Full-Time / Direct Hiring: From early career professionals to senior management, our comprehensive services enable you to unearth outstanding data talent across various specializations, ensuring your organization thrives in the data-driven era.
+* Executive Search: With our dedicated executive search team and an extensive network encompassing the director to C-suite level, we assist both global corporations and ambitious startups in securing top-tier leadership talent to accomplish their goals.
+* GenAI, Prompt, LLM Training: Elevate your team's data expertise with our all-encompassing training programs covering essential tools and technologies such as Python, SQL, Machine Learning, LLM’s and AI. Highly bespoke, customised to your team learning requirements and budgets.</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>George Ethell</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Helping Founders &amp; AI Leaders hire top Research, Machine Learning, and Software Engineering talent across World Models, AIGC, Multimodal AI, Agents…</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>https://static.licdn.com/aero-v1/sc/h/9c8pery4andzj6ohjkjp54ma2</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgeethell</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4452934313</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>qoHAclyiBouGDbBgN98OcQ==</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-llm-agentic-systems-at-auxo-talent-4452934313?position=4&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=qoHAclyiBouGDbBgN98OcQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer (LLM / Agentic Systems)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Auxo Talent</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/auxotalent?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D0BAQFd1BEyLRUXwg/company-logo_100_100/company-logo_100_100/0/1726121227211/auxotalent_logo?e=2147483647&amp;v=beta&amp;t=RgLpMT_wYZuTV1ghbvLv31T4i0TPZWmrHIIQEXVh1NI</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;AI Engineer (LLM / Agentic Systems)&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Bay Area, California | Hybrid | $140,000 to $160,000 + equity&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;A well-funded early stage company is applying AI to the operational side of critical infrastructure. Their platform pulls live data from sensor and control networks across large facilities, then uses agentic AI to spot problems, connect related events and give operators recommendations in real time. It is a genuinely hard technical problem in a market that is growing quickly.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;This suits an engineer with roughly three to six years behind them who has already shipped LLM-powered systems into production and wants more ownership than a large team allows. You would be joining a small engineering group and working end to end, from data pipelines and model integration through to agentic orchestration, evaluation and production support.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;It is not a research role, but research thinking matters. You will be expected to keep up with the field, bring ideas forward and then build them properly.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What you will work on&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Multi-agent orchestration and LLM-driven triage workflows&lt;/li&gt;&lt;li&gt;Time-series modelling for anomaly detection and failure prediction on multivariate data&lt;/li&gt;&lt;li&gt;Retrieval-augmented knowledge systems for operations teams&lt;/li&gt;&lt;li&gt;Data and ML pipelines: ingestion, ETL and dataset construction&lt;/li&gt;&lt;li&gt;Fine-tuning and post-training of language models for operational use cases&lt;/li&gt;&lt;li&gt;Evaluation frameworks, AI observability and production benchmarking&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What you will need&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Degree in Computer Science, Machine Learning, Mathematics or similar, or equivalent demonstrated experience&lt;/li&gt;&lt;li&gt;Around three years or more of professional AI/ML engineering experience&lt;/li&gt;&lt;li&gt;Strong Python, with solid fundamentals across testing, version control and CI/CD&lt;/li&gt;&lt;li&gt;Hands-on experience taking LLM APIs into production, not just prototypes&lt;/li&gt;&lt;li&gt;Familiarity with agentic concepts such as tool and function calling, and agent frameworks&lt;/li&gt;&lt;li&gt;Daily use of AI-assisted coding tools&lt;/li&gt;&lt;li&gt;Ability to read ML research and turn it into practical experiments&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Nice to have&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;LangGraph, LangChain or similar agent frameworks, MCP a plus&lt;/li&gt;&lt;li&gt;Time-series forecasting and anomaly prediction&lt;/li&gt;&lt;li&gt;Fine-tuning or post-training experience&lt;/li&gt;&lt;li&gt;PyTorch and model serving frameworks&lt;/li&gt;&lt;li&gt;Cloud ML platforms, GCP in particular&lt;/li&gt;&lt;li&gt;LLM evaluation and benchmarking, harness design&lt;/li&gt;&lt;li&gt;Exposure to industrial or building control systems&lt;/li&gt;&lt;li&gt;Background in DevOps, distributed systems or observability tooling&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;On offer&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;$140,000 to $160,000 base, stock options, full medical, dental and vision, 401(k) and paid time off.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>$140,000.00/yr - $160,000.00/yr</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+AI Engineer (LLM / Agentic Systems)
+Bay Area, California | Hybrid | $140,000 to $160,000 + equity
+A well-funded early stage company is applying AI to the operational side of critical infrastructure. Their platform pulls live data from sensor and control networks across large facilities, then uses agentic AI to spot problems, connect related events and give operators recommendations in real time. It is a genuinely hard technical problem in a market that is growing quickly.
+This suits an engineer with roughly three to six years behind them who has already shipped LLM-powered systems into production and wants more ownership than a large team allows. You would be joining a small engineering group and working end to end, from data pipelines and model integration through to agentic orchestration, evaluation and production support.
+It is not a research role, but research thinking matters. You will be expected to keep up with the field, bring ideas forward and then build them properly.
+What you will work on
+- Multi-agent orchestration and LLM-driven triage workflows
+- Time-series modelling for anomaly detection and failure prediction on multivariate data
+- Retrieval-augmented knowledge systems for operations teams
+- Data and ML pipelines: ingestion, ETL and dataset construction
+- Fine-tuning and post-training of language models for operational use cases
+- Evaluation frameworks, AI observability and production benchmarking
+What you will need
+- Degree in Computer Science, Machine Learning, Mathematics or similar, or equivalent demonstrated experience
+- Around three years or more of professional AI/ML engineering experience
+- Strong Python, with solid fundamentals across testing, version control and CI/CD
+- Hands-on experience taking LLM APIs into production, not just prototypes
+- Familiarity with agentic concepts such as tool and function calling, and agent frameworks
+- Daily use of AI-assisted coding tools
+- Ability to read ML research and turn it into practical experiments
+Nice to have
+- LangGraph, LangChain or similar agent frameworks, MCP a plus
+- Time-series forecasting and anomaly prediction
+- Fine-tuning or post-training experience
+- PyTorch and model serving frameworks
+- Cloud ML platforms, GCP in particular
+- LLM evaluation and benchmarking, harness design
+- Exposure to industrial or building control systems
+- Background in DevOps, distributed systems or observability tooling
+On offer
+$140,000 to $160,000 base, stock options, full medical, dental and vision, 401(k) and paid time off.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>IT Services and IT Consulting and Data Infrastructure and Analytics</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>http://www.auxotalent.com</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Auxo is a global STEMx workforce solutions partner, supporting the industries shaping the future of work. We bring together four specialist divisions across Technology, Advanced Engineering, Future Build and Frontier, connecting ambitious organisations with the talent and capability they need to grow.
+Our work spans permanent hiring, contract recruitment, executive search, global mobility, advisory services and complex workforce programmes delivered through Auxo XPO. This unified approach gives clients a single partner with deep expertise, wider reach and stronger delivery across fast changing markets.
+Auxo exists to help businesses stay competitive in a world where skills, industries and technologies evolve quickly. By combining specialist insight with global scale, we help clients build teams that drive progress. For candidates, we open doors to opportunities in the industries that will define tomorrow.
+Challenge. Growth. Tenacity. These values guide how we work and how we deliver for the people and organisations who trust us.
+The future, powered by talent.</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ethan Boon</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Headhunter | Physical AI | Building teams that build robots | Irish | Arsenal Supporter in Manchester</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E03AQHF_BaaRyQHNw/profile-displayphoto-shrink_400_400/B4EZVhGcC7GgAk-/0/1741090833998?e=2147483647&amp;v=beta&amp;t=W_SUFUWY-1VlSbEteeLD647I3E86TyzrnymebAnwXAI</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/ethan-boon</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4454092284</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rwjy3v4AiuPueetqlRJssA==</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-at-translucent-ai-4454092284?position=1&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=Rwjy3v4AiuPueetqlRJssA%3D%3D</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Translucent AI</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/translucentai?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4D0BAQFvaeCnyJlj3Q/company-logo_100_100/B4DZf1jNi_GYAQ-/0/1752171338278/translucentai_logo?e=2147483647&amp;v=beta&amp;t=m775Vd5YtG6VtIENnI4-FaRRYZsVEIxuc-SI6jq8T8w</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>&lt;strong&gt;Role Details&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Full-Time&lt;/li&gt;&lt;li&gt;Office Location - New York City (hybrid)&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Why Translucent&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Healthcare providers drive $2.5 trillion in medical expenditures annually — and operate on razor-thin 2–5% margins. Despite these stakes, the finance teams behind these organizations are buried in spreadsheets, manual data pulls, and disconnected systems, spending more time finding and cleaning data than actually using it to make decisions.&lt;br&gt;&lt;br&gt;Translucent is changing that. We're building the agentic AI platform designed exclusively for healthcare finance— giving every finance team, department, service line their own arsenal of AI Agents that run 24/7, understand their specific data, business logic, and workflows.&lt;br&gt;&lt;br&gt;Founded in 2024 and backed by GV, NEA, FPV, and Virtue, we've already been deployed by healthcare organizations managing over $5 billion in combined revenue. The product-market fit is real, the problem is massive, and we're just getting started. If you want to work at the intersection of AI and one of the most complex, consequential industries in the world, this is the place.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Role Overview&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We're looking for an AI Engineer to help build the agentic platform at the core of Translucent: the AI financial platform transforming how healthcare organizations make business decisions.&lt;br&gt;&lt;br&gt;You'll work hands-on across R&amp;amp;D and platform engineering — improving the underlying agent capabilities every team builds on, rather than configuring agents for a single customer. You'll standardize the tool surfaces new capabilities plug into, make the agent platform ready to integrate across products, and own the evals, context, and harness engineering that make it reliable enough for healthcare finance. You'll match the right agentic architecture to each use case, turn core capabilities into an ecosystem others build on, and own quality end-to-end.&lt;br&gt;&lt;br&gt;If you are energized by fast-paced environments, love sweating the details of production AI systems, partnering closely with product and design, and seeing your work in customers' hands quickly, you'll feel at home here.&lt;br&gt;&lt;br&gt;&lt;strong&gt;What You’ll Do&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Standardize tool and skill surfaces — define the contracts (MCP-style tool, connector, and skill interfaces) that let us add new capabilities continuously without destabilizing the platform as it grows&lt;/li&gt;&lt;li&gt;Make the agent platform integration-ready — build the connective tissue so agents, tools, context, and data compose cleanly across products, and match the right agentic architecture to each use case&lt;/li&gt;&lt;li&gt;Own evals and benchmarks — build production-grade eval harnesses, replay, and benchmarks for agentic AI, and gate releases on them; in healthcare finance, accuracy is non-negotiable&lt;/li&gt;&lt;li&gt;Lead context and harness engineering — establish best practices for grounding agents in each customer's business rules and data, and for the control loops that keep outputs reliable&lt;/li&gt;&lt;li&gt;Fine-tune and evaluate models — fine-tune in-house and open-source models, benchmark them against frontier baselines, and make the build-vs-buy calls on model, framework, and infra&lt;/li&gt;&lt;li&gt;Turn capabilities into an ecosystem — build reusable core capabilities that translate across features and products, and ship them end-to-end with product and design&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;What You Have&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;3+ years of software engineering experience, with meaningful production work in Python&lt;/li&gt;&lt;li&gt;Direct experience shipping LLM-powered or agentic systems in production — not just prototypes. You know where models fail and how to make them reliable&lt;/li&gt;&lt;li&gt;Hands-on experience with at least one modern agent framework (LangGraph, Google ADK, LlamaIndex, Claude Agent SDK, or equivalent), and a clear point of view on what to use vs. build&lt;/li&gt;&lt;li&gt;Production evals and benchmarking — you've built eval harnesses and benchmarks that gate real releases, not one-off spot checks&lt;/li&gt;&lt;li&gt;Context engineering — grounding agents through retrieval, context layers, and knowledge transfer so outputs match a specific org or user&lt;/li&gt;&lt;li&gt;Comfort with the data and retrieval layer — SQL, BigQuery or a comparable warehouse, embeddings, and vector search&lt;/li&gt;&lt;li&gt;A bias toward shipping — you take an ambiguous problem to a working V1 fast, then iterate&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Plus deep, demonstrable expertise in at least one (ideally two) of the following:&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Tool-surface and connector platform engineering — standardized tool/skill contracts (e.g., MCP) and connector ecosystems that scale without breaking&lt;/li&gt;&lt;li&gt;Harness and loop engineering — agent control loops, orchestration, and inference harnesses; right-sizing agent architecture per use case and keeping it reliable at scale&lt;/li&gt;&lt;li&gt;Open-source and in-house model fine-tuning — fine-tuning open models and benchmarking them against frontier baselines&lt;/li&gt;&lt;li&gt;Production context-layer engineering — systems that capture business rules and preferences and feed them to agents reliably&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Nice to Have&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Experience with healthcare finance, accounting, or other structured financial data — or genuine curiosity about it&lt;/li&gt;&lt;li&gt;Applied ML or model-evaluation research background&lt;/li&gt;&lt;li&gt;Open-source contributions to agent or LLM tooling&lt;/li&gt;&lt;li&gt;Experience designing tool-use APIs or developer-facing AI products&lt;/li&gt;&lt;li&gt;Familiarity with our stack: Vertex AI (Gemini, Claude on Vertex), GenKit, MCP, BigQuery&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Experience Level&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We're looking for engineers who own meaningful surface area and drive work forward independently. You'll bring sharp judgment on architecture and build-vs-buy trade-offs under ambiguity, a bias toward shipping a working V1 fast, and the craft to make agentic systems reliable enough for healthcare finance — not just demos.&lt;br&gt;&lt;br&gt;https://www.translucent.co/&lt;br&gt;&lt;br&gt;&lt;strong&gt;Base Salary&lt;/strong&gt;: $175,000-$275,000 USD + equity</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Role Details
+- Full-Time
+- Office Location - New York City (hybrid)
+Why Translucent
+Healthcare providers drive $2.5 trillion in medical expenditures annually — and operate on razor-thin 2–5% margins. Despite these stakes, the finance teams behind these organizations are buried in spreadsheets, manual data pulls, and disconnected systems, spending more time finding and cleaning data than actually using it to make decisions.
+Translucent is changing that. We're building the agentic AI platform designed exclusively for healthcare finance— giving every finance team, department, service line their own arsenal of AI Agents that run 24/7, understand their specific data, business logic, and workflows.
+Founded in 2024 and backed by GV, NEA, FPV, and Virtue, we've already been deployed by healthcare organizations managing over $5 billion in combined revenue. The product-market fit is real, the problem is massive, and we're just getting started. If you want to work at the intersection of AI and one of the most complex, consequential industries in the world, this is the place.
+Role Overview
+We're looking for an AI Engineer to help build the agentic platform at the core of Translucent: the AI financial platform transforming how healthcare organizations make business decisions.
+You'll work hands-on across R&amp;amp;D and platform engineering — improving the underlying agent capabilities every team builds on, rather than configuring agents for a single customer. You'll standardize the tool surfaces new capabilities plug into, make the agent platform ready to integrate across products, and own the evals, context, and harness engineering that make it reliable enough for healthcare finance. You'll match the right agentic architecture to each use case, turn core capabilities into an ecosystem others build on, and own quality end-to-end.
+If you are energized by fast-paced environments, love sweating the details of production AI systems, partnering closely with product and design, and seeing your work in customers' hands quickly, you'll feel at home here.
+What You’ll Do
+- Standardize tool and skill surfaces — define the contracts (MCP-style tool, connector, and skill interfaces) that let us add new capabilities continuously without destabilizing the platform as it grows
+- Make the agent platform integration-ready — build the connective tissue so agents, tools, context, and data compose cleanly across products, and match the right agentic architecture to each use case
+- Own evals and benchmarks — build production-grade eval harnesses, replay, and benchmarks for agentic AI, and gate releases on them; in healthcare finance, accuracy is non-negotiable
+- Lead context and harness engineering — establish best practices for grounding agents in each customer's business rules and data, and for the control loops that keep outputs reliable
+- Fine-tune and evaluate models — fine-tune in-house and open-source models, benchmark them against frontier baselines, and make the build-vs-buy calls on model, framework, and infra
+- Turn capabilities into an ecosystem — build reusable core capabilities that translate across features and products, and ship them end-to-end with product and design
+What You Have
+- 3+ years of software engineering experience, with meaningful production work in Python
+- Direct experience shipping LLM-powered or agentic systems in production — not just prototypes. You know where models fail and how to make them reliable
+- Hands-on experience with at least one modern agent framework (LangGraph, Google ADK, LlamaIndex, Claude Agent SDK, or equivalent), and a clear point of view on what to use vs. build
+- Production evals and benchmarking — you've built eval harnesses and benchmarks that gate real releases, not one-off spot checks
+- Context engineering — grounding agents through retrieval, context layers, and knowledge transfer so outputs match a specific org or user
+- Comfort with the data and retrieval layer — SQL, BigQuery or a comparable warehouse, embeddings, and vector search
+- A bias toward shipping — you take an ambiguous problem to a working V1 fast, then iterate
+Plus deep, demonstrable expertise in at least one (ideally two) of the following:
+- Tool-surface and connector platform engineering — standardized tool/skill contracts (e.g., MCP) and connector ecosystems that scale without breaking
+- Harness and loop engineering — agent control loops, orchestration, and inference harnesses; right-sizing agent architecture per use case and keeping it reliable at scale
+- Open-source and in-house model fine-tuning — fine-tuning open models and benchmarking them against frontier baselines
+- Production context-layer engineering — systems that capture business rules and preferences and feed them to agents reliably
+Nice to Have
+- Experience with healthcare finance, accounting, or other structured financial data — or genuine curiosity about it
+- Applied ML or model-evaluation research background
+- Open-source contributions to agent or LLM tooling
+- Experience designing tool-use APIs or developer-facing AI products
+- Familiarity with our stack: Vertex AI (Gemini, Claude on Vertex), GenKit, MCP, BigQuery
+Experience Level
+We're looking for engineers who own meaningful surface area and drive work forward independently. You'll bring sharp judgment on architecture and build-vs-buy trade-offs under ambiguity, a bias toward shipping a working V1 fast, and the craft to make agentic systems reliable enough for healthcare finance — not just demos.
+https://www.translucent.co/
+Base Salary: $175,000-$275,000 USD + equity</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Hospitals and Health Care</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'addressLocality': 'New York', 'addressRegion': 'New York', 'postalCode': '10003', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>https://www.translucent.ai</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>The AI-native platform for healthcare finance.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Hospitals and clinics shouldn't have to choose between financial health and patient health. But today, they do.
+Healthcare finance teams are drowning in manual data work—pulling numbers from multiple systems, building spreadsheets, answering endless questions from operators. By the time they finish analyzing last month's performance, they're already behind on this month's decisions.
+The result? Finance leaders are forced to make difficult tradeoffs: cut services to stay solvent, or keep services running and risk financial instability.
+What We Do
+Translucent is healthcare's financial operating system. We automate the manual data work that consumes finance teams—connecting fragmented data sources, running analyses, and surfacing insights instantly.
+Instead of spending days building reports, finance teams can focus on what matters: moving the margin and making strategic decisions that improve both financial performance and patient care.
+Why It Matters
+When healthcare finance teams have the financial clarity they need, hospitals can maintain strong margins while delivering excellent patient care. No more forced tradeoffs between the two.
+We serve health systems and medical groups across the United States—from large multi-billion dollar organizations to small rural hospitals where every decision affects whether patients can access care locally.
+Our Team &amp; Backing
+Translucent is backed by GV, NEA, FPV Ventures, Virtue, and Redesign Health. We're headquartered in New York City and bring together expertise in agentic AI, healthcare operations, and enterprise software.</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4454317490</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>iePAq0f204NqU2YILM222w==</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-ml-engineer-at-capgemini-4454317490?position=3&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=iePAq0f204NqU2YILM222w%3D%3D</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://fr.linkedin.com/company/capgemini?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQHIL3HctxNfvg/company-logo_100_100/B4EZokv7VQIUAQ-/0/1761553135376/capgemini_logo?e=2147483647&amp;v=beta&amp;t=zG4Rnn4ZR9lwfNpFaLXXm6DKX3XwtS0cYTIC2dDtWfg</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Atlanta, GA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Choosing Capgemini means choosing a company where you will be empowered to shape your career in the way you’d like, where you’ll be supported and inspired by a collaborative community of colleagues around the world, and where you’ll be able to reimagine what’s possible. Join us and help the world’s leading organizations unlock the value of technology and build a more sustainable, more inclusive world.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Job Location: Atlanta, GA/ NYC, NY&lt;br&gt;&lt;br&gt;&lt;/strong&gt;&lt;strong&gt;Responsibilities&lt;br&gt;&lt;br&gt;&lt;/strong&gt;We are seeking a highly skilled AIML Engineer with strong hands‑on experience in Python, modern AI/LLM integration, API development, and distributed data technologies.&lt;br&gt;&lt;br&gt;This role will focus on building, integrating, and deploying AI/ML models-particularly those involving Large Language Models (LLMs), agentic AI workflows, and real‑time data pipelines.&lt;br&gt;&lt;br&gt;The ideal candidate will have a strong engineering background with a deep understanding of ML systems design, inferencing pipelines, and microservices‑based APIs.&lt;br&gt;&lt;br&gt;Experience working in Agile environments and collaborating with cross‑functional teams is essential.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Required Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Python&lt;br&gt;&lt;br&gt;Experience in Integration LLM&lt;br&gt;&lt;br&gt;FAST API&lt;br&gt;&lt;br&gt;Kafka Integration&lt;br&gt;&lt;br&gt;Rest API Integration for ML Models&lt;br&gt;&lt;br&gt;GitHub and CoPilot&lt;br&gt;&lt;br&gt;Agentic AI Implementation&lt;br&gt;&lt;br&gt;&lt;strong&gt;Good‑to‑Have Skills&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Java/Angular&lt;br&gt;&lt;br&gt;Spring Boot&lt;br&gt;&lt;br&gt;CI/CD&lt;br&gt;&lt;br&gt;Containerization (Docket, Kubernetes)&lt;br&gt;&lt;br&gt;Cloud ML platforms&lt;br&gt;&lt;br&gt;Finance domain Experience&lt;br&gt;&lt;br&gt;&lt;strong&gt;Life at Capgemini&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Capgemini supports all aspects of your well-being throughout the changing stages of your life and career. For eligible employees, we offer:&lt;br&gt;&lt;br&gt;Flexible work&lt;br&gt;&lt;br&gt;Healthcare including dental, vision, mental health, and well-being programs&lt;br&gt;&lt;br&gt;Financial well-being programs such as 401(k) and Employee Share Ownership Plan&lt;br&gt;&lt;br&gt;Paid time off and paid holidays&lt;br&gt;&lt;br&gt;Paid parental leave&lt;br&gt;&lt;br&gt;Family building benefits like adoption assistance, surrogacy, and cryopreservation&lt;br&gt;&lt;br&gt;Social well-being benefits like subsidized back-up child/elder care and tutoring&lt;br&gt;&lt;br&gt;Mentoring, coaching and learning programs&lt;br&gt;&lt;br&gt;Employee Resource Groups nd Qualifications required for this position. Physical, mental, sensory or environmental demands may be referenced in an attempt to communicate the manner in which this position traditionally is performed. Whenever necessary to provide individuals with disabilities an equal employment opportunity, Capgemini will consider reasonable accommodations that might involve varying job requirements and/or changing the way this job is performed, provided that such accommodations do not pose an undue hardship.&lt;br&gt;&lt;br&gt;Capgemini is committed to providing reasonable accommodations&lt;br&gt;&lt;br&gt;Disaster Relief&lt;br&gt;&lt;br&gt;The base compensation range for this role in the posted location is: 103330 to 128656&lt;br&gt;&lt;br&gt;Capgemini provides compensation range information in accordance with applicable national, state, provincial, and local pay transparency laws. The base compensation range listed for this position reflects the minimum and maximum target compensation Capgemini, in good faith, believes it may pay for the role at the time of this posting. This range may be subject to change as permitted by law.&lt;br&gt;&lt;br&gt;The actual compensation offered to any candidate may fall outside of the posted range and will be determined based on multiple factors legally permitted in the applicable jurisdiction.&lt;br&gt;&lt;br&gt;These may include, but are not limited to: Geographic location, Education and qualifications, Certifications and licenses, Relevant experience and skills, Seniority and performance, Market and business consideration, Internal pay equity.&lt;br&gt;&lt;br&gt;It is not typical for candidates to be hired at or near the top of the posted compensation range.&lt;br&gt;&lt;br&gt;In addition to base salary, this role may be eligible for additional compensation such as variable incentives, bonuses, or commissions, depending on the position and applicable laws.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Capgemini offers a comprehensive, non-negotiable benefits package to all regular, full-time employees.&lt;/strong&gt; In the U.S. and Canada, available benefits are determined by local policy and eligibility and may include:&lt;br&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Paid time off based on employee grade (A-F), defined by policy: Vacation: 12-25 days, depending on grade, Company paid holidays, Personal Days, Sick Leave&lt;/li&gt;&lt;li&gt;Medical, dental, and vision coverage (or provincial healthcare coordination in Canada)&lt;/li&gt;&lt;li&gt;Retirement savings plans (e.g., 401(k) in the U.S., RRSP in Canada)&lt;/li&gt;&lt;li&gt;Life and disability insurance&lt;/li&gt;&lt;li&gt;Employee assistance programs&lt;/li&gt;&lt;li&gt;Other benefits as provided by local policy and eligibility&lt;br&gt;&lt;br&gt;&lt;/li&gt;&lt;/ul&gt;&lt;strong&gt;Important Notice:&lt;/strong&gt; Compensation (including bonuses, commissions, or other forms of incentive pay) is not considered earned, vested, or payable until it becomes due under the terms of applicable plans or agreements and is subject to Capgemini’s discretion, consistent with applicable laws. The Company reserves the right to amend or withdraw compensation programs at any time, within the limits of applicable legislation.&lt;br&gt;&lt;br&gt;&lt;strong&gt;Disclaimers&lt;br&gt;&lt;br&gt;&lt;/strong&gt;Capgemini is an Equal Opportunity Employer encouraging inclusion in the workplace. Capgemini also participates in the Partnership Accreditation in Indigenous Relations (PAIR) program which supports meaningful engagement with Indigenous communities across Canada by promoting fairness, accessibility, inclusion and respect. We value the rich cultural heritage and contributions of Indigenous Peoples and actively work to create a welcoming and respectful environment. All qualified applicants will receive consideration for employment without regard to race, national origin, gender identity/expression, age, religion, disability, sexual orientation, genetics, veteran status, marital status or any other characteristic protected by law.&lt;br&gt;&lt;br&gt;This is a general description of the Duties, Responsibilities and Qualifications required for this position. Physical, mental, sensory or environmental demands may be referenced in an attempt to communicate the manner in which this position traditionally is performed. Whenever necessary to provide individuals with disabilities an equal employment opportunity, Capgemini will consider reasonable accommodations that might involve varying job requirements and/or changing the way this job is performed, provided that such accommodation does not pose an undue hardship. Capgemini is committed to providing reasonable accommodation during our recruitment process. If you need assistance or accommodation, please reach out to your recruiting contact.&lt;br&gt;&lt;br&gt;Please be aware that Capgemini may capture your image (video or screenshot) during the interview process and that image may be used for verification, including during the hiring and onboarding process.&lt;br&gt;&lt;br&gt;Click the following link for more information on your rights as an Applicant in the United States. http://www.capgemini.com/resources/equal-employment-opportunity-is-the-law&lt;br&gt;&lt;br&gt;Capgemini is a global business and technology transformation partner, helping organizations to accelerate their dual transition to a digital and sustainable world, while creating tangible impact for enterprises and society. It is a responsible and diverse group of 340,000 team members in more than 50 countries. With its strong over 55-year heritage, Capgemini is trusted by its clients to unlock the value of technology to address the entire breadth of their business needs. It delivers end-to-end services and solutions leveraging strengths from strategy and design to engineering, all fueled by its market leading capabilities in AI, generative AI, cloud and data, combined with its deep industry expertise and partner ecosystem.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Choosing Capgemini means choosing a company where you will be empowered to shape your career in the way you’d like, where you’ll be supported and inspired by a collaborative community of colleagues around the world, and where you’ll be able to reimagine what’s possible. Join us and help the world’s leading organizations unlock the value of technology and build a more sustainable, more inclusive world.
+Job Location: Atlanta, GA/ NYC, NY
+Responsibilities
+We are seeking a highly skilled AIML Engineer with strong hands‑on experience in Python, modern AI/LLM integration, API development, and distributed data technologies.
+This role will focus on building, integrating, and deploying AI/ML models-particularly those involving Large Language Models (LLMs), agentic AI workflows, and real‑time data pipelines.
+The ideal candidate will have a strong engineering background with a deep understanding of ML systems design, inferencing pipelines, and microservices‑based APIs.
+Experience working in Agile environments and collaborating with cross‑functional teams is essential.
+Required Skills
+Python
+Experience in Integration LLM
+FAST API
+Kafka Integration
+Rest API Integration for ML Models
+GitHub and CoPilot
+Agentic AI Implementation
+Good‑to‑Have Skills
+Java/Angular
+Spring Boot
+CI/CD
+Containerization (Docket, Kubernetes)
+Cloud ML platforms
+Finance domain Experience
+Life at Capgemini
+Capgemini supports all aspects of your well-being throughout the changing stages of your life and career. For eligible employees, we offer:
+Flexible work
+Healthcare including dental, vision, mental health, and well-being programs
+Financial well-being programs such as 401(k) and Employee Share Ownership Plan
+Paid time off and paid holidays
+Paid parental leave
+Family building benefits like adoption assistance, surrogacy, and cryopreservation
+Social well-being benefits like subsidized back-up child/elder care and tutoring
+Mentoring, coaching and learning programs
+Employee Resource Groups nd Qualifications required for this position. Physical, mental, sensory or environmental demands may be referenced in an attempt to communicate the manner in which this position traditionally is performed. Whenever necessary to provide individuals with disabilities an equal employment opportunity, Capgemini will consider reasonable accommodations that might involve varying job requirements and/or changing the way this job is performed, provided that such accommodations do not pose an undue hardship.
+Capgemini is committed to providing reasonable accommodations
+Disaster Relief
+The base compensation range for this role in the posted location is: 103330 to 128656
+Capgemini provides compensation range information in accordance with applicable national, state, provincial, and local pay transparency laws. The base compensation range listed for this position reflects the minimum and maximum target compensation Capgemini, in good faith, believes it may pay for the role at the time of this posting. This range may be subject to change as permitted by law.
+The actual compensation offered to any candidate may fall outside of the posted range and will be determined based on multiple factors legally permitted in the applicable jurisdiction.
+These may include, but are not limited to: Geographic location, Education and qualifications, Certifications and licenses, Relevant experience and skills, Seniority and performance, Market and business consideration, Internal pay equity.
+It is not typical for candidates to be hired at or near the top of the posted compensation range.
+In addition to base salary, this role may be eligible for additional compensation such as variable incentives, bonuses, or commissions, depending on the position and applicable laws.
+Capgemini offers a comprehensive, non-negotiable benefits package to all regular, full-time employees. In the U.S. and Canada, available benefits are determined by local policy and eligibility and may include:
+- Paid time off based on employee grade (A-F), defined by policy: Vacation: 12-25 days, depending on grade, Company paid holidays, Personal Days, Sick Leave
+- Medical, dental, and vision coverage (or provincial healthcare coordination in Canada)
+- Retirement savings plans (e.g., 401(k) in the U.S., RRSP in Canada)
+- Life and disability insurance
+- Employee assistance programs
+- Other benefits as provided by local policy and eligibility
+Important Notice: Compensation (including bonuses, commissions, or other forms of incentive pay) is not considered earned, vested, or payable until it becomes due under the terms of applicable plans or agreements and is subject to Capgemini’s discretion, consistent with applicable laws. The Company reserves the right to amend or withdraw compensation programs at any time, within the limits of applicable legislation.
+Disclaimers
+Capgemini is an Equal Opportunity Employer encouraging inclusion in the workplace. Capgemini also participates in the Partnership Accreditation in Indigenous Relations (PAIR) program which supports meaningful engagement with Indigenous communities across Canada by promoting fairness, accessibility, inclusion and respect. We value the rich cultural heritage and contributions of Indigenous Peoples and actively work to create a welcoming and respectful environment. All qualified applicants will receive consideration for employment without regard to race, national origin, gender identity/expression, age, religion, disability, sexual orientation, genetics, veteran status, marital status or any other characteristic protected by law.
+This is a general description of the Duties, Responsibilities and Qualifications required for this position. Physical, mental, sensory or environmental demands may be referenced in an attempt to communicate the manner in which this position traditionally is performed. Whenever necessary to provide individuals with disabilities an equal employment opportunity, Capgemini will consider reasonable accommodations that might involve varying job requirements and/or changing the way this job is performed, provided that such accommodation does not pose an undue hardship. Capgemini is committed to providing reasonable accommodation during our recruitment process. If you need assistance or accommodation, please reach out to your recruiting contact.
+Please be aware that Capgemini may capture your image (video or screenshot) during the interview process and that image may be used for verification, including during the hiring and onboarding process.
+Click the following link for more information on your rights as an Applicant in the United States. http://www.capgemini.com/resources/equal-employment-opportunity-is-the-law
+Capgemini is a global business and technology transformation partner, helping organizations to accelerate their dual transition to a digital and sustainable world, while creating tangible impact for enterprises and society. It is a responsible and diverse group of 340,000 team members in more than 50 countries. With its strong over 55-year heritage, Capgemini is trusted by its clients to unlock the value of technology to address the entire breadth of their business needs. It delivers end-to-end services and solutions leveraging strengths from strategy and design to engineering, all fueled by its market leading capabilities in AI, generative AI, cloud and data, combined with its deep industry expertise and partner ecosystem.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>IT Services and IT Consulting</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': "Place de l'Étoile", 'addressLocality': 'Paris', 'addressRegion': 'France', 'postalCode': '75017', 'addressCountry': 'FR'}</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>https://www.capgemini.com</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Make it real.</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capgemini is an AI-powered global business and technology transformation partner, delivering tangible business value. We imagine the future of organizations and make it real with AI, technology and people. With our strong heritage of nearly 60 years, we are a responsible and diverse group of 420,000 team members in more than 50 countries. We deliver end-to-end services and solutions with our deep industry expertise and strong partner ecosystem, leveraging our capabilities across strategy, technology, design, engineering and business operations. The Group reported 2025 global revenues of €22.5 billion.
+Make it real | www.capgemini.com
+</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>347372</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4454367102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>AJ+4G+1PpZWM90ASw6AeVw==</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hqan1SC6SBVwlDMjIWeHxQ==</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/applied-ai-engineer-at-meeboss-4454367102?position=2&amp;pageNum=0&amp;refId=Hqan1SC6SBVwlDMjIWeHxQ%3D%3D&amp;trackingId=AJ%2B4G%2B1PpZWM90ASw6AeVw%3D%3D</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MeeBoss</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meeboss?trk=public_jobs_jserp-result_job-search-card-subtitle</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQH7KwZNWpOqRg/company-logo_100_100/B56ZcuuX28GsAQ-/0/1748835598284/meeboss_logo?e=2147483647&amp;v=beta&amp;t=kIyFeq5olRjgZVEaLtZYV4GgvbbKxUxoI-Xw6gtzuHY</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;About the job&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;MeeBoss is sharing this active opportunity on behalf of the hiring company. This role involves building systems that automate finance operations by deploying AI to operate computers like humans, navigating browsers, processing documents, and working through legacy systems for large enterprises.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;The position focuses on browser agent reliability, document understanding, and inference optimization to improve accuracy and speed.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Job title&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Applied AI Engineer&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Company&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;MeeBoss&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Location&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;San Francisco, CA On-site&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Compensation&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;$180,000-250,000/year&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What you will do&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Work on browser agent reliability, document understanding, and inference optimization.&lt;/li&gt;&lt;li&gt;Push to state-of-the-art across core automation capabilities including UI interaction, unstructured data parsing, and tool use.&lt;/li&gt;&lt;li&gt;Build adaptive systems that self-heal when environments change.&lt;/li&gt;&lt;li&gt;Design fine-tuning pipelines that learn from customer-specific workflows.&lt;/li&gt;&lt;li&gt;Optimize latency across the stack through model selection, quantization, caching, and routing strategies.&lt;/li&gt;&lt;li&gt;Turn research into production systems.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What we are looking for&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Strong Python expertise and proficiency in ML frameworks, particularly PyTorch.&lt;/li&gt;&lt;li&gt;Eval-and-metric mindset, focusing on production metrics rather than just benchmarks.&lt;/li&gt;&lt;li&gt;Comfort with messy data and the ability to make it useful.&lt;/li&gt;&lt;li&gt;Track record of shipping end-to-end systems.&lt;/li&gt;&lt;li&gt;Clear communication skills to describe work without buzzwords.&lt;/li&gt;&lt;li&gt;Based in San Francisco or willing to relocate for in-person work 5 days a week.&lt;/li&gt;&lt;li&gt;Experience with RL, retrieval systems, or agent-based systems (Nice-to-have).&lt;/li&gt;&lt;li&gt;Cross-stack range including inference optimization, data pipelines, fine-tuning, and model monitoring (Nice-to-have).&lt;/li&gt;&lt;li&gt;Published ML papers or significant OSS contributions (Nice-to-have).&lt;/li&gt;&lt;li&gt;Lab or research exposure (Nice-to-have).&lt;/li&gt;&lt;li&gt;Recent applied work on LLMs, browser agents, RAG, or production AI workflows (Nice-to-have).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;About MeeBoss&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;MeeBoss helps job seekers and hiring teams make direct, relevant career connections.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+About the job
+MeeBoss is sharing this active opportunity on behalf of the hiring company. This role involves building systems that automate finance operations by deploying AI to operate computers like humans, navigating browsers, processing documents, and working through legacy systems for large enterprises.
+The position focuses on browser agent reliability, document understanding, and inference optimization to improve accuracy and speed.
+Job title
+Applied AI Engineer
+Company
+MeeBoss
+Location
+San Francisco, CA On-site
+Compensation
+$180,000-250,000/year
+What you will do
+- Work on browser agent reliability, document understanding, and inference optimization.
+- Push to state-of-the-art across core automation capabilities including UI interaction, unstructured data parsing, and tool use.
+- Build adaptive systems that self-heal when environments change.
+- Design fine-tuning pipelines that learn from customer-specific workflows.
+- Optimize latency across the stack through model selection, quantization, caching, and routing strategies.
+- Turn research into production systems.
+What we are looking for
+- Strong Python expertise and proficiency in ML frameworks, particularly PyTorch.
+- Eval-and-metric mindset, focusing on production metrics rather than just benchmarks.
+- Comfort with messy data and the ability to make it useful.
+- Track record of shipping end-to-end systems.
+- Clear communication skills to describe work without buzzwords.
+- Based in San Francisco or willing to relocate for in-person work 5 days a week.
+- Experience with RL, retrieval systems, or agent-based systems (Nice-to-have).
+- Cross-stack range including inference optimization, data pipelines, fine-tuning, and model monitoring (Nice-to-have).
+- Published ML papers or significant OSS contributions (Nice-to-have).
+- Lab or research exposure (Nice-to-have).
+- Recent applied work on LLMs, browser agents, RAG, or production AI workflows (Nice-to-have).
+About MeeBoss
+MeeBoss helps job seekers and hiring teams make direct, relevant career connections.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Mid-Senior level</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Engineering, Information Technology, and Marketing</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Human Resources Services</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/search/?position=1&amp;pageNum=0&amp;keywords=AI+Engineer&amp;location=United+States&amp;distance=0&amp;f_TPR=r86400</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>{'type': 'PostalAddress', 'streetAddress': '10800 NE 8th St', 'addressLocality': 'Bellevue', 'addressRegion': 'Washington', 'postalCode': '98004', 'addressCountry': 'US'}</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>meeboss.com</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>We simplify hiring through fast job matching and direct connections, all in one seamless platform.</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>MeeBoss is transforming the hiring experience by building the human connection early. Experience the transformative power of our innovative job-matching and direct chat platform designed to help companies find the right talent faster and more affordably. Personalized matches and direct two-way engagement empowers job seekers and employers to quickly connect, assess fit, and advance the process. Skip the noise – Download MeeBoss today!</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2026-08-14 05:10:51</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Wenjing Zhou</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>https://static.licdn.com/aero-v1/sc/h/9c8pery4andzj6ohjkjp54ma2</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wenjing-zhou-84a117422</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
